--- a/research/traditional_assets/database/data/belgium/belgium_household_products.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_household_products.xlsx
@@ -644,10 +644,10 @@
         <v>0.05537074793432772</v>
       </c>
       <c r="X2">
-        <v>0.1095059946497601</v>
+        <v>0.1094762433221848</v>
       </c>
       <c r="Y2">
-        <v>-0.05413524671543238</v>
+        <v>-0.05410549538785712</v>
       </c>
       <c r="Z2">
         <v>2.366152725506859</v>
@@ -656,10 +656,10 @@
         <v>0.1610109549812923</v>
       </c>
       <c r="AB2">
-        <v>0.08258033827055625</v>
+        <v>0.08256625479005944</v>
       </c>
       <c r="AC2">
-        <v>0.07843061671073601</v>
+        <v>0.07844470019123281</v>
       </c>
       <c r="AD2">
         <v>784.2</v>
@@ -775,10 +775,10 @@
         <v>0.05537074793432772</v>
       </c>
       <c r="X3">
-        <v>0.1095059946497601</v>
+        <v>0.1094762433221848</v>
       </c>
       <c r="Y3">
-        <v>-0.05413524671543238</v>
+        <v>-0.05410549538785712</v>
       </c>
       <c r="Z3">
         <v>2.366152725506859</v>
@@ -787,10 +787,10 @@
         <v>0.1610109549812923</v>
       </c>
       <c r="AB3">
-        <v>0.08258033827055625</v>
+        <v>0.08256625479005944</v>
       </c>
       <c r="AC3">
-        <v>0.07843061671073601</v>
+        <v>0.07844470019123281</v>
       </c>
       <c r="AD3">
         <v>784.2</v>
@@ -1127,49 +1127,49 @@
         <v>2.89613034623218</v>
       </c>
       <c r="F2">
-        <v>4.50736313117696</v>
+        <v>4.59432151473672</v>
       </c>
       <c r="G2">
         <v>4.23205612520237</v>
       </c>
       <c r="H2">
-        <v>3.53590933621155</v>
+        <v>3.61627091203454</v>
       </c>
       <c r="I2">
         <v>0.526626821570076</v>
       </c>
       <c r="J2">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="K2">
         <v>704.9</v>
       </c>
       <c r="L2">
-        <v>1051.46083984824</v>
+        <v>1086.03068907853</v>
       </c>
       <c r="M2">
         <v>1396.6</v>
       </c>
       <c r="N2">
-        <v>1614.16483984824</v>
+        <v>1663.62568907853</v>
       </c>
       <c r="O2">
         <v>784.2</v>
       </c>
       <c r="P2">
-        <v>655.204</v>
+        <v>670.095</v>
       </c>
       <c r="Q2">
-        <v>0.08258033827055621</v>
+        <v>0.0825662547900594</v>
       </c>
       <c r="R2">
-        <v>0.0776229087640693</v>
+        <v>0.076664966667014</v>
       </c>
       <c r="S2">
         <v>0.0583774624969006</v>
       </c>
       <c r="T2">
-        <v>0.0478774624969006</v>
+        <v>0.0459274624969006</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1182,16 +1182,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.10950599464976</v>
+        <v>0.109476243322185</v>
       </c>
       <c r="X2">
-        <v>0.10099433083113</v>
+        <v>0.101813833715289</v>
       </c>
       <c r="Y2">
         <v>1.24116850287875</v>
       </c>
       <c r="Z2">
-        <v>1.07533781305346</v>
+        <v>1.09181387760484</v>
       </c>
       <c r="AA2">
         <v>784.1999999999999</v>
@@ -1224,7 +1224,7 @@
         <v>704.9</v>
       </c>
       <c r="AK2">
-        <v>0.05132743418963755</v>
+        <v>0.0513034637718367</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1412,13 +1412,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.08052901715217191</v>
+        <v>0.08051279835877041</v>
       </c>
       <c r="C2">
-        <v>1571.592258890672</v>
+        <v>1571.716711631768</v>
       </c>
       <c r="D2">
-        <v>1479.092258890672</v>
+        <v>1479.216711631768</v>
       </c>
       <c r="E2">
         <v>-784.1999999999999</v>
@@ -1463,19 +1463,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.08052901715217191</v>
+        <v>0.08051279835877041</v>
       </c>
       <c r="T2">
         <v>0.6766170509100436</v>
       </c>
       <c r="U2">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V2">
         <v>0.25</v>
       </c>
       <c r="W2">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1494,13 +1494,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.08041646923426048</v>
+        <v>0.08038979098784249</v>
       </c>
       <c r="C3">
-        <v>1561.510205551596</v>
+        <v>1562.086066017674</v>
       </c>
       <c r="D3">
-        <v>1483.901205551596</v>
+        <v>1484.477066017674</v>
       </c>
       <c r="E3">
         <v>-769.309</v>
@@ -1527,37 +1527,37 @@
         <v>188.525</v>
       </c>
       <c r="M3">
-        <v>0.8582668587217953</v>
+        <v>0.8374194587217952</v>
       </c>
       <c r="N3">
-        <v>187.6667331412782</v>
+        <v>187.6875805412782</v>
       </c>
       <c r="O3">
-        <v>46.91668328531954</v>
+        <v>46.92189513531955</v>
       </c>
       <c r="P3">
-        <v>140.7500498559586</v>
+        <v>140.7656854059586</v>
       </c>
       <c r="Q3">
-        <v>183.8500498559586</v>
+        <v>183.8656854059587</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.08079211576696109</v>
+        <v>0.08077577410391261</v>
       </c>
       <c r="T3">
         <v>0.6817429376593621</v>
       </c>
       <c r="U3">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V3">
         <v>0.25</v>
       </c>
       <c r="W3">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>219.6577883489147</v>
+        <v>225.1261276968143</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1576,13 +1576,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.08030392131634904</v>
+        <v>0.08026678361691457</v>
       </c>
       <c r="C4">
-        <v>1551.459524700827</v>
+        <v>1552.492967415239</v>
       </c>
       <c r="D4">
-        <v>1488.741524700827</v>
+        <v>1489.774967415239</v>
       </c>
       <c r="E4">
         <v>-754.4179999999999</v>
@@ -1609,37 +1609,37 @@
         <v>188.525</v>
       </c>
       <c r="M4">
-        <v>1.716533717443591</v>
+        <v>1.67483891744359</v>
       </c>
       <c r="N4">
-        <v>186.8084662825564</v>
+        <v>186.8501610825564</v>
       </c>
       <c r="O4">
-        <v>46.7021165706391</v>
+        <v>46.7125402706391</v>
       </c>
       <c r="P4">
-        <v>140.1063497119173</v>
+        <v>140.1376208119173</v>
       </c>
       <c r="Q4">
-        <v>183.2063497119173</v>
+        <v>183.2376208119173</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.08106058374123576</v>
+        <v>0.08104411670099648</v>
       </c>
       <c r="T4">
         <v>0.6869734343423403</v>
       </c>
       <c r="U4">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V4">
         <v>0.25</v>
       </c>
       <c r="W4">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>109.8288941744573</v>
+        <v>112.5630638484071</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1658,13 +1658,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.08019137339843763</v>
+        <v>0.08014377624598665</v>
       </c>
       <c r="C5">
-        <v>1541.440524343649</v>
+        <v>1542.937819265177</v>
       </c>
       <c r="D5">
-        <v>1493.613524343649</v>
+        <v>1495.110819265177</v>
       </c>
       <c r="E5">
         <v>-739.5269999999999</v>
@@ -1691,37 +1691,37 @@
         <v>188.525</v>
       </c>
       <c r="M5">
-        <v>2.574800576165385</v>
+        <v>2.512258376165386</v>
       </c>
       <c r="N5">
-        <v>185.9501994238346</v>
+        <v>186.0127416238346</v>
       </c>
       <c r="O5">
-        <v>46.48754985595865</v>
+        <v>46.50318540595865</v>
       </c>
       <c r="P5">
-        <v>139.4626495678759</v>
+        <v>139.5095562178759</v>
       </c>
       <c r="Q5">
-        <v>182.562649567876</v>
+        <v>182.609556217876</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.08133458713766042</v>
+        <v>0.08131799213513363</v>
       </c>
       <c r="T5">
         <v>0.6923117763177508</v>
       </c>
       <c r="U5">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V5">
         <v>0.25</v>
       </c>
       <c r="W5">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>73.21926278297158</v>
+        <v>75.04204256560476</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1740,13 +1740,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.08007882548052622</v>
+        <v>0.08002076887505874</v>
       </c>
       <c r="C6">
-        <v>1531.45351653045</v>
+        <v>1533.421030808907</v>
       </c>
       <c r="D6">
-        <v>1498.51751653045</v>
+        <v>1500.485030808907</v>
       </c>
       <c r="E6">
         <v>-724.636</v>
@@ -1773,37 +1773,37 @@
         <v>188.525</v>
       </c>
       <c r="M6">
-        <v>3.433067434887181</v>
+        <v>3.349677834887181</v>
       </c>
       <c r="N6">
-        <v>185.0919325651128</v>
+        <v>185.1753221651128</v>
       </c>
       <c r="O6">
-        <v>46.2729831412782</v>
+        <v>46.2938305412782</v>
       </c>
       <c r="P6">
-        <v>138.8189494238346</v>
+        <v>138.8814916238346</v>
       </c>
       <c r="Q6">
-        <v>181.9189494238346</v>
+        <v>181.9814916238346</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.08161429893817729</v>
+        <v>0.08159757330748199</v>
       </c>
       <c r="T6">
         <v>0.6977613337509825</v>
       </c>
       <c r="U6">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V6">
         <v>0.25</v>
       </c>
       <c r="W6">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>54.91444708722867</v>
+        <v>56.28153192420357</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1822,13 +1822,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.07996627756261479</v>
+        <v>0.07989776150413082</v>
       </c>
       <c r="C7">
-        <v>1521.498817423347</v>
+        <v>1523.943017193194</v>
       </c>
       <c r="D7">
-        <v>1503.453817423347</v>
+        <v>1505.898017193194</v>
       </c>
       <c r="E7">
         <v>-709.7449999999999</v>
@@ -1855,37 +1855,37 @@
         <v>188.525</v>
       </c>
       <c r="M7">
-        <v>4.291334293608976</v>
+        <v>4.187097293608977</v>
       </c>
       <c r="N7">
-        <v>184.233665706391</v>
+        <v>184.337902706391</v>
       </c>
       <c r="O7">
-        <v>46.05841642659775</v>
+        <v>46.08447567659775</v>
       </c>
       <c r="P7">
-        <v>138.1752492797933</v>
+        <v>138.2534270297932</v>
       </c>
       <c r="Q7">
-        <v>181.2752492797933</v>
+        <v>181.3534270297933</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.0818998994081787</v>
+        <v>0.08188304039924819</v>
       </c>
       <c r="T7">
         <v>0.7033256187091244</v>
       </c>
       <c r="U7">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V7">
         <v>0.25</v>
       </c>
       <c r="W7">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>43.93155766978294</v>
+        <v>45.02522553936285</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1904,13 +1904,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.07985372964470336</v>
+        <v>0.0797747541332029</v>
       </c>
       <c r="C8">
-        <v>1511.576747364133</v>
+        <v>1514.504199577038</v>
       </c>
       <c r="D8">
-        <v>1508.422747364133</v>
+        <v>1511.350199577038</v>
       </c>
       <c r="E8">
         <v>-694.8539999999999</v>
@@ -1937,37 +1937,37 @@
         <v>188.525</v>
       </c>
       <c r="M8">
-        <v>5.149601152330771</v>
+        <v>5.024516752330771</v>
       </c>
       <c r="N8">
-        <v>183.3753988476692</v>
+        <v>183.5004832476692</v>
       </c>
       <c r="O8">
-        <v>45.8438497119173</v>
+        <v>45.8751208119173</v>
       </c>
       <c r="P8">
-        <v>137.5315491357519</v>
+        <v>137.6253624357519</v>
       </c>
       <c r="Q8">
-        <v>180.6315491357519</v>
+        <v>180.7253624357519</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.08219157648392482</v>
+        <v>0.08217458125892432</v>
       </c>
       <c r="T8">
         <v>0.7090082927089287</v>
       </c>
       <c r="U8">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V8">
         <v>0.25</v>
       </c>
       <c r="W8">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>36.60963139148579</v>
+        <v>37.52102128280238</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1986,13 +1986,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.07974118172679194</v>
+        <v>0.07965174676227496</v>
       </c>
       <c r="C9">
-        <v>1501.687630943574</v>
+        <v>1505.105005240921</v>
       </c>
       <c r="D9">
-        <v>1513.424630943574</v>
+        <v>1516.842005240921</v>
       </c>
       <c r="E9">
         <v>-679.963</v>
@@ -2019,37 +2019,37 @@
         <v>188.525</v>
       </c>
       <c r="M9">
-        <v>6.007868011052567</v>
+        <v>5.861936211052567</v>
       </c>
       <c r="N9">
-        <v>182.5171319889474</v>
+        <v>182.6630637889474</v>
       </c>
       <c r="O9">
-        <v>45.62928299723685</v>
+        <v>45.66576594723685</v>
       </c>
       <c r="P9">
-        <v>136.8878489917105</v>
+        <v>136.9972978417105</v>
       </c>
       <c r="Q9">
-        <v>179.9878489917106</v>
+        <v>180.0972978417106</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.08248952618495581</v>
+        <v>0.08247239181450745</v>
       </c>
       <c r="T9">
         <v>0.7148131747517397</v>
       </c>
       <c r="U9">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V9">
         <v>0.25</v>
       </c>
       <c r="W9">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>31.37968404984495</v>
+        <v>32.16087538525917</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2068,13 +2068,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.07962863380888051</v>
+        <v>0.07952873939134704</v>
       </c>
       <c r="C10">
-        <v>1491.831797072093</v>
+        <v>1495.745867698419</v>
       </c>
       <c r="D10">
-        <v>1518.459797072093</v>
+        <v>1522.373867698419</v>
       </c>
       <c r="E10">
         <v>-665.0719999999999</v>
@@ -2101,37 +2101,37 @@
         <v>188.525</v>
       </c>
       <c r="M10">
-        <v>6.866134869774362</v>
+        <v>6.699355669774362</v>
       </c>
       <c r="N10">
-        <v>181.6588651302256</v>
+        <v>181.8256443302256</v>
       </c>
       <c r="O10">
-        <v>45.41471628255641</v>
+        <v>45.45641108255641</v>
       </c>
       <c r="P10">
-        <v>136.2441488476692</v>
+        <v>136.3692332476692</v>
       </c>
       <c r="Q10">
-        <v>179.3441488476692</v>
+        <v>179.4692332476693</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.08279395305340051</v>
+        <v>0.08277667651260326</v>
       </c>
       <c r="T10">
         <v>0.7207442498824378</v>
       </c>
       <c r="U10">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V10">
         <v>0.25</v>
       </c>
       <c r="W10">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>27.45722354361434</v>
+        <v>28.14076596210179</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2150,13 +2150,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.07951608589096908</v>
+        <v>0.07940573202041912</v>
       </c>
       <c r="C11">
-        <v>1482.009579051868</v>
+        <v>1486.427226810286</v>
       </c>
       <c r="D11">
-        <v>1523.528579051868</v>
+        <v>1527.946226810286</v>
       </c>
       <c r="E11">
         <v>-650.1809999999999</v>
@@ -2183,37 +2183,37 @@
         <v>188.525</v>
       </c>
       <c r="M11">
-        <v>7.724401728496156</v>
+        <v>7.536775128496156</v>
       </c>
       <c r="N11">
-        <v>180.8005982715038</v>
+        <v>180.9882248715038</v>
       </c>
       <c r="O11">
-        <v>45.20014956787595</v>
+        <v>45.24705621787596</v>
       </c>
       <c r="P11">
-        <v>135.6004487036279</v>
+        <v>135.7411686536279</v>
       </c>
       <c r="Q11">
-        <v>178.7004487036279</v>
+        <v>178.8411686536279</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.08310507062225059</v>
+        <v>0.08308764878648139</v>
       </c>
       <c r="T11">
         <v>0.7268056783127117</v>
       </c>
       <c r="U11">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V11">
         <v>0.25</v>
       </c>
       <c r="W11">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>24.40642092765719</v>
+        <v>25.01401418853493</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2232,13 +2232,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.07940353797305766</v>
+        <v>0.07928272464949121</v>
       </c>
       <c r="C12">
-        <v>1472.221314650373</v>
+        <v>1477.149528901041</v>
       </c>
       <c r="D12">
-        <v>1528.631314650373</v>
+        <v>1533.559528901041</v>
       </c>
       <c r="E12">
         <v>-635.29</v>
@@ -2265,37 +2265,37 @@
         <v>188.525</v>
       </c>
       <c r="M12">
-        <v>8.582668587217952</v>
+        <v>8.374194587217954</v>
       </c>
       <c r="N12">
-        <v>179.942331412782</v>
+        <v>180.150805412782</v>
       </c>
       <c r="O12">
-        <v>44.98558285319551</v>
+        <v>45.03770135319551</v>
       </c>
       <c r="P12">
-        <v>134.9567485595865</v>
+        <v>135.1131040595865</v>
       </c>
       <c r="Q12">
-        <v>178.0567485595865</v>
+        <v>178.2131040595866</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.08342310191485289</v>
+        <v>0.08340553155533462</v>
       </c>
       <c r="T12">
         <v>0.7330018051525472</v>
       </c>
       <c r="U12">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>21.96577883489147</v>
+        <v>22.51261276968143</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2314,13 +2314,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.07929099005514625</v>
+        <v>0.07915971727856329</v>
       </c>
       <c r="C13">
-        <v>1462.467346175413</v>
+        <v>1467.913226878137</v>
       </c>
       <c r="D13">
-        <v>1533.768346175412</v>
+        <v>1539.214226878137</v>
       </c>
       <c r="E13">
         <v>-620.3989999999999</v>
@@ -2347,37 +2347,37 @@
         <v>188.525</v>
       </c>
       <c r="M13">
-        <v>9.440935445939747</v>
+        <v>9.211614045939747</v>
       </c>
       <c r="N13">
-        <v>179.0840645540602</v>
+        <v>179.3133859540602</v>
       </c>
       <c r="O13">
-        <v>44.77101613851506</v>
+        <v>44.82834648851506</v>
       </c>
       <c r="P13">
-        <v>134.3130484155452</v>
+        <v>134.4850394655452</v>
       </c>
       <c r="Q13">
-        <v>177.4130484155452</v>
+        <v>177.5850394655452</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.08374827997807549</v>
+        <v>0.08373055775719576</v>
       </c>
       <c r="T13">
         <v>0.7393371707977725</v>
       </c>
       <c r="U13">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V13">
         <v>0.25</v>
       </c>
       <c r="W13">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>19.96888984990134</v>
+        <v>20.4660116088013</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2396,13 +2396,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.07917844213723482</v>
+        <v>0.07903670990763538</v>
       </c>
       <c r="C14">
-        <v>1452.748020551669</v>
+        <v>1458.718780353775</v>
       </c>
       <c r="D14">
-        <v>1538.940020551669</v>
+        <v>1544.910780353775</v>
       </c>
       <c r="E14">
         <v>-605.5079999999999</v>
@@ -2429,37 +2429,37 @@
         <v>188.525</v>
       </c>
       <c r="M14">
-        <v>10.29920230466154</v>
+        <v>10.04903350466154</v>
       </c>
       <c r="N14">
-        <v>178.2257976953384</v>
+        <v>178.4759664953384</v>
       </c>
       <c r="O14">
-        <v>44.55644942383461</v>
+        <v>44.61899162383461</v>
       </c>
       <c r="P14">
-        <v>133.6693482715038</v>
+        <v>133.8569748715038</v>
       </c>
       <c r="Q14">
-        <v>176.7693482715038</v>
+        <v>176.9569748715039</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.08408084845182585</v>
+        <v>0.08406297091819012</v>
       </c>
       <c r="T14">
         <v>0.7458165220258436</v>
       </c>
       <c r="U14">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V14">
         <v>0.25</v>
       </c>
       <c r="W14">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.30481569574289</v>
+        <v>18.76051064140119</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2478,13 +2478,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.07906589421932339</v>
+        <v>0.07891370253670746</v>
       </c>
       <c r="C15">
-        <v>1443.063689398799</v>
+        <v>1449.566655769439</v>
       </c>
       <c r="D15">
-        <v>1544.146689398799</v>
+        <v>1550.649655769439</v>
       </c>
       <c r="E15">
         <v>-590.617</v>
@@ -2511,37 +2511,37 @@
         <v>188.525</v>
       </c>
       <c r="M15">
-        <v>11.15746916338334</v>
+        <v>10.88645296338334</v>
       </c>
       <c r="N15">
-        <v>177.3675308366167</v>
+        <v>177.6385470366166</v>
       </c>
       <c r="O15">
-        <v>44.34188270915416</v>
+        <v>44.40963675915416</v>
       </c>
       <c r="P15">
-        <v>133.0256481274625</v>
+        <v>133.2289102774625</v>
       </c>
       <c r="Q15">
-        <v>176.1256481274625</v>
+        <v>176.3289102774625</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.08442106217784634</v>
+        <v>0.08440302576104641</v>
       </c>
       <c r="T15">
         <v>0.7524448238568588</v>
       </c>
       <c r="U15">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>16.89675294991652</v>
+        <v>17.31739443821649</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.07895334630141196</v>
+        <v>0.07879069516577954</v>
       </c>
       <c r="C16">
-        <v>1433.414709111128</v>
+        <v>1440.457326523207</v>
       </c>
       <c r="D16">
-        <v>1549.388709111128</v>
+        <v>1556.431326523207</v>
       </c>
       <c r="E16">
         <v>-575.7259999999999</v>
@@ -2593,37 +2593,37 @@
         <v>188.525</v>
       </c>
       <c r="M16">
-        <v>12.01573602210513</v>
+        <v>11.72387242210513</v>
       </c>
       <c r="N16">
-        <v>176.5092639778948</v>
+        <v>176.8011275778948</v>
       </c>
       <c r="O16">
-        <v>44.12731599447371</v>
+        <v>44.20028189447371</v>
       </c>
       <c r="P16">
-        <v>132.3819479834211</v>
+        <v>132.6008456834211</v>
       </c>
       <c r="Q16">
-        <v>175.4819479834212</v>
+        <v>175.7008456834212</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.08476918785098358</v>
+        <v>0.08475098885606215</v>
       </c>
       <c r="T16">
         <v>0.7592272722420839</v>
       </c>
       <c r="U16">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>15.68984202492248</v>
+        <v>16.08043769262959</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2642,13 +2642,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.07884079838350054</v>
+        <v>0.07866768779485162</v>
       </c>
       <c r="C17">
-        <v>1423.80144093897</v>
+        <v>1431.391273099932</v>
       </c>
       <c r="D17">
-        <v>1554.66644093897</v>
+        <v>1562.256273099932</v>
       </c>
       <c r="E17">
         <v>-560.8349999999999</v>
@@ -2675,37 +2675,37 @@
         <v>188.525</v>
       </c>
       <c r="M17">
-        <v>12.87400288082693</v>
+        <v>12.56129188082693</v>
       </c>
       <c r="N17">
-        <v>175.650997119173</v>
+        <v>175.963708119173</v>
       </c>
       <c r="O17">
-        <v>43.91274927979326</v>
+        <v>43.99092702979326</v>
       </c>
       <c r="P17">
-        <v>131.7382478393798</v>
+        <v>131.9727810893798</v>
       </c>
       <c r="Q17">
-        <v>174.8382478393798</v>
+        <v>175.0727810893798</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.08512550471642996</v>
+        <v>0.08510713931801944</v>
       </c>
       <c r="T17">
         <v>0.7661693076481376</v>
       </c>
       <c r="U17">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V17">
         <v>0.25</v>
       </c>
       <c r="W17">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.64385255659431</v>
+        <v>15.00840851312095</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2724,13 +2724,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.07872825046558912</v>
+        <v>0.07854468042392368</v>
       </c>
       <c r="C18">
-        <v>1414.224251071618</v>
+        <v>1422.368983204346</v>
       </c>
       <c r="D18">
-        <v>1559.980251071618</v>
+        <v>1568.124983204346</v>
       </c>
       <c r="E18">
         <v>-545.944</v>
@@ -2757,37 +2757,37 @@
         <v>188.525</v>
       </c>
       <c r="M18">
-        <v>13.73226973954872</v>
+        <v>13.39871133954872</v>
       </c>
       <c r="N18">
-        <v>174.7927302604513</v>
+        <v>175.1262886604513</v>
       </c>
       <c r="O18">
-        <v>43.69818256511282</v>
+        <v>43.78157216511281</v>
       </c>
       <c r="P18">
-        <v>131.0945476953385</v>
+        <v>131.3447164953384</v>
       </c>
       <c r="Q18">
-        <v>174.1945476953385</v>
+        <v>174.4447164953385</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.08549030531676789</v>
+        <v>0.08547176955288047</v>
       </c>
       <c r="T18">
         <v>0.7732766296114784</v>
       </c>
       <c r="U18">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>13.72861177180717</v>
+        <v>14.07038298105089</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2806,13 +2806,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.0786157025476777</v>
+        <v>0.07842167305299577</v>
       </c>
       <c r="C19">
-        <v>1404.683510722039</v>
+        <v>1413.390951897184</v>
       </c>
       <c r="D19">
-        <v>1565.330510722039</v>
+        <v>1574.037951897184</v>
       </c>
       <c r="E19">
         <v>-531.0529999999999</v>
@@ -2839,37 +2839,37 @@
         <v>188.525</v>
       </c>
       <c r="M19">
-        <v>14.59053659827052</v>
+        <v>14.23613079827052</v>
       </c>
       <c r="N19">
-        <v>173.9344634017295</v>
+        <v>174.2888692017295</v>
       </c>
       <c r="O19">
-        <v>43.48361585043236</v>
+        <v>43.57221730043236</v>
       </c>
       <c r="P19">
-        <v>130.4508475512971</v>
+        <v>130.7166519012971</v>
       </c>
       <c r="Q19">
-        <v>173.5508475512971</v>
+        <v>173.8166519012971</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.08586389629301761</v>
+        <v>0.08584518605846106</v>
       </c>
       <c r="T19">
         <v>0.7805552123450203</v>
       </c>
       <c r="U19">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>12.92104637346557</v>
+        <v>13.24271339393025</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2888,13 +2888,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.07865165462976628</v>
+        <v>0.07850116568206786</v>
       </c>
       <c r="C20">
-        <v>1388.079449640292</v>
+        <v>1394.673653585006</v>
       </c>
       <c r="D20">
-        <v>1563.617449640292</v>
+        <v>1570.211653585006</v>
       </c>
       <c r="E20">
         <v>-516.162</v>
@@ -2921,37 +2921,37 @@
         <v>188.525</v>
       </c>
       <c r="M20">
-        <v>15.74364525699231</v>
+        <v>15.47560725699231</v>
       </c>
       <c r="N20">
-        <v>172.7813547430077</v>
+        <v>173.0493927430077</v>
       </c>
       <c r="O20">
-        <v>43.19533868575191</v>
+        <v>43.26234818575192</v>
       </c>
       <c r="P20">
-        <v>129.5860160572557</v>
+        <v>129.7870445572557</v>
       </c>
       <c r="Q20">
-        <v>172.6860160572558</v>
+        <v>172.8870445572558</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.08624659924429777</v>
+        <v>0.08622771028368993</v>
       </c>
       <c r="T20">
         <v>0.7880113214866972</v>
       </c>
       <c r="U20">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.04405246249690057</v>
+        <v>0.04330246249690057</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.97467275987239</v>
+        <v>12.18207446527303</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2970,13 +2970,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.07854735671185485</v>
+        <v>0.07838940831113994</v>
       </c>
       <c r="C21">
-        <v>1378.168455991413</v>
+        <v>1385.167308762837</v>
       </c>
       <c r="D21">
-        <v>1568.597455991413</v>
+        <v>1575.596308762837</v>
       </c>
       <c r="E21">
         <v>-501.271</v>
@@ -3003,37 +3003,37 @@
         <v>188.525</v>
       </c>
       <c r="M21">
-        <v>16.61829221571411</v>
+        <v>16.33536321571411</v>
       </c>
       <c r="N21">
-        <v>171.9067077842859</v>
+        <v>172.1896367842859</v>
       </c>
       <c r="O21">
-        <v>42.97667694607146</v>
+        <v>43.04740919607147</v>
       </c>
       <c r="P21">
-        <v>128.9300308382144</v>
+        <v>129.1422275882144</v>
       </c>
       <c r="Q21">
-        <v>172.0300308382144</v>
+        <v>172.2422275882144</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.08663875165116512</v>
+        <v>0.08661967955151706</v>
       </c>
       <c r="T21">
         <v>0.7956515320886626</v>
       </c>
       <c r="U21">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V21">
         <v>0.25</v>
       </c>
       <c r="W21">
-        <v>0.04405246249690057</v>
+        <v>0.04330246249690057</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.34442682514226</v>
+        <v>11.54091265131129</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3052,13 +3052,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.07844305879394342</v>
+        <v>0.07827765094021201</v>
       </c>
       <c r="C22">
-        <v>1368.28928560376</v>
+        <v>1375.69802172586</v>
       </c>
       <c r="D22">
-        <v>1573.60928560376</v>
+        <v>1581.01802172586</v>
       </c>
       <c r="E22">
         <v>-486.3799999999999</v>
@@ -3085,37 +3085,37 @@
         <v>188.525</v>
       </c>
       <c r="M22">
-        <v>17.4929391744359</v>
+        <v>17.1951191744359</v>
       </c>
       <c r="N22">
-        <v>171.0320608255641</v>
+        <v>171.3298808255641</v>
       </c>
       <c r="O22">
-        <v>42.75801520639102</v>
+        <v>42.83247020639102</v>
       </c>
       <c r="P22">
-        <v>128.2740456191731</v>
+        <v>128.4974106191731</v>
       </c>
       <c r="Q22">
-        <v>171.3740456191731</v>
+        <v>171.5974106191731</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.08704070786820414</v>
+        <v>0.08702144805103987</v>
       </c>
       <c r="T22">
         <v>0.8034827479556769</v>
       </c>
       <c r="U22">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V22">
         <v>0.25</v>
       </c>
       <c r="W22">
-        <v>0.04405246249690057</v>
+        <v>0.04330246249690057</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.77720548388515</v>
+        <v>10.96386701874572</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3134,13 +3134,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.07833876087603199</v>
+        <v>0.07816589356928409</v>
       </c>
       <c r="C23">
-        <v>1358.44224449082</v>
+        <v>1366.266176348596</v>
       </c>
       <c r="D23">
-        <v>1578.65324449082</v>
+        <v>1586.477176348596</v>
       </c>
       <c r="E23">
         <v>-471.489</v>
@@ -3167,37 +3167,37 @@
         <v>188.525</v>
       </c>
       <c r="M23">
-        <v>18.3675861331577</v>
+        <v>18.0548751331577</v>
       </c>
       <c r="N23">
-        <v>170.1574138668423</v>
+        <v>170.4701248668423</v>
       </c>
       <c r="O23">
-        <v>42.53935346671057</v>
+        <v>42.61753121671057</v>
       </c>
       <c r="P23">
-        <v>127.6180604001317</v>
+        <v>127.8525936501317</v>
       </c>
       <c r="Q23">
-        <v>170.7180604001317</v>
+        <v>170.9525936501317</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.08745284019200364</v>
+        <v>0.08743338790498097</v>
       </c>
       <c r="T23">
         <v>0.8115122224522359</v>
       </c>
       <c r="U23">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.04405246249690057</v>
+        <v>0.04330246249690057</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.26400522274776</v>
+        <v>10.44177811309116</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3216,13 +3216,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.07859746295812058</v>
+        <v>0.07805413619835616</v>
       </c>
       <c r="C24">
-        <v>1331.099034947442</v>
+        <v>1356.872161825917</v>
       </c>
       <c r="D24">
-        <v>1566.201034947442</v>
+        <v>1591.974161825917</v>
       </c>
       <c r="E24">
         <v>-456.598</v>
@@ -3249,45 +3249,45 @@
         <v>188.525</v>
       </c>
       <c r="M24">
-        <v>19.96295749187949</v>
+        <v>18.91463109187949</v>
       </c>
       <c r="N24">
-        <v>168.5620425081205</v>
+        <v>169.6103689081205</v>
       </c>
       <c r="O24">
-        <v>42.14051062703012</v>
+        <v>42.40259222703012</v>
       </c>
       <c r="P24">
-        <v>126.4215318810904</v>
+        <v>127.2077766810904</v>
       </c>
       <c r="Q24">
-        <v>169.5215318810904</v>
+        <v>170.3077766810904</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.0878755400112852</v>
+        <v>0.08785589031927954</v>
       </c>
       <c r="T24">
         <v>0.8197475809102451</v>
       </c>
       <c r="U24">
-        <v>0.0609366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V24">
         <v>0.25</v>
       </c>
       <c r="W24">
-        <v>0.04570246249690058</v>
+        <v>0.04330246249690057</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y24">
-        <v>9.443740992620354</v>
+        <v>9.967151835223385</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3298,13 +3298,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.07850966504020916</v>
+        <v>0.07823562882742824</v>
       </c>
       <c r="C25">
-        <v>1320.411966407152</v>
+        <v>1333.073316148503</v>
       </c>
       <c r="D25">
-        <v>1570.404966407152</v>
+        <v>1583.066316148503</v>
       </c>
       <c r="E25">
         <v>-441.7069999999999</v>
@@ -3331,37 +3331,37 @@
         <v>188.525</v>
       </c>
       <c r="M25">
-        <v>20.87036465060129</v>
+        <v>20.35662515060129</v>
       </c>
       <c r="N25">
-        <v>167.6546353493987</v>
+        <v>168.1683748493987</v>
       </c>
       <c r="O25">
-        <v>41.91365883734967</v>
+        <v>42.04209371234967</v>
       </c>
       <c r="P25">
-        <v>125.740976512049</v>
+        <v>126.126281137049</v>
       </c>
       <c r="Q25">
-        <v>168.8409765120491</v>
+        <v>169.226281137049</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.08830921904665198</v>
+        <v>0.08828936682226118</v>
       </c>
       <c r="T25">
         <v>0.8281968447827482</v>
       </c>
       <c r="U25">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V25">
         <v>0.25</v>
       </c>
       <c r="W25">
-        <v>0.04570246249690058</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.033143558158599</v>
+        <v>9.261112714178527</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3380,13 +3380,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.07842186712229773</v>
+        <v>0.07813662145650033</v>
       </c>
       <c r="C26">
-        <v>1309.747526640857</v>
+        <v>1323.029304699154</v>
       </c>
       <c r="D26">
-        <v>1574.631526640857</v>
+        <v>1587.913304699154</v>
       </c>
       <c r="E26">
         <v>-426.816</v>
@@ -3413,37 +3413,37 @@
         <v>188.525</v>
       </c>
       <c r="M26">
-        <v>21.77777180932308</v>
+        <v>21.24169580932308</v>
       </c>
       <c r="N26">
-        <v>166.7472281906769</v>
+        <v>167.2833041906769</v>
       </c>
       <c r="O26">
-        <v>41.68680704766922</v>
+        <v>41.82082604766922</v>
       </c>
       <c r="P26">
-        <v>125.0604211430077</v>
+        <v>125.4624781430077</v>
       </c>
       <c r="Q26">
-        <v>168.1604211430077</v>
+        <v>168.5624781430077</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.08875431068821263</v>
+        <v>0.08873425060163709</v>
       </c>
       <c r="T26">
         <v>0.8368684577045277</v>
       </c>
       <c r="U26">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V26">
         <v>0.25</v>
       </c>
       <c r="W26">
-        <v>0.04570246249690058</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.656762576568656</v>
+        <v>8.875233017754422</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3462,13 +3462,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.07833406920438631</v>
+        <v>0.0780376140855724</v>
       </c>
       <c r="C27">
-        <v>1299.105898849671</v>
+        <v>1313.015065154888</v>
       </c>
       <c r="D27">
-        <v>1578.880898849671</v>
+        <v>1592.790065154888</v>
       </c>
       <c r="E27">
         <v>-411.925</v>
@@ -3495,37 +3495,37 @@
         <v>188.525</v>
       </c>
       <c r="M27">
-        <v>22.68517896804488</v>
+        <v>22.12676646804488</v>
       </c>
       <c r="N27">
-        <v>165.8398210319551</v>
+        <v>166.3982335319551</v>
       </c>
       <c r="O27">
-        <v>41.45995525798877</v>
+        <v>41.59955838298877</v>
       </c>
       <c r="P27">
-        <v>124.3798657739663</v>
+        <v>124.7986751489663</v>
       </c>
       <c r="Q27">
-        <v>167.4798657739663</v>
+        <v>167.8986751489663</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.08921127144021489</v>
+        <v>0.08919099794846301</v>
       </c>
       <c r="T27">
         <v>0.8457713136375545</v>
       </c>
       <c r="U27">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.04570246249690058</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.310492073505911</v>
+        <v>8.520223697044246</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3544,13 +3544,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.07824627128647488</v>
+        <v>0.07793860671464449</v>
       </c>
       <c r="C28">
-        <v>1288.487268217639</v>
+        <v>1303.030872664973</v>
       </c>
       <c r="D28">
-        <v>1583.153268217639</v>
+        <v>1597.696872664973</v>
       </c>
       <c r="E28">
         <v>-397.0339999999999</v>
@@ -3577,37 +3577,37 @@
         <v>188.525</v>
       </c>
       <c r="M28">
-        <v>23.59258612676668</v>
+        <v>23.01183712676668</v>
       </c>
       <c r="N28">
-        <v>164.9324138732333</v>
+        <v>165.5131628732333</v>
       </c>
       <c r="O28">
-        <v>41.23310346830833</v>
+        <v>41.37829071830833</v>
       </c>
       <c r="P28">
-        <v>123.699310404925</v>
+        <v>124.134872154925</v>
       </c>
       <c r="Q28">
-        <v>166.799310404925</v>
+        <v>167.234872154925</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.0896805824828118</v>
+        <v>0.08966008981817614</v>
       </c>
       <c r="T28">
         <v>0.8549147872985011</v>
       </c>
       <c r="U28">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.04570246249690058</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.990857762986453</v>
+        <v>8.192522785619467</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3626,13 +3626,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.07815847336856346</v>
+        <v>0.07783959934371656</v>
       </c>
       <c r="C29">
-        <v>1277.891821938638</v>
+        <v>1293.077005779696</v>
       </c>
       <c r="D29">
-        <v>1587.448821938638</v>
+        <v>1602.634005779697</v>
       </c>
       <c r="E29">
         <v>-382.1429999999999</v>
@@ -3659,37 +3659,37 @@
         <v>188.525</v>
       </c>
       <c r="M29">
-        <v>24.49999328548847</v>
+        <v>23.89690778548847</v>
       </c>
       <c r="N29">
-        <v>164.0250067145115</v>
+        <v>164.6280922145115</v>
       </c>
       <c r="O29">
-        <v>41.00625167862788</v>
+        <v>41.15702305362787</v>
       </c>
       <c r="P29">
-        <v>123.0187550358836</v>
+        <v>123.4710691608836</v>
       </c>
       <c r="Q29">
-        <v>166.1187550358837</v>
+        <v>166.5710691608836</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.09016275136219221</v>
+        <v>0.09014203351993619</v>
       </c>
       <c r="T29">
         <v>0.8643087670871449</v>
       </c>
       <c r="U29">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.04570246249690058</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.694900068061028</v>
+        <v>7.889096015781707</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3708,13 +3708,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.07838567545065203</v>
+        <v>0.07774059197278864</v>
       </c>
       <c r="C30">
-        <v>1251.932410050116</v>
+        <v>1283.153746503072</v>
       </c>
       <c r="D30">
-        <v>1576.380410050116</v>
+        <v>1607.601746503072</v>
       </c>
       <c r="E30">
         <v>-367.2519999999999</v>
@@ -3741,45 +3741,45 @@
         <v>188.525</v>
       </c>
       <c r="M30">
-        <v>26.03282244421027</v>
+        <v>24.78197844421027</v>
       </c>
       <c r="N30">
-        <v>162.4921775557897</v>
+        <v>163.7430215557897</v>
       </c>
       <c r="O30">
-        <v>40.62304438894743</v>
+        <v>40.93575538894743</v>
       </c>
       <c r="P30">
-        <v>121.8691331668423</v>
+        <v>122.8072661668423</v>
       </c>
       <c r="Q30">
-        <v>164.9691331668423</v>
+        <v>165.9072661668423</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.09065831382155538</v>
+        <v>0.09063736454674512</v>
       </c>
       <c r="T30">
         <v>0.8739636907588064</v>
       </c>
       <c r="U30">
-        <v>0.0624366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.04682746249690058</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>7.241819453269777</v>
+        <v>7.607342586646647</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3790,13 +3790,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.07830912753274061</v>
+        <v>0.07781558460186072</v>
       </c>
       <c r="C31">
-        <v>1240.753248766925</v>
+        <v>1264.497134131148</v>
       </c>
       <c r="D31">
-        <v>1580.092248766925</v>
+        <v>1603.836134131148</v>
       </c>
       <c r="E31">
         <v>-352.361</v>
@@ -3823,37 +3823,37 @@
         <v>188.525</v>
       </c>
       <c r="M31">
-        <v>26.96256610293206</v>
+        <v>26.01252030293206</v>
       </c>
       <c r="N31">
-        <v>161.5624338970679</v>
+        <v>162.5124796970679</v>
       </c>
       <c r="O31">
-        <v>40.39060847426698</v>
+        <v>40.62811992426698</v>
       </c>
       <c r="P31">
-        <v>121.1718254228009</v>
+        <v>121.8843597728009</v>
       </c>
       <c r="Q31">
-        <v>164.271825422801</v>
+        <v>164.984359772801</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.09116783578681611</v>
+        <v>0.09114664856022472</v>
       </c>
       <c r="T31">
         <v>0.8838905841113598</v>
       </c>
       <c r="U31">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V31">
         <v>0.25</v>
       </c>
       <c r="W31">
-        <v>0.04682746249690058</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.992101541088062</v>
+        <v>7.247471517734865</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3872,13 +3872,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.07823257961482918</v>
+        <v>0.0777225772309328</v>
       </c>
       <c r="C32">
-        <v>1229.591608971618</v>
+        <v>1254.278958043692</v>
       </c>
       <c r="D32">
-        <v>1583.821608971618</v>
+        <v>1608.508958043692</v>
       </c>
       <c r="E32">
         <v>-337.47</v>
@@ -3905,37 +3905,37 @@
         <v>188.525</v>
       </c>
       <c r="M32">
-        <v>27.89230976165386</v>
+        <v>26.90950376165386</v>
       </c>
       <c r="N32">
-        <v>160.6326902383461</v>
+        <v>161.6154962383461</v>
       </c>
       <c r="O32">
-        <v>40.15817255958653</v>
+        <v>40.40387405958653</v>
       </c>
       <c r="P32">
-        <v>120.4745176787596</v>
+        <v>121.2116221787596</v>
       </c>
       <c r="Q32">
-        <v>163.5745176787596</v>
+        <v>164.3116221787596</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.09169191552251288</v>
+        <v>0.09167048354551804</v>
       </c>
       <c r="T32">
         <v>0.8941011029882719</v>
       </c>
       <c r="U32">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V32">
         <v>0.25</v>
       </c>
       <c r="W32">
-        <v>0.04682746249690058</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.759031489718459</v>
+        <v>7.005889133810368</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3954,13 +3954,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.07815603169691776</v>
+        <v>0.07762956986000487</v>
       </c>
       <c r="C33">
-        <v>1218.447615021233</v>
+        <v>1244.088090340788</v>
       </c>
       <c r="D33">
-        <v>1587.568615021233</v>
+        <v>1613.209090340788</v>
       </c>
       <c r="E33">
         <v>-322.579</v>
@@ -3987,37 +3987,37 @@
         <v>188.525</v>
       </c>
       <c r="M33">
-        <v>28.82205342037565</v>
+        <v>27.80648722037565</v>
       </c>
       <c r="N33">
-        <v>159.7029465796243</v>
+        <v>160.7185127796243</v>
       </c>
       <c r="O33">
-        <v>39.92573664490608</v>
+        <v>40.17962819490608</v>
       </c>
       <c r="P33">
-        <v>119.7772099347182</v>
+        <v>120.5388845847182</v>
       </c>
       <c r="Q33">
-        <v>162.8772099347183</v>
+        <v>163.6388845847183</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.09223118597518636</v>
+        <v>0.09220950215357349</v>
       </c>
       <c r="T33">
         <v>0.9046075789340801</v>
       </c>
       <c r="U33">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V33">
         <v>0.25</v>
       </c>
       <c r="W33">
-        <v>0.04682746249690058</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.540998215856573</v>
+        <v>6.779892710139066</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4036,13 +4036,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.07807948377900634</v>
+        <v>0.07753656248907695</v>
       </c>
       <c r="C34">
-        <v>1207.321392452415</v>
+        <v>1233.924771112808</v>
       </c>
       <c r="D34">
-        <v>1591.333392452415</v>
+        <v>1617.936771112808</v>
       </c>
       <c r="E34">
         <v>-307.6879999999999</v>
@@ -4069,37 +4069,37 @@
         <v>188.525</v>
       </c>
       <c r="M34">
-        <v>29.75179707909745</v>
+        <v>28.70347067909745</v>
       </c>
       <c r="N34">
-        <v>158.7732029209025</v>
+        <v>159.8215293209025</v>
       </c>
       <c r="O34">
-        <v>39.69330073022563</v>
+        <v>39.95538233022563</v>
       </c>
       <c r="P34">
-        <v>119.0799021906769</v>
+        <v>119.8661469906769</v>
       </c>
       <c r="Q34">
-        <v>162.1799021906769</v>
+        <v>162.9661469906769</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.0927863173235267</v>
+        <v>0.09276437425010114</v>
       </c>
       <c r="T34">
         <v>0.9154230688782944</v>
       </c>
       <c r="U34">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V34">
         <v>0.25</v>
       </c>
       <c r="W34">
-        <v>0.04682746249690058</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.336592021611055</v>
+        <v>6.56802106294722</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4118,13 +4118,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.07800293586109491</v>
+        <v>0.07744355511814904</v>
       </c>
       <c r="C35">
-        <v>1196.213067995433</v>
+        <v>1223.789243272839</v>
       </c>
       <c r="D35">
-        <v>1595.116067995433</v>
+        <v>1622.69224327284</v>
       </c>
       <c r="E35">
         <v>-292.7969999999999</v>
@@ -4151,37 +4151,37 @@
         <v>188.525</v>
       </c>
       <c r="M35">
-        <v>30.68154073781924</v>
+        <v>29.60045413781924</v>
       </c>
       <c r="N35">
-        <v>157.8434592621807</v>
+        <v>158.9245458621807</v>
       </c>
       <c r="O35">
-        <v>39.46086481554519</v>
+        <v>39.73113646554518</v>
       </c>
       <c r="P35">
-        <v>118.3825944466356</v>
+        <v>119.1934093966356</v>
       </c>
       <c r="Q35">
-        <v>161.4825944466356</v>
+        <v>162.2934093966356</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.09335801975689213</v>
+        <v>0.09333580969279381</v>
       </c>
       <c r="T35">
         <v>0.9265614092686046</v>
       </c>
       <c r="U35">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V35">
         <v>0.25</v>
       </c>
       <c r="W35">
-        <v>0.04682746249690058</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.144574081562236</v>
+        <v>6.368990121645789</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4200,13 +4200,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.07828338794318349</v>
+        <v>0.07735054774722111</v>
       </c>
       <c r="C36">
-        <v>1167.550301847619</v>
+        <v>1213.681752598291</v>
       </c>
       <c r="D36">
-        <v>1581.344301847619</v>
+        <v>1627.475752598292</v>
       </c>
       <c r="E36">
         <v>-277.9059999999999</v>
@@ -4233,45 +4233,45 @@
         <v>188.525</v>
       </c>
       <c r="M36">
-        <v>32.32009599654103</v>
+        <v>30.49743759654104</v>
       </c>
       <c r="N36">
-        <v>156.2049040034589</v>
+        <v>158.0275624034589</v>
       </c>
       <c r="O36">
-        <v>39.05122600086474</v>
+        <v>39.50689060086474</v>
       </c>
       <c r="P36">
-        <v>117.1536780025942</v>
+        <v>118.5206718025942</v>
       </c>
       <c r="Q36">
-        <v>160.2536780025942</v>
+        <v>161.6206718025942</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.09394704650642015</v>
+        <v>0.09392456136102262</v>
       </c>
       <c r="T36">
         <v>0.9380372751252879</v>
       </c>
       <c r="U36">
-        <v>0.0638366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V36">
         <v>0.25</v>
       </c>
       <c r="W36">
-        <v>0.04787746249690057</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y36">
-        <v>5.833058169758417</v>
+        <v>6.181666882773855</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4282,13 +4282,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.07821734002527206</v>
+        <v>0.0775200403762932</v>
       </c>
       <c r="C37">
-        <v>1155.881173184277</v>
+        <v>1190.094510702423</v>
       </c>
       <c r="D37">
-        <v>1584.566173184277</v>
+        <v>1618.779510702423</v>
       </c>
       <c r="E37">
         <v>-263.0149999999999</v>
@@ -4315,37 +4315,37 @@
         <v>188.525</v>
       </c>
       <c r="M37">
-        <v>33.27068705526283</v>
+        <v>31.91560605526284</v>
       </c>
       <c r="N37">
-        <v>155.2543129447371</v>
+        <v>156.6093939447371</v>
       </c>
       <c r="O37">
-        <v>38.81357823618428</v>
+        <v>39.15234848618429</v>
       </c>
       <c r="P37">
-        <v>116.4407347085529</v>
+        <v>117.4570454585529</v>
       </c>
       <c r="Q37">
-        <v>159.5407347085529</v>
+        <v>160.5570454585529</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.09455419715593365</v>
+        <v>0.09453142846519694</v>
       </c>
       <c r="T37">
         <v>0.9498662445467921</v>
       </c>
       <c r="U37">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V37">
         <v>0.25</v>
       </c>
       <c r="W37">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.666399364908175</v>
+        <v>5.906984804661495</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4364,13 +4364,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.07815129210736065</v>
+        <v>0.07743453300536529</v>
       </c>
       <c r="C38">
-        <v>1144.225199970359</v>
+        <v>1179.579032226596</v>
       </c>
       <c r="D38">
-        <v>1587.801199970359</v>
+        <v>1623.155032226596</v>
       </c>
       <c r="E38">
         <v>-248.124</v>
@@ -4397,37 +4397,37 @@
         <v>188.525</v>
       </c>
       <c r="M38">
-        <v>34.22127811398462</v>
+        <v>32.82748051398463</v>
       </c>
       <c r="N38">
-        <v>154.3037218860154</v>
+        <v>155.6975194860154</v>
       </c>
       <c r="O38">
-        <v>38.57593047150384</v>
+        <v>38.92437987150384</v>
       </c>
       <c r="P38">
-        <v>115.7277914145115</v>
+        <v>116.7731396145115</v>
       </c>
       <c r="Q38">
-        <v>158.8277914145115</v>
+        <v>159.8731396145115</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.09518032126324444</v>
+        <v>0.09515726016637668</v>
       </c>
       <c r="T38">
         <v>0.9620648692627183</v>
       </c>
       <c r="U38">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V38">
         <v>0.25</v>
       </c>
       <c r="W38">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.508999382549616</v>
+        <v>5.742901893420899</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4446,13 +4446,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.07808524418944922</v>
+        <v>0.07734902563443735</v>
       </c>
       <c r="C39">
-        <v>1132.582462944612</v>
+        <v>1169.087271715712</v>
       </c>
       <c r="D39">
-        <v>1591.049462944613</v>
+        <v>1627.554271715712</v>
       </c>
       <c r="E39">
         <v>-233.2329999999999</v>
@@ -4479,37 +4479,37 @@
         <v>188.525</v>
       </c>
       <c r="M39">
-        <v>35.17186917270642</v>
+        <v>33.73935497270642</v>
       </c>
       <c r="N39">
-        <v>153.3531308272936</v>
+        <v>154.7856450272936</v>
       </c>
       <c r="O39">
-        <v>38.33828270682339</v>
+        <v>38.69641125682339</v>
       </c>
       <c r="P39">
-        <v>115.0148481204702</v>
+        <v>116.0892337704702</v>
       </c>
       <c r="Q39">
-        <v>158.1148481204702</v>
+        <v>159.1892337704702</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.09582632232634286</v>
+        <v>0.09580295954060976</v>
       </c>
       <c r="T39">
         <v>0.9746507519061343</v>
       </c>
       <c r="U39">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V39">
         <v>0.25</v>
       </c>
       <c r="W39">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.360107507345572</v>
+        <v>5.587688328733847</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4528,13 +4528,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.07801919627153779</v>
+        <v>0.07726351826350944</v>
       </c>
       <c r="C40">
-        <v>1120.953043507825</v>
+        <v>1158.619422542373</v>
       </c>
       <c r="D40">
-        <v>1594.311043507825</v>
+        <v>1631.977422542373</v>
       </c>
       <c r="E40">
         <v>-218.342</v>
@@ -4561,37 +4561,37 @@
         <v>188.525</v>
       </c>
       <c r="M40">
-        <v>36.12246023142821</v>
+        <v>34.65122943142821</v>
       </c>
       <c r="N40">
-        <v>152.4025397685718</v>
+        <v>153.8737705685718</v>
       </c>
       <c r="O40">
-        <v>38.10063494214294</v>
+        <v>38.46844264214294</v>
       </c>
       <c r="P40">
-        <v>114.3019048264288</v>
+        <v>115.4053279264288</v>
       </c>
       <c r="Q40">
-        <v>157.4019048264288</v>
+        <v>158.5053279264288</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.09649316213341222</v>
+        <v>0.09646948792691487</v>
       </c>
       <c r="T40">
         <v>0.9876426307638541</v>
       </c>
       <c r="U40">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V40">
         <v>0.25</v>
       </c>
       <c r="W40">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.219052046625952</v>
+        <v>5.440643899030325</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4610,13 +4610,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.07795314835362636</v>
+        <v>0.07717801089258153</v>
       </c>
       <c r="C41">
-        <v>1109.33702372963</v>
+        <v>1148.175680187003</v>
       </c>
       <c r="D41">
-        <v>1597.58602372963</v>
+        <v>1636.424680187003</v>
       </c>
       <c r="E41">
         <v>-203.4509999999999</v>
@@ -4643,37 +4643,37 @@
         <v>188.525</v>
       </c>
       <c r="M41">
-        <v>37.07305129015001</v>
+        <v>35.56310389015002</v>
       </c>
       <c r="N41">
-        <v>151.45194870985</v>
+        <v>152.96189610985</v>
       </c>
       <c r="O41">
-        <v>37.86298717746249</v>
+        <v>38.24047402746249</v>
       </c>
       <c r="P41">
-        <v>113.5889615323875</v>
+        <v>114.7214220823875</v>
       </c>
       <c r="Q41">
-        <v>156.6889615323875</v>
+        <v>157.8214220823875</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.09718186554071336</v>
+        <v>0.09715786970293491</v>
       </c>
       <c r="T41">
         <v>1.001060472862811</v>
       </c>
       <c r="U41">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V41">
         <v>0.25</v>
       </c>
       <c r="W41">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.085230199276569</v>
+        <v>5.301140209311598</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4692,13 +4692,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.07788710043571495</v>
+        <v>0.0770925035216536</v>
       </c>
       <c r="C42">
-        <v>1097.734486355386</v>
+        <v>1137.756242266641</v>
       </c>
       <c r="D42">
-        <v>1600.874486355386</v>
+        <v>1640.896242266641</v>
       </c>
       <c r="E42">
         <v>-188.5599999999999</v>
@@ -4725,37 +4725,37 @@
         <v>188.525</v>
       </c>
       <c r="M42">
-        <v>38.02364234887181</v>
+        <v>36.47497834887181</v>
       </c>
       <c r="N42">
-        <v>150.5013576511282</v>
+        <v>152.0500216511282</v>
       </c>
       <c r="O42">
-        <v>37.62533941278204</v>
+        <v>38.01250541278204</v>
       </c>
       <c r="P42">
-        <v>112.8760182383461</v>
+        <v>114.0375162383461</v>
       </c>
       <c r="Q42">
-        <v>155.9760182383461</v>
+        <v>157.1375162383461</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.09789352572825787</v>
+        <v>0.09786919753815562</v>
       </c>
       <c r="T42">
         <v>1.014925576365066</v>
       </c>
       <c r="U42">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V42">
         <v>0.25</v>
       </c>
       <c r="W42">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.958099444294653</v>
+        <v>5.168611704078809</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4774,13 +4774,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.07782105251780352</v>
+        <v>0.07700699615072568</v>
       </c>
       <c r="C43">
-        <v>1086.145514813149</v>
+        <v>1127.361308564212</v>
       </c>
       <c r="D43">
-        <v>1604.176514813149</v>
+        <v>1645.392308564212</v>
       </c>
       <c r="E43">
         <v>-173.6689999999999</v>
@@ -4807,37 +4807,37 @@
         <v>188.525</v>
       </c>
       <c r="M43">
-        <v>38.97423340759361</v>
+        <v>37.38685280759361</v>
       </c>
       <c r="N43">
-        <v>149.5507665924064</v>
+        <v>151.1381471924064</v>
       </c>
       <c r="O43">
-        <v>37.38769164810159</v>
+        <v>37.78453679810159</v>
       </c>
       <c r="P43">
-        <v>112.1630749443048</v>
+        <v>113.3536103943048</v>
       </c>
       <c r="Q43">
-        <v>155.2630749443048</v>
+        <v>156.4536103943048</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.09862930998995642</v>
+        <v>0.0986046381813499</v>
       </c>
       <c r="T43">
         <v>1.029260683375872</v>
       </c>
       <c r="U43">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V43">
         <v>0.25</v>
       </c>
       <c r="W43">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.83717018955576</v>
+        <v>5.042548003979325</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4856,13 +4856,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.0777550045998921</v>
+        <v>0.07692148877979776</v>
       </c>
       <c r="C44">
-        <v>1074.570193220723</v>
+        <v>1116.991081058286</v>
       </c>
       <c r="D44">
-        <v>1607.492193220723</v>
+        <v>1649.913081058286</v>
       </c>
       <c r="E44">
         <v>-158.778</v>
@@ -4889,37 +4889,37 @@
         <v>188.525</v>
       </c>
       <c r="M44">
-        <v>39.92482446631539</v>
+        <v>38.2987272663154</v>
       </c>
       <c r="N44">
-        <v>148.6001755336846</v>
+        <v>150.2262727336846</v>
       </c>
       <c r="O44">
-        <v>37.15004388342115</v>
+        <v>37.55656818342115</v>
       </c>
       <c r="P44">
-        <v>111.4501316502634</v>
+        <v>112.6697045502634</v>
       </c>
       <c r="Q44">
-        <v>154.5501316502635</v>
+        <v>155.7697045502635</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.09939046612274803</v>
+        <v>0.0993654388467233</v>
       </c>
       <c r="T44">
         <v>1.044090104421533</v>
       </c>
       <c r="U44">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V44">
         <v>0.25</v>
       </c>
       <c r="W44">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.721999470756814</v>
+        <v>4.922487337217914</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4938,13 +4938,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.07768895668198068</v>
+        <v>0.07683598140886984</v>
       </c>
       <c r="C45">
-        <v>1063.00860639281</v>
+        <v>1106.64576395332</v>
       </c>
       <c r="D45">
-        <v>1610.82160639281</v>
+        <v>1654.45876395332</v>
       </c>
       <c r="E45">
         <v>-143.8869999999999</v>
@@ -4971,37 +4971,37 @@
         <v>188.525</v>
       </c>
       <c r="M45">
-        <v>40.87541552503719</v>
+        <v>39.21060172503719</v>
       </c>
       <c r="N45">
-        <v>147.6495844749628</v>
+        <v>149.3143982749628</v>
       </c>
       <c r="O45">
-        <v>36.91239611874069</v>
+        <v>37.3285995687407</v>
       </c>
       <c r="P45">
-        <v>110.7371883562221</v>
+        <v>111.9857987062221</v>
       </c>
       <c r="Q45">
-        <v>153.8371883562221</v>
+        <v>155.0857987062221</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1001783294882692</v>
+        <v>0.1001529342722852</v>
       </c>
       <c r="T45">
         <v>1.0594398560302</v>
       </c>
       <c r="U45">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V45">
         <v>0.25</v>
       </c>
       <c r="W45">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.612185529576422</v>
+        <v>4.808010887515172</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5020,13 +5020,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.07762290876406926</v>
+        <v>0.07675047403794193</v>
       </c>
       <c r="C46">
-        <v>1051.460839848235</v>
+        <v>1096.325563710405</v>
       </c>
       <c r="D46">
-        <v>1614.164839848235</v>
+        <v>1659.029563710405</v>
       </c>
       <c r="E46">
         <v>-128.996</v>
@@ -5053,37 +5053,37 @@
         <v>188.525</v>
       </c>
       <c r="M46">
-        <v>41.82600658375899</v>
+        <v>40.12247618375899</v>
       </c>
       <c r="N46">
-        <v>146.698993416241</v>
+        <v>148.402523816241</v>
       </c>
       <c r="O46">
-        <v>36.67474835406025</v>
+        <v>37.10063095406025</v>
       </c>
       <c r="P46">
-        <v>110.0242450621807</v>
+        <v>111.3018928621808</v>
       </c>
       <c r="Q46">
-        <v>153.1242450621808</v>
+        <v>154.4018928621808</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1009943308311304</v>
+        <v>0.1009685545344744</v>
       </c>
       <c r="T46">
         <v>1.075337813053462</v>
       </c>
       <c r="U46">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V46">
         <v>0.25</v>
       </c>
       <c r="W46">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.507363131176958</v>
+        <v>4.698737912798917</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5102,13 +5102,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.07843436084615782</v>
+        <v>0.076664966667014</v>
       </c>
       <c r="C47">
-        <v>996.4336954235403</v>
+        <v>1086.03068907853</v>
       </c>
       <c r="D47">
-        <v>1574.02869542354</v>
+        <v>1663.62568907853</v>
       </c>
       <c r="E47">
         <v>-114.1049999999999</v>
@@ -5135,45 +5135,45 @@
         <v>188.525</v>
       </c>
       <c r="M47">
-        <v>44.51884464248078</v>
+        <v>41.03435064248079</v>
       </c>
       <c r="N47">
-        <v>144.0061553575192</v>
+        <v>147.4906493575192</v>
       </c>
       <c r="O47">
-        <v>36.0015388393798</v>
+        <v>36.8726623393798</v>
       </c>
       <c r="P47">
-        <v>108.0046165181394</v>
+        <v>110.6179870181394</v>
       </c>
       <c r="Q47">
-        <v>151.1046165181394</v>
+        <v>153.7179870181394</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1018400049500956</v>
+        <v>0.1018138337152886</v>
       </c>
       <c r="T47">
         <v>1.091813877604843</v>
       </c>
       <c r="U47">
-        <v>0.06643661666253409</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V47">
         <v>0.25</v>
       </c>
       <c r="W47">
-        <v>0.04982746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y47">
-        <v>4.234723553901612</v>
+        <v>4.594321514736719</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5184,13 +5184,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.0783878129282464</v>
+        <v>0.07744195929608608</v>
       </c>
       <c r="C48">
-        <v>983.7910131816581</v>
+        <v>1030.288081696908</v>
       </c>
       <c r="D48">
-        <v>1576.277013181658</v>
+        <v>1622.774081696908</v>
       </c>
       <c r="E48">
         <v>-99.21399999999994</v>
@@ -5217,37 +5217,37 @@
         <v>188.525</v>
       </c>
       <c r="M48">
-        <v>45.50815230120257</v>
+        <v>43.65869010120258</v>
       </c>
       <c r="N48">
-        <v>143.0168476987974</v>
+        <v>144.8663098987974</v>
       </c>
       <c r="O48">
-        <v>35.75421192469935</v>
+        <v>36.21657747469935</v>
       </c>
       <c r="P48">
-        <v>107.262635774098</v>
+        <v>108.649732424098</v>
       </c>
       <c r="Q48">
-        <v>150.3626357740981</v>
+        <v>151.7497324240981</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1027170003327262</v>
+        <v>0.1026904195324293</v>
       </c>
       <c r="T48">
         <v>1.108900166769238</v>
       </c>
       <c r="U48">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V48">
         <v>0.25</v>
       </c>
       <c r="W48">
-        <v>0.04982746249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.142664346208099</v>
+        <v>4.318155207199106</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5266,13 +5266,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.07834126501033498</v>
+        <v>0.07737520192515816</v>
       </c>
       <c r="C49">
-        <v>971.1547630505381</v>
+        <v>1018.828006115406</v>
       </c>
       <c r="D49">
-        <v>1578.531763050538</v>
+        <v>1626.205006115406</v>
       </c>
       <c r="E49">
         <v>-84.32299999999998</v>
@@ -5299,37 +5299,37 @@
         <v>188.525</v>
       </c>
       <c r="M49">
-        <v>46.49745995992436</v>
+        <v>44.60779205992437</v>
       </c>
       <c r="N49">
-        <v>142.0275400400756</v>
+        <v>143.9172079400756</v>
       </c>
       <c r="O49">
-        <v>35.50688501001891</v>
+        <v>35.9793019850189</v>
       </c>
       <c r="P49">
-        <v>106.5206550300567</v>
+        <v>107.9379059550567</v>
       </c>
       <c r="Q49">
-        <v>149.6206550300568</v>
+        <v>151.0379059550567</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1036270898807391</v>
+        <v>0.1036000840596507</v>
       </c>
       <c r="T49">
         <v>1.126631221562478</v>
       </c>
       <c r="U49">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V49">
         <v>0.25</v>
       </c>
       <c r="W49">
-        <v>0.04982746249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.054522551607928</v>
+        <v>4.226279564492742</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5348,13 +5348,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.07926671709242356</v>
+        <v>0.07730844455423024</v>
       </c>
       <c r="C50">
-        <v>912.6127678625818</v>
+        <v>1007.382468826561</v>
       </c>
       <c r="D50">
-        <v>1534.880767862582</v>
+        <v>1629.650468826561</v>
       </c>
       <c r="E50">
         <v>-69.43200000000002</v>
@@ -5381,45 +5381,45 @@
         <v>188.525</v>
       </c>
       <c r="M50">
-        <v>49.41664121864616</v>
+        <v>45.55689401864616</v>
       </c>
       <c r="N50">
-        <v>139.1083587813538</v>
+        <v>142.9681059813538</v>
       </c>
       <c r="O50">
-        <v>34.77708969533845</v>
+        <v>35.74202649533845</v>
       </c>
       <c r="P50">
-        <v>104.3312690860154</v>
+        <v>107.2260794860154</v>
       </c>
       <c r="Q50">
-        <v>147.4312690860154</v>
+        <v>150.3260794860154</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1045721828729063</v>
+        <v>0.104544735684073</v>
       </c>
       <c r="T50">
         <v>1.145044240001612</v>
       </c>
       <c r="U50">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V50">
         <v>0.25</v>
       </c>
       <c r="W50">
-        <v>0.05185246249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>3.815010396312906</v>
+        <v>4.13823207356581</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5430,13 +5430,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.07924041917451213</v>
+        <v>0.07724168718330232</v>
       </c>
       <c r="C51">
-        <v>898.9288151853565</v>
+        <v>995.9515624340085</v>
       </c>
       <c r="D51">
-        <v>1536.087815185356</v>
+        <v>1633.110562434008</v>
       </c>
       <c r="E51">
         <v>-54.54099999999994</v>
@@ -5463,45 +5463,45 @@
         <v>188.525</v>
       </c>
       <c r="M51">
-        <v>50.44615457736796</v>
+        <v>46.50599597736797</v>
       </c>
       <c r="N51">
-        <v>138.078845422632</v>
+        <v>142.019004022632</v>
       </c>
       <c r="O51">
-        <v>34.519711355658</v>
+        <v>35.504751005658</v>
       </c>
       <c r="P51">
-        <v>103.559134066974</v>
+        <v>106.514253016974</v>
       </c>
       <c r="Q51">
-        <v>146.659134066974</v>
+        <v>149.614253016974</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1055543383353546</v>
+        <v>0.1055264324702373</v>
       </c>
       <c r="T51">
         <v>1.164179337595222</v>
       </c>
       <c r="U51">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V51">
         <v>0.25</v>
       </c>
       <c r="W51">
-        <v>0.05185246249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y51">
-        <v>3.737153041286112</v>
+        <v>4.053778357778752</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5512,13 +5512,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.0792141212566007</v>
+        <v>0.07848742981237439</v>
       </c>
       <c r="C52">
-        <v>885.2467624731901</v>
+        <v>918.8214859055222</v>
       </c>
       <c r="D52">
-        <v>1537.29676247319</v>
+        <v>1570.871485905522</v>
       </c>
       <c r="E52">
         <v>-39.64999999999998</v>
@@ -5545,37 +5545,37 @@
         <v>188.525</v>
       </c>
       <c r="M52">
-        <v>51.47566793608976</v>
+        <v>50.06102293608976</v>
       </c>
       <c r="N52">
-        <v>137.0493320639102</v>
+        <v>138.4639770639102</v>
       </c>
       <c r="O52">
-        <v>34.26233301597755</v>
+        <v>34.61599426597756</v>
       </c>
       <c r="P52">
-        <v>102.7869990479327</v>
+        <v>103.8479827979327</v>
       </c>
       <c r="Q52">
-        <v>145.8869990479327</v>
+        <v>146.9479827979327</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1065757800163008</v>
+        <v>0.1065473971278482</v>
       </c>
       <c r="T52">
         <v>1.184079839092576</v>
       </c>
       <c r="U52">
-        <v>0.06913661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V52">
         <v>0.25</v>
       </c>
       <c r="W52">
-        <v>0.05185246249690057</v>
+        <v>0.05042746249690057</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.662409980460389</v>
+        <v>3.765903869776689</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5594,13 +5594,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.07918782333868929</v>
+        <v>0.07844692244144648</v>
       </c>
       <c r="C53">
-        <v>871.566614215602</v>
+        <v>905.8795784753889</v>
       </c>
       <c r="D53">
-        <v>1538.507614215602</v>
+        <v>1572.820578475389</v>
       </c>
       <c r="E53">
         <v>-24.75900000000001</v>
@@ -5627,37 +5627,37 @@
         <v>188.525</v>
       </c>
       <c r="M53">
-        <v>52.50518129481155</v>
+        <v>51.06224339481155</v>
       </c>
       <c r="N53">
-        <v>136.0198187051884</v>
+        <v>137.4627566051884</v>
       </c>
       <c r="O53">
-        <v>34.0049546762971</v>
+        <v>34.3656891512971</v>
       </c>
       <c r="P53">
-        <v>102.0148640288913</v>
+        <v>103.0970674538913</v>
       </c>
       <c r="Q53">
-        <v>145.1148640288913</v>
+        <v>146.1970674538913</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1076389131944286</v>
+        <v>0.1076100338123004</v>
       </c>
       <c r="T53">
         <v>1.20479260595717</v>
       </c>
       <c r="U53">
-        <v>0.06913661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V53">
         <v>0.25</v>
       </c>
       <c r="W53">
-        <v>0.05185246249690057</v>
+        <v>0.05042746249690057</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.590598020059205</v>
+        <v>3.692062617428126</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5676,13 +5676,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.07916152542077785</v>
+        <v>0.07840641507051856</v>
       </c>
       <c r="C54">
-        <v>857.8883749162729</v>
+        <v>892.9425138110454</v>
       </c>
       <c r="D54">
-        <v>1539.720374916273</v>
+        <v>1574.774513811045</v>
       </c>
       <c r="E54">
         <v>-9.867999999999938</v>
@@ -5709,37 +5709,37 @@
         <v>188.525</v>
       </c>
       <c r="M54">
-        <v>53.53469465353335</v>
+        <v>52.06346385353335</v>
       </c>
       <c r="N54">
-        <v>134.9903053464666</v>
+        <v>136.4615361464666</v>
       </c>
       <c r="O54">
-        <v>33.74757633661666</v>
+        <v>34.11538403661666</v>
       </c>
       <c r="P54">
-        <v>101.24272900985</v>
+        <v>102.34615210985</v>
       </c>
       <c r="Q54">
-        <v>144.34272900985</v>
+        <v>145.44615210985</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1087463435883116</v>
+        <v>0.1087169470252714</v>
       </c>
       <c r="T54">
         <v>1.226368404774454</v>
       </c>
       <c r="U54">
-        <v>0.06913661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V54">
         <v>0.25</v>
       </c>
       <c r="W54">
-        <v>0.05185246249690057</v>
+        <v>0.05042746249690057</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.52154805813499</v>
+        <v>3.621061413246816</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5758,13 +5758,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.08100347750286643</v>
+        <v>0.07836590769959065</v>
       </c>
       <c r="C55">
-        <v>762.4345626151216</v>
+        <v>880.0103099836322</v>
       </c>
       <c r="D55">
-        <v>1459.157562615122</v>
+        <v>1576.733309983632</v>
       </c>
       <c r="E55">
         <v>5.023000000000025</v>
@@ -5791,45 +5791,45 @@
         <v>188.525</v>
       </c>
       <c r="M55">
-        <v>58.27355611225515</v>
+        <v>53.06468431225515</v>
       </c>
       <c r="N55">
-        <v>130.2514438877448</v>
+        <v>135.4603156877448</v>
       </c>
       <c r="O55">
-        <v>32.5628609719362</v>
+        <v>33.86507892193621</v>
       </c>
       <c r="P55">
-        <v>97.68858291580861</v>
+        <v>101.5952367658086</v>
       </c>
       <c r="Q55">
-        <v>140.7885829158086</v>
+        <v>144.6952367658087</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1099008986798067</v>
+        <v>0.109870962928156</v>
       </c>
       <c r="T55">
         <v>1.248862322690347</v>
       </c>
       <c r="U55">
-        <v>0.0738366166625341</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V55">
         <v>0.25</v>
       </c>
       <c r="W55">
-        <v>0.05537746249690058</v>
+        <v>0.05042746249690057</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y55">
-        <v>3.235172393406629</v>
+        <v>3.552739499789329</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5840,13 +5840,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.08101242958495501</v>
+        <v>0.07945940032866272</v>
       </c>
       <c r="C56">
-        <v>747.1725999057981</v>
+        <v>813.8959894359004</v>
       </c>
       <c r="D56">
-        <v>1458.786599905798</v>
+        <v>1525.5099894359</v>
       </c>
       <c r="E56">
         <v>19.9140000000001</v>
@@ -5873,37 +5873,37 @@
         <v>188.525</v>
       </c>
       <c r="M56">
-        <v>59.37305717097695</v>
+        <v>56.31742397097694</v>
       </c>
       <c r="N56">
-        <v>129.151942829023</v>
+        <v>132.207576029023</v>
       </c>
       <c r="O56">
-        <v>32.28798570725576</v>
+        <v>33.05189400725576</v>
       </c>
       <c r="P56">
-        <v>96.86395712176727</v>
+        <v>99.15568202176729</v>
       </c>
       <c r="Q56">
-        <v>139.9639571217673</v>
+        <v>142.2556820217673</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.111105651818758</v>
+        <v>0.1110751534355139</v>
       </c>
       <c r="T56">
         <v>1.272334237037365</v>
       </c>
       <c r="U56">
-        <v>0.0738366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V56">
         <v>0.25</v>
       </c>
       <c r="W56">
-        <v>0.05537746249690058</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.175261793528728</v>
+        <v>3.347543028551092</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5922,13 +5922,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.08102138166704359</v>
+        <v>0.07943989295773479</v>
       </c>
       <c r="C57">
-        <v>731.910825768783</v>
+        <v>799.8896144035117</v>
       </c>
       <c r="D57">
-        <v>1458.415825768783</v>
+        <v>1526.394614403512</v>
       </c>
       <c r="E57">
         <v>34.80500000000006</v>
@@ -5955,37 +5955,37 @@
         <v>188.525</v>
       </c>
       <c r="M57">
-        <v>60.47255822969874</v>
+        <v>57.36033922969874</v>
       </c>
       <c r="N57">
-        <v>128.0524417703012</v>
+        <v>131.1646607703012</v>
       </c>
       <c r="O57">
-        <v>32.01311044257531</v>
+        <v>32.79116519257531</v>
       </c>
       <c r="P57">
-        <v>96.03933132772593</v>
+        <v>98.37349557772592</v>
       </c>
       <c r="Q57">
-        <v>139.139331327726</v>
+        <v>141.4734955777259</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1123639495416628</v>
+        <v>0.1123328635209766</v>
       </c>
       <c r="T57">
         <v>1.296849347577584</v>
       </c>
       <c r="U57">
-        <v>0.0738366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V57">
         <v>0.25</v>
       </c>
       <c r="W57">
-        <v>0.05537746249690058</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.117529760919115</v>
+        <v>3.286678609850162</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6004,13 +6004,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08103033374913216</v>
+        <v>0.07942038558680688</v>
       </c>
       <c r="C58">
-        <v>716.6492400603273</v>
+        <v>785.884265933256</v>
       </c>
       <c r="D58">
-        <v>1458.045240060327</v>
+        <v>1527.280265933256</v>
       </c>
       <c r="E58">
         <v>49.69600000000014</v>
@@ -6037,37 +6037,37 @@
         <v>188.525</v>
       </c>
       <c r="M58">
-        <v>61.57205928842055</v>
+        <v>58.40325448842054</v>
       </c>
       <c r="N58">
-        <v>126.9529407115794</v>
+        <v>130.1217455115794</v>
       </c>
       <c r="O58">
-        <v>31.73823517789486</v>
+        <v>32.53043637789486</v>
       </c>
       <c r="P58">
-        <v>95.21470553368457</v>
+        <v>97.59130913368458</v>
       </c>
       <c r="Q58">
-        <v>138.3147055336846</v>
+        <v>140.6913091336846</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1136794426156087</v>
+        <v>0.1136477422466876</v>
       </c>
       <c r="T58">
         <v>1.322478781324176</v>
       </c>
       <c r="U58">
-        <v>0.0738366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V58">
         <v>0.25</v>
       </c>
       <c r="W58">
-        <v>0.05537746249690058</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.061859586616988</v>
+        <v>3.227987920388552</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6086,13 +6086,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08103928583122073</v>
+        <v>0.07940087821587896</v>
       </c>
       <c r="C59">
-        <v>701.3878426368271</v>
+        <v>771.87994581308</v>
       </c>
       <c r="D59">
-        <v>1457.674842636827</v>
+        <v>1528.16694581308</v>
       </c>
       <c r="E59">
         <v>64.5870000000001</v>
@@ -6119,37 +6119,37 @@
         <v>188.525</v>
       </c>
       <c r="M59">
-        <v>62.67156034714234</v>
+        <v>59.44616974714233</v>
       </c>
       <c r="N59">
-        <v>125.8534396528576</v>
+        <v>129.0788302528576</v>
       </c>
       <c r="O59">
-        <v>31.46335991321441</v>
+        <v>32.26970756321441</v>
       </c>
       <c r="P59">
-        <v>94.39007973964323</v>
+        <v>96.80912268964323</v>
       </c>
       <c r="Q59">
-        <v>137.4900797396432</v>
+        <v>139.9091226896433</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1150561214139242</v>
+        <v>0.1150237781224317</v>
       </c>
       <c r="T59">
         <v>1.349300281756657</v>
       </c>
       <c r="U59">
-        <v>0.0738366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V59">
         <v>0.25</v>
       </c>
       <c r="W59">
-        <v>0.05537746249690058</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.008142751764058</v>
+        <v>3.171356553364192</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6168,13 +6168,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.08509373791330932</v>
+        <v>0.07938137084495103</v>
       </c>
       <c r="C60">
-        <v>536.0893447862545</v>
+        <v>757.8766558350867</v>
       </c>
       <c r="D60">
-        <v>1307.267344786254</v>
+        <v>1529.054655835087</v>
       </c>
       <c r="E60">
         <v>79.47799999999995</v>
@@ -6201,45 +6201,45 @@
         <v>188.525</v>
       </c>
       <c r="M60">
-        <v>71.80326680586411</v>
+        <v>60.48908500586411</v>
       </c>
       <c r="N60">
-        <v>116.7217331941359</v>
+        <v>128.0359149941359</v>
       </c>
       <c r="O60">
-        <v>29.18043329853397</v>
+        <v>32.00897874853396</v>
       </c>
       <c r="P60">
-        <v>87.5412998956019</v>
+        <v>96.02693624560189</v>
       </c>
       <c r="Q60">
-        <v>130.6412998956019</v>
+        <v>139.1269362456019</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1164983563454928</v>
+        <v>0.1164653395160683</v>
       </c>
       <c r="T60">
         <v>1.377398996495446</v>
       </c>
       <c r="U60">
-        <v>0.08313661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V60">
         <v>0.25</v>
       </c>
       <c r="W60">
-        <v>0.06235246249690057</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y60">
-        <v>2.625576918522644</v>
+        <v>3.116677992099292</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6250,13 +6250,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.08517243999539789</v>
+        <v>0.07936186347402312</v>
       </c>
       <c r="C61">
-        <v>518.5852310982763</v>
+        <v>743.8743977955418</v>
       </c>
       <c r="D61">
-        <v>1304.654231098276</v>
+        <v>1529.943397795542</v>
       </c>
       <c r="E61">
         <v>94.36899999999991</v>
@@ -6283,45 +6283,45 @@
         <v>188.525</v>
       </c>
       <c r="M61">
-        <v>73.04125416458591</v>
+        <v>61.5320002645859</v>
       </c>
       <c r="N61">
-        <v>115.4837458354141</v>
+        <v>126.9929997354141</v>
       </c>
       <c r="O61">
-        <v>28.87093645885352</v>
+        <v>31.74824993385352</v>
       </c>
       <c r="P61">
-        <v>86.61280937656055</v>
+        <v>95.24474980156056</v>
       </c>
       <c r="Q61">
-        <v>129.7128093765606</v>
+        <v>138.3447498015606</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1180109442005526</v>
+        <v>0.1179772209776873</v>
       </c>
       <c r="T61">
         <v>1.406868380245883</v>
       </c>
       <c r="U61">
-        <v>0.08313661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V61">
         <v>0.25</v>
       </c>
       <c r="W61">
-        <v>0.06235246249690057</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y61">
-        <v>2.581075614818871</v>
+        <v>3.063852941385745</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6332,13 +6332,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.08525114207748646</v>
+        <v>0.0793423561030952</v>
       </c>
       <c r="C62">
-        <v>501.0915433435993</v>
+        <v>729.8731734948927</v>
       </c>
       <c r="D62">
-        <v>1302.051543343599</v>
+        <v>1530.833173494893</v>
       </c>
       <c r="E62">
         <v>109.26</v>
@@ -6365,45 +6365,45 @@
         <v>188.525</v>
       </c>
       <c r="M62">
-        <v>74.2792415233077</v>
+        <v>62.5749155233077</v>
       </c>
       <c r="N62">
-        <v>114.2457584766923</v>
+        <v>125.9500844766923</v>
       </c>
       <c r="O62">
-        <v>28.56143961917307</v>
+        <v>31.48752111917307</v>
       </c>
       <c r="P62">
-        <v>85.6843188575192</v>
+        <v>94.4625633575192</v>
       </c>
       <c r="Q62">
-        <v>128.7843188575192</v>
+        <v>137.5625633575192</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1195991614483653</v>
+        <v>0.1195646965123871</v>
       </c>
       <c r="T62">
         <v>1.437811233183843</v>
       </c>
       <c r="U62">
-        <v>0.08313661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V62">
         <v>0.25</v>
       </c>
       <c r="W62">
-        <v>0.06235246249690057</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y62">
-        <v>2.538057687905223</v>
+        <v>3.012788725695982</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6414,13 +6414,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.08748009415957506</v>
+        <v>0.08289134873216727</v>
       </c>
       <c r="C63">
-        <v>416.5699305284968</v>
+        <v>568.5082426518034</v>
       </c>
       <c r="D63">
-        <v>1232.420930528497</v>
+        <v>1384.359242651803</v>
       </c>
       <c r="E63">
         <v>124.151</v>
@@ -6447,45 +6447,45 @@
         <v>188.525</v>
       </c>
       <c r="M63">
-        <v>79.78647858202949</v>
+        <v>70.70296858202951</v>
       </c>
       <c r="N63">
-        <v>108.7385214179705</v>
+        <v>117.8220314179705</v>
       </c>
       <c r="O63">
-        <v>27.18463035449262</v>
+        <v>29.45550785449262</v>
       </c>
       <c r="P63">
-        <v>81.55389106347786</v>
+        <v>88.36652356347784</v>
       </c>
       <c r="Q63">
-        <v>124.6538910634779</v>
+        <v>131.4665235634779</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1212688257345274</v>
+        <v>0.1212335810488665</v>
       </c>
       <c r="T63">
         <v>1.47034089909298</v>
       </c>
       <c r="U63">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V63">
         <v>0.25</v>
       </c>
       <c r="W63">
-        <v>0.06587746249690057</v>
+        <v>0.05837746249690058</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y63">
-        <v>2.362869039346999</v>
+        <v>2.666436838239309</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6496,13 +6496,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.08759404624166361</v>
+        <v>0.08293034136123936</v>
       </c>
       <c r="C64">
-        <v>398.3187167260044</v>
+        <v>552.1634502956795</v>
       </c>
       <c r="D64">
-        <v>1229.060716726004</v>
+        <v>1382.905450295679</v>
       </c>
       <c r="E64">
         <v>139.042</v>
@@ -6529,45 +6529,45 @@
         <v>188.525</v>
       </c>
       <c r="M64">
-        <v>81.0944536407513</v>
+        <v>71.86203364075131</v>
       </c>
       <c r="N64">
-        <v>107.4305463592487</v>
+        <v>116.6629663592487</v>
       </c>
       <c r="O64">
-        <v>26.85763658981217</v>
+        <v>29.16574158981217</v>
       </c>
       <c r="P64">
-        <v>80.57290976943651</v>
+        <v>87.4972247694365</v>
       </c>
       <c r="Q64">
-        <v>123.6729097694365</v>
+        <v>130.5972247694365</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1230263670883823</v>
+        <v>0.1229903016135816</v>
       </c>
       <c r="T64">
         <v>1.504582652681544</v>
       </c>
       <c r="U64">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V64">
         <v>0.25</v>
       </c>
       <c r="W64">
-        <v>0.06587746249690057</v>
+        <v>0.05837746249690058</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y64">
-        <v>2.32475824838979</v>
+        <v>2.623429792461256</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6578,13 +6578,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.0877079983237522</v>
+        <v>0.08296933399031145</v>
       </c>
       <c r="C65">
-        <v>380.0857764452431</v>
+        <v>535.821708152191</v>
       </c>
       <c r="D65">
-        <v>1225.718776445243</v>
+        <v>1381.454708152191</v>
       </c>
       <c r="E65">
         <v>153.933</v>
@@ -6611,45 +6611,45 @@
         <v>188.525</v>
       </c>
       <c r="M65">
-        <v>82.40242869947309</v>
+        <v>73.0210986994731</v>
       </c>
       <c r="N65">
-        <v>106.1225713005269</v>
+        <v>115.5039013005269</v>
       </c>
       <c r="O65">
-        <v>26.53064282513172</v>
+        <v>28.87597532513172</v>
       </c>
       <c r="P65">
-        <v>79.59192847539516</v>
+        <v>86.62792597539516</v>
       </c>
       <c r="Q65">
-        <v>122.6919284753952</v>
+        <v>129.7279259753952</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1248789106775806</v>
+        <v>0.1248419800466597</v>
       </c>
       <c r="T65">
         <v>1.540675311869491</v>
       </c>
       <c r="U65">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V65">
         <v>0.25</v>
       </c>
       <c r="W65">
-        <v>0.06587746249690057</v>
+        <v>0.05837746249690058</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y65">
-        <v>2.287857323812174</v>
+        <v>2.581788049723776</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6660,13 +6660,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.08782195040584077</v>
+        <v>0.08300832661938351</v>
       </c>
       <c r="C66">
-        <v>361.8709610277757</v>
+        <v>519.4830066318874</v>
       </c>
       <c r="D66">
-        <v>1222.394961027776</v>
+        <v>1380.007006631887</v>
       </c>
       <c r="E66">
         <v>168.8240000000001</v>
@@ -6693,45 +6693,45 @@
         <v>188.525</v>
       </c>
       <c r="M66">
-        <v>83.71040375819489</v>
+        <v>74.18016375819491</v>
       </c>
       <c r="N66">
-        <v>104.8145962418051</v>
+        <v>114.3448362418051</v>
       </c>
       <c r="O66">
-        <v>26.20364906045127</v>
+        <v>28.58620906045127</v>
       </c>
       <c r="P66">
-        <v>78.61094718135382</v>
+        <v>85.7586271813538</v>
       </c>
       <c r="Q66">
-        <v>121.7109471813538</v>
+        <v>128.8586271813538</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1268343733550678</v>
+        <v>0.1267965295037976</v>
       </c>
       <c r="T66">
         <v>1.578773118790102</v>
       </c>
       <c r="U66">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V66">
         <v>0.25</v>
       </c>
       <c r="W66">
-        <v>0.06587746249690057</v>
+        <v>0.05837746249690058</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y66">
-        <v>2.252109553127609</v>
+        <v>2.541447611446841</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6742,13 +6742,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.08793590248792935</v>
+        <v>0.0830473192484556</v>
       </c>
       <c r="C67">
-        <v>343.6741234232863</v>
+        <v>503.147336185471</v>
       </c>
       <c r="D67">
-        <v>1219.089123423286</v>
+        <v>1378.562336185471</v>
       </c>
       <c r="E67">
         <v>183.715</v>
@@ -6775,45 +6775,45 @@
         <v>188.525</v>
       </c>
       <c r="M67">
-        <v>85.01837881691668</v>
+        <v>75.3392288169167</v>
       </c>
       <c r="N67">
-        <v>103.5066211830833</v>
+        <v>113.1857711830833</v>
       </c>
       <c r="O67">
-        <v>25.87665529577082</v>
+        <v>28.29644279577082</v>
       </c>
       <c r="P67">
-        <v>77.62996588731247</v>
+        <v>84.88932838731246</v>
       </c>
       <c r="Q67">
-        <v>120.7299658873125</v>
+        <v>127.9893283873125</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1289015767569828</v>
+        <v>0.1288627675013435</v>
       </c>
       <c r="T67">
         <v>1.619047943249033</v>
       </c>
       <c r="U67">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V67">
         <v>0.25</v>
       </c>
       <c r="W67">
-        <v>0.06587746249690057</v>
+        <v>0.05837746249690058</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y67">
-        <v>2.217461713848722</v>
+        <v>2.502348417424582</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6824,13 +6824,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.08804985457001793</v>
+        <v>0.08501681187752766</v>
       </c>
       <c r="C68">
-        <v>325.4951181678973</v>
+        <v>419.0240801746386</v>
       </c>
       <c r="D68">
-        <v>1215.801118167897</v>
+        <v>1309.330080174639</v>
       </c>
       <c r="E68">
         <v>198.6060000000001</v>
@@ -6857,37 +6857,37 @@
         <v>188.525</v>
       </c>
       <c r="M68">
-        <v>86.32635387563847</v>
+        <v>80.33123727563849</v>
       </c>
       <c r="N68">
-        <v>102.1986461243615</v>
+        <v>108.1937627243615</v>
       </c>
       <c r="O68">
-        <v>25.54966153109038</v>
+        <v>27.04844068109037</v>
       </c>
       <c r="P68">
-        <v>76.64898459327112</v>
+        <v>81.14532204327112</v>
       </c>
       <c r="Q68">
-        <v>119.7489845932711</v>
+        <v>124.2453220432711</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1310903803590104</v>
+        <v>0.1310505489105097</v>
       </c>
       <c r="T68">
         <v>1.661691875029078</v>
       </c>
       <c r="U68">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V68">
         <v>0.25</v>
       </c>
       <c r="W68">
-        <v>0.06587746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.183863809093439</v>
+        <v>2.346845466267612</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6906,13 +6906,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.08816380665210651</v>
+        <v>0.08508505450659976</v>
       </c>
       <c r="C69">
-        <v>307.3338013628337</v>
+        <v>401.8586241985298</v>
       </c>
       <c r="D69">
-        <v>1212.530801362834</v>
+        <v>1307.05562419853</v>
       </c>
       <c r="E69">
         <v>213.4970000000001</v>
@@ -6939,37 +6939,37 @@
         <v>188.525</v>
       </c>
       <c r="M69">
-        <v>87.63432893436027</v>
+        <v>81.54837723436027</v>
       </c>
       <c r="N69">
-        <v>100.8906710656397</v>
+        <v>106.9766227656397</v>
       </c>
       <c r="O69">
-        <v>25.22266776640993</v>
+        <v>26.74415569140993</v>
       </c>
       <c r="P69">
-        <v>75.66800329922978</v>
+        <v>80.23246707422977</v>
       </c>
       <c r="Q69">
-        <v>118.7680032992298</v>
+        <v>123.3324670742298</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1334118387247973</v>
+        <v>0.1333709231323526</v>
       </c>
       <c r="T69">
         <v>1.706920287523065</v>
       </c>
       <c r="U69">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V69">
         <v>0.25</v>
       </c>
       <c r="W69">
-        <v>0.06587746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.151268826868163</v>
+        <v>2.311817921994961</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6988,13 +6988,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.08827775873419508</v>
+        <v>0.08515329713567184</v>
       </c>
       <c r="C70">
-        <v>289.1900306534274</v>
+        <v>384.7010564994816</v>
       </c>
       <c r="D70">
-        <v>1209.278030653427</v>
+        <v>1304.789056499482</v>
       </c>
       <c r="E70">
         <v>228.388</v>
@@ -7021,37 +7021,37 @@
         <v>188.525</v>
       </c>
       <c r="M70">
-        <v>88.94230399308206</v>
+        <v>82.76551719308208</v>
       </c>
       <c r="N70">
-        <v>99.58269600691791</v>
+        <v>105.7594828069179</v>
       </c>
       <c r="O70">
-        <v>24.89567400172948</v>
+        <v>26.43987070172948</v>
       </c>
       <c r="P70">
-        <v>74.68702200518844</v>
+        <v>79.31961210518843</v>
       </c>
       <c r="Q70">
-        <v>117.7870220051885</v>
+        <v>122.4196121051884</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1358783882384459</v>
+        <v>0.1358363207430608</v>
       </c>
       <c r="T70">
         <v>1.754975475797926</v>
       </c>
       <c r="U70">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V70">
         <v>0.25</v>
       </c>
       <c r="W70">
-        <v>0.06587746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.119632520590691</v>
+        <v>2.277820599612682</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7070,13 +7070,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08839171081628365</v>
+        <v>0.08522153976474392</v>
       </c>
       <c r="C71">
-        <v>271.0636652084629</v>
+        <v>367.5513361113033</v>
       </c>
       <c r="D71">
-        <v>1206.042665208463</v>
+        <v>1302.530336111303</v>
       </c>
       <c r="E71">
         <v>243.2790000000001</v>
@@ -7103,37 +7103,37 @@
         <v>188.525</v>
       </c>
       <c r="M71">
-        <v>90.25027905180387</v>
+        <v>83.98265715180388</v>
       </c>
       <c r="N71">
-        <v>98.27472094819611</v>
+        <v>104.5423428481961</v>
       </c>
       <c r="O71">
-        <v>24.56868023704903</v>
+        <v>26.13558571204902</v>
       </c>
       <c r="P71">
-        <v>73.70604071114708</v>
+        <v>78.40675713614708</v>
       </c>
       <c r="Q71">
-        <v>116.8060407111471</v>
+        <v>121.5067571361471</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1385040699787815</v>
+        <v>0.1384607762641372</v>
       </c>
       <c r="T71">
         <v>1.806130998800197</v>
       </c>
       <c r="U71">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V71">
         <v>0.25</v>
       </c>
       <c r="W71">
-        <v>0.06587746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.088913208698072</v>
+        <v>2.244808706864672</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7152,13 +7152,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08850566289837222</v>
+        <v>0.08528978239381599</v>
       </c>
       <c r="C72">
-        <v>252.9545656998519</v>
+        <v>350.4094223509815</v>
       </c>
       <c r="D72">
-        <v>1202.824565699852</v>
+        <v>1300.279422350982</v>
       </c>
       <c r="E72">
         <v>258.1700000000002</v>
@@ -7185,37 +7185,37 @@
         <v>188.525</v>
       </c>
       <c r="M72">
-        <v>91.55825411052567</v>
+        <v>85.19979711052568</v>
       </c>
       <c r="N72">
-        <v>96.96674588947431</v>
+        <v>103.3252028894743</v>
       </c>
       <c r="O72">
-        <v>24.24168647236858</v>
+        <v>25.83130072236857</v>
       </c>
       <c r="P72">
-        <v>72.72505941710574</v>
+        <v>77.49390216710572</v>
       </c>
       <c r="Q72">
-        <v>115.8250594171058</v>
+        <v>120.5939021671057</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1413047971684728</v>
+        <v>0.1412601954866186</v>
       </c>
       <c r="T72">
         <v>1.86069689000262</v>
       </c>
       <c r="U72">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V72">
         <v>0.25</v>
       </c>
       <c r="W72">
-        <v>0.06587746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.059071591430956</v>
+        <v>2.21274001105232</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7234,13 +7234,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.08861961498046081</v>
+        <v>0.08535802502288807</v>
       </c>
       <c r="C73">
-        <v>234.8625942826325</v>
+        <v>333.2752748162343</v>
       </c>
       <c r="D73">
-        <v>1199.623594282632</v>
+        <v>1298.036274816234</v>
       </c>
       <c r="E73">
         <v>273.061</v>
@@ -7267,37 +7267,37 @@
         <v>188.525</v>
       </c>
       <c r="M73">
-        <v>92.86622916924745</v>
+        <v>86.41693706924745</v>
       </c>
       <c r="N73">
-        <v>95.65877083075253</v>
+        <v>102.1080629307525</v>
       </c>
       <c r="O73">
-        <v>23.91469270768813</v>
+        <v>25.52701573268813</v>
       </c>
       <c r="P73">
-        <v>71.7440781230644</v>
+        <v>76.5810471980644</v>
       </c>
       <c r="Q73">
-        <v>114.8440781230644</v>
+        <v>119.6810471980644</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1442986779574531</v>
+        <v>0.144252678103754</v>
       </c>
       <c r="T73">
         <v>1.919025946115555</v>
       </c>
       <c r="U73">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V73">
         <v>0.25</v>
       </c>
       <c r="W73">
-        <v>0.06587746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.030070583100943</v>
+        <v>2.181574658783977</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7316,13 +7316,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.08873356706254938</v>
+        <v>0.08542626765196015</v>
       </c>
       <c r="C74">
-        <v>216.787614575288</v>
+        <v>316.148853383098</v>
       </c>
       <c r="D74">
-        <v>1196.439614575288</v>
+        <v>1295.800853383098</v>
       </c>
       <c r="E74">
         <v>287.9519999999999</v>
@@ -7349,37 +7349,37 @@
         <v>188.525</v>
       </c>
       <c r="M74">
-        <v>94.17420422796923</v>
+        <v>87.63407702796924</v>
       </c>
       <c r="N74">
-        <v>94.35079577203075</v>
+        <v>100.8909229720307</v>
       </c>
       <c r="O74">
-        <v>23.58769894300769</v>
+        <v>25.22273074300768</v>
       </c>
       <c r="P74">
-        <v>70.76309682902306</v>
+        <v>75.66819222902305</v>
       </c>
       <c r="Q74">
-        <v>113.8630968290231</v>
+        <v>118.7681922290231</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1475064073742177</v>
+        <v>0.1474589094792562</v>
       </c>
       <c r="T74">
         <v>1.981521363379413</v>
       </c>
       <c r="U74">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V74">
         <v>0.25</v>
       </c>
       <c r="W74">
-        <v>0.06587746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.001875158335653</v>
+        <v>2.151275010745311</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7398,13 +7398,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.09777176914463795</v>
+        <v>0.08549451028103223</v>
       </c>
       <c r="C75">
-        <v>-6.171403764689558</v>
+        <v>299.0301182035316</v>
       </c>
       <c r="D75">
-        <v>988.3715962353102</v>
+        <v>1293.573118203532</v>
       </c>
       <c r="E75">
         <v>302.843</v>
@@ -7431,45 +7431,45 @@
         <v>188.525</v>
       </c>
       <c r="M75">
-        <v>113.200980186691</v>
+        <v>88.85121698669104</v>
       </c>
       <c r="N75">
-        <v>75.32401981330894</v>
+        <v>99.67378301330893</v>
       </c>
       <c r="O75">
-        <v>18.83100495332723</v>
+        <v>24.91844575332723</v>
       </c>
       <c r="P75">
-        <v>56.4930148599817</v>
+        <v>74.7553372599817</v>
       </c>
       <c r="Q75">
-        <v>99.59301485998172</v>
+        <v>117.8553372599817</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1509517463774094</v>
+        <v>0.150902639475166</v>
       </c>
       <c r="T75">
         <v>2.048646070810965</v>
       </c>
       <c r="U75">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V75">
         <v>0.25</v>
       </c>
       <c r="W75">
-        <v>0.07810246249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y75">
-        <v>1.665400773819136</v>
+        <v>2.12180549005017</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7480,13 +7480,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.09800797122672653</v>
+        <v>0.08556275291010432</v>
       </c>
       <c r="C76">
-        <v>-25.53404714447447</v>
+        <v>281.9190297030507</v>
       </c>
       <c r="D76">
-        <v>983.8999528555254</v>
+        <v>1291.353029703051</v>
       </c>
       <c r="E76">
         <v>317.734</v>
@@ -7513,45 +7513,45 @@
         <v>188.525</v>
       </c>
       <c r="M76">
-        <v>114.7516785454128</v>
+        <v>90.06835694541284</v>
       </c>
       <c r="N76">
-        <v>73.77332145458713</v>
+        <v>98.45664305458713</v>
       </c>
       <c r="O76">
-        <v>18.44333036364678</v>
+        <v>24.61416076364678</v>
       </c>
       <c r="P76">
-        <v>55.32999109094035</v>
+        <v>73.84248229094035</v>
       </c>
       <c r="Q76">
-        <v>98.42999109094038</v>
+        <v>116.9424822909404</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1546621114577696</v>
+        <v>0.1546112717784534</v>
       </c>
       <c r="T76">
         <v>2.120934217275714</v>
       </c>
       <c r="U76">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V76">
         <v>0.25</v>
       </c>
       <c r="W76">
-        <v>0.07810246249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y76">
-        <v>1.642895357956716</v>
+        <v>2.09313244288733</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7562,13 +7562,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.0982441733088151</v>
+        <v>0.08563099553917639</v>
       </c>
       <c r="C77">
-        <v>-44.85641106478761</v>
+        <v>264.8155485783841</v>
       </c>
       <c r="D77">
-        <v>979.4685889352123</v>
+        <v>1289.140548578384</v>
       </c>
       <c r="E77">
         <v>332.6249999999999</v>
@@ -7595,45 +7595,45 @@
         <v>188.525</v>
       </c>
       <c r="M77">
-        <v>116.3023769041346</v>
+        <v>91.28549690413463</v>
       </c>
       <c r="N77">
-        <v>72.22262309586536</v>
+        <v>97.23950309586535</v>
       </c>
       <c r="O77">
-        <v>18.05565577396634</v>
+        <v>24.30987577396634</v>
       </c>
       <c r="P77">
-        <v>54.16696732189902</v>
+        <v>72.92962732189901</v>
       </c>
       <c r="Q77">
-        <v>97.26696732189905</v>
+        <v>116.029627321899</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1586693057445587</v>
+        <v>0.1586165946660038</v>
       </c>
       <c r="T77">
         <v>2.199005415457642</v>
       </c>
       <c r="U77">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V77">
         <v>0.25</v>
       </c>
       <c r="W77">
-        <v>0.07810246249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y77">
-        <v>1.620990086517293</v>
+        <v>2.065224010315499</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.09848037539090368</v>
+        <v>0.08569923816824848</v>
       </c>
       <c r="C78">
-        <v>-64.13903732656263</v>
+        <v>247.7196357951511</v>
       </c>
       <c r="D78">
-        <v>975.0769626734374</v>
+        <v>1286.935635795151</v>
       </c>
       <c r="E78">
         <v>347.516</v>
@@ -7677,45 +7677,45 @@
         <v>188.525</v>
       </c>
       <c r="M78">
-        <v>117.8530752628564</v>
+        <v>92.50263686285643</v>
       </c>
       <c r="N78">
-        <v>70.67192473714356</v>
+        <v>96.02236313714354</v>
       </c>
       <c r="O78">
-        <v>17.66798118428589</v>
+        <v>24.00559078428589</v>
       </c>
       <c r="P78">
-        <v>53.00394355285766</v>
+        <v>72.01677235285766</v>
       </c>
       <c r="Q78">
-        <v>96.10394355285769</v>
+        <v>115.1167723528577</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1630104328885802</v>
+        <v>0.1629556944608501</v>
       </c>
       <c r="T78">
         <v>2.283582546821397</v>
       </c>
       <c r="U78">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V78">
         <v>0.25</v>
       </c>
       <c r="W78">
-        <v>0.07810246249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y78">
-        <v>1.599661269589434</v>
+        <v>2.038050010179768</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7726,13 +7726,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.09871657747299226</v>
+        <v>0.08576748079732055</v>
       </c>
       <c r="C79">
-        <v>-83.38245805705333</v>
+        <v>230.6312525855722</v>
       </c>
       <c r="D79">
-        <v>970.7245419429466</v>
+        <v>1284.738252585572</v>
       </c>
       <c r="E79">
         <v>362.407</v>
@@ -7759,45 +7759,45 @@
         <v>188.525</v>
       </c>
       <c r="M79">
-        <v>119.4037736215782</v>
+        <v>93.71977682157822</v>
       </c>
       <c r="N79">
-        <v>69.12122637842174</v>
+        <v>94.80522317842176</v>
       </c>
       <c r="O79">
-        <v>17.28030659460543</v>
+        <v>23.70130579460544</v>
       </c>
       <c r="P79">
-        <v>51.8409197838163</v>
+        <v>71.10391738381631</v>
       </c>
       <c r="Q79">
-        <v>94.94091978381633</v>
+        <v>114.2039173838163</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1677290493494731</v>
+        <v>0.1676721072813353</v>
       </c>
       <c r="T79">
         <v>2.375514211347219</v>
       </c>
       <c r="U79">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V79">
         <v>0.25</v>
       </c>
       <c r="W79">
-        <v>0.07810246249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y79">
-        <v>1.578886447906454</v>
+        <v>2.011581828229382</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7808,13 +7808,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.09895277955508083</v>
+        <v>0.09414272342639263</v>
       </c>
       <c r="C80">
-        <v>-102.587195924775</v>
+        <v>-6.837083104618841</v>
       </c>
       <c r="D80">
-        <v>966.4108040752251</v>
+        <v>1062.160916895381</v>
       </c>
       <c r="E80">
         <v>377.2980000000001</v>
@@ -7841,37 +7841,37 @@
         <v>188.525</v>
       </c>
       <c r="M80">
-        <v>120.9544719803</v>
+        <v>111.4301883803</v>
       </c>
       <c r="N80">
-        <v>67.57052801969994</v>
+        <v>77.09481161969994</v>
       </c>
       <c r="O80">
-        <v>16.89263200492498</v>
+        <v>19.27370290492498</v>
       </c>
       <c r="P80">
-        <v>50.67789601477495</v>
+        <v>57.82110871477495</v>
       </c>
       <c r="Q80">
-        <v>93.77789601477497</v>
+        <v>100.921108714775</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1728766309431745</v>
+        <v>0.1728172849036826</v>
       </c>
       <c r="T80">
         <v>2.475803299920841</v>
       </c>
       <c r="U80">
-        <v>0.1041366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V80">
         <v>0.25</v>
       </c>
       <c r="W80">
-        <v>0.07810246249690057</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.558644313958935</v>
+        <v>1.691866474788529</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7890,13 +7890,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.09918898163716941</v>
+        <v>0.0943174660554647</v>
       </c>
       <c r="C81">
-        <v>-121.7537643487387</v>
+        <v>-25.55360834750218</v>
       </c>
       <c r="D81">
-        <v>962.1352356512613</v>
+        <v>1058.335391652498</v>
       </c>
       <c r="E81">
         <v>392.189</v>
@@ -7923,37 +7923,37 @@
         <v>188.525</v>
       </c>
       <c r="M81">
-        <v>122.5051703390218</v>
+        <v>112.8587805390218</v>
       </c>
       <c r="N81">
-        <v>66.01982966097816</v>
+        <v>75.66621946097816</v>
       </c>
       <c r="O81">
-        <v>16.50495741524454</v>
+        <v>18.91655486524454</v>
       </c>
       <c r="P81">
-        <v>49.51487224573362</v>
+        <v>56.74966459573362</v>
       </c>
       <c r="Q81">
-        <v>92.61487224573364</v>
+        <v>99.84966459573364</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1785144584029427</v>
+        <v>0.1784524794424441</v>
       </c>
       <c r="T81">
         <v>2.585643730263381</v>
       </c>
       <c r="U81">
-        <v>0.1041366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V81">
         <v>0.25</v>
       </c>
       <c r="W81">
-        <v>0.07810246249690057</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.538914639098695</v>
+        <v>1.670450443462093</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7972,13 +7972,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.09942518371925799</v>
+        <v>0.09449220868453678</v>
       </c>
       <c r="C82">
-        <v>-140.8826677021589</v>
+        <v>-44.24267612412586</v>
       </c>
       <c r="D82">
-        <v>957.8973322978411</v>
+        <v>1054.537323875874</v>
       </c>
       <c r="E82">
         <v>407.08</v>
@@ -8005,37 +8005,37 @@
         <v>188.525</v>
       </c>
       <c r="M82">
-        <v>124.0558686977436</v>
+        <v>114.2873726977436</v>
       </c>
       <c r="N82">
-        <v>64.46913130225636</v>
+        <v>74.23762730225636</v>
       </c>
       <c r="O82">
-        <v>16.11728282556409</v>
+        <v>18.55940682556409</v>
       </c>
       <c r="P82">
-        <v>48.35184847669227</v>
+        <v>55.67822047669227</v>
       </c>
       <c r="Q82">
-        <v>91.45184847669229</v>
+        <v>98.7782204766923</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.1847160686086877</v>
+        <v>0.1846511934350817</v>
       </c>
       <c r="T82">
         <v>2.706468203640175</v>
       </c>
       <c r="U82">
-        <v>0.1041366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V82">
         <v>0.25</v>
       </c>
       <c r="W82">
-        <v>0.07810246249690057</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.519678206109962</v>
+        <v>1.649569812918816</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8054,13 +8054,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09966138580134656</v>
+        <v>0.09466695131360886</v>
       </c>
       <c r="C83">
-        <v>-159.9744015107974</v>
+        <v>-62.90458098876798</v>
       </c>
       <c r="D83">
-        <v>953.6965984892025</v>
+        <v>1050.766419011232</v>
       </c>
       <c r="E83">
         <v>421.9710000000001</v>
@@ -8087,37 +8087,37 @@
         <v>188.525</v>
       </c>
       <c r="M83">
-        <v>125.6065670564654</v>
+        <v>115.7159648564654</v>
       </c>
       <c r="N83">
-        <v>62.91843294353455</v>
+        <v>72.80903514353456</v>
       </c>
       <c r="O83">
-        <v>15.72960823588364</v>
+        <v>18.20225878588364</v>
       </c>
       <c r="P83">
-        <v>47.18882470765092</v>
+        <v>54.60677635765092</v>
       </c>
       <c r="Q83">
-        <v>90.28882470765095</v>
+        <v>97.70677635765094</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.1915704798887216</v>
+        <v>0.1915024036374706</v>
       </c>
       <c r="T83">
         <v>2.840011042635579</v>
       </c>
       <c r="U83">
-        <v>0.1041366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V83">
         <v>0.25</v>
       </c>
       <c r="W83">
-        <v>0.07810246249690057</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.500916746775271</v>
+        <v>1.629204753500066</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8136,13 +8136,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1438586453781467</v>
+        <v>0.09484169394268095</v>
       </c>
       <c r="C84">
-        <v>-604.7181285028056</v>
+        <v>-81.5396132975477</v>
       </c>
       <c r="D84">
-        <v>523.8438714971945</v>
+        <v>1047.022386702452</v>
       </c>
       <c r="E84">
         <v>436.8620000000002</v>
@@ -8169,45 +8169,45 @@
         <v>188.525</v>
       </c>
       <c r="M84">
-        <v>207.0147202151873</v>
+        <v>117.1445570151872</v>
       </c>
       <c r="N84">
-        <v>-18.48972021518728</v>
+        <v>71.38044298481276</v>
       </c>
       <c r="O84">
-        <v>-4.622430053796819</v>
+        <v>17.84511074620319</v>
       </c>
       <c r="P84">
-        <v>-13.86729016139046</v>
+        <v>53.53533223860957</v>
       </c>
       <c r="Q84">
-        <v>29.23270983860957</v>
+        <v>96.63533223860959</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2027191615271379</v>
+        <v>0.1991148594179027</v>
       </c>
       <c r="T84">
-        <v>3.057218113560372</v>
+        <v>2.988391974852694</v>
       </c>
       <c r="U84">
-        <v>0.1695366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V84">
-        <v>0.227671007892618</v>
+        <v>0.25</v>
       </c>
       <c r="W84">
-        <v>0.1309380442722706</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y84">
-        <v>0.9106840315704718</v>
+        <v>1.609336402847626</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8218,13 +8218,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.145096011544772</v>
+        <v>0.09501643657175303</v>
       </c>
       <c r="C85">
-        <v>-626.1369504475206</v>
+        <v>-100.1480592829548</v>
       </c>
       <c r="D85">
-        <v>517.3160495524794</v>
+        <v>1043.304940717045</v>
       </c>
       <c r="E85">
         <v>451.753</v>
@@ -8251,45 +8251,45 @@
         <v>188.525</v>
       </c>
       <c r="M85">
-        <v>209.539289973909</v>
+        <v>118.573149173909</v>
       </c>
       <c r="N85">
-        <v>-21.01428997390903</v>
+        <v>69.95185082609098</v>
       </c>
       <c r="O85">
-        <v>-5.253572493477257</v>
+        <v>17.48796270652274</v>
       </c>
       <c r="P85">
-        <v>-15.76071748043177</v>
+        <v>52.46388811956823</v>
       </c>
       <c r="Q85">
-        <v>27.33928251956825</v>
+        <v>95.56388811956825</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.211949700440499</v>
+        <v>0.2076228982313268</v>
       </c>
       <c r="T85">
-        <v>3.237054473181571</v>
+        <v>3.154229487330646</v>
       </c>
       <c r="U85">
-        <v>0.1695366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V85">
-        <v>0.2249279837011407</v>
+        <v>0.25</v>
       </c>
       <c r="W85">
-        <v>0.1314030873131171</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y85">
-        <v>0.8997119348045627</v>
+        <v>1.589946807632594</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8300,13 +8300,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.1463333777113973</v>
+        <v>0.09519117920082511</v>
       </c>
       <c r="C86">
-        <v>-647.3950833514409</v>
+        <v>-118.730201126795</v>
       </c>
       <c r="D86">
-        <v>510.948916648559</v>
+        <v>1039.613798873205</v>
       </c>
       <c r="E86">
         <v>466.6439999999999</v>
@@ -8333,45 +8333,45 @@
         <v>188.525</v>
       </c>
       <c r="M86">
-        <v>212.0638597326308</v>
+        <v>120.0017413326308</v>
       </c>
       <c r="N86">
-        <v>-23.53885973263081</v>
+        <v>68.52325866736919</v>
       </c>
       <c r="O86">
-        <v>-5.884714933157703</v>
+        <v>17.1308146668423</v>
       </c>
       <c r="P86">
-        <v>-17.65414479947311</v>
+        <v>51.39244400052689</v>
       </c>
       <c r="Q86">
-        <v>25.44585520052691</v>
+        <v>94.49244400052692</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.22233405671803</v>
+        <v>0.2171944418964289</v>
       </c>
       <c r="T86">
-        <v>3.439370377755417</v>
+        <v>3.34079668886834</v>
       </c>
       <c r="U86">
-        <v>0.1695366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V86">
-        <v>0.2222502696094605</v>
+        <v>0.25</v>
       </c>
       <c r="W86">
-        <v>0.1318570579006101</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y86">
-        <v>0.8890010784378417</v>
+        <v>1.571018869446492</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8382,13 +8382,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.1475707438780227</v>
+        <v>0.0953659218298972</v>
       </c>
       <c r="C87">
-        <v>-668.4983883640933</v>
+        <v>-137.2863170315932</v>
       </c>
       <c r="D87">
-        <v>504.7366116359066</v>
+        <v>1035.948682968407</v>
       </c>
       <c r="E87">
         <v>481.535</v>
@@ -8415,45 +8415,45 @@
         <v>188.525</v>
       </c>
       <c r="M87">
-        <v>214.5884294913526</v>
+        <v>121.4303334913526</v>
       </c>
       <c r="N87">
-        <v>-26.06342949135262</v>
+        <v>67.09466650864739</v>
       </c>
       <c r="O87">
-        <v>-6.515857372838155</v>
+        <v>16.77366662716185</v>
       </c>
       <c r="P87">
-        <v>-19.54757211851447</v>
+        <v>50.32099988148555</v>
       </c>
       <c r="Q87">
-        <v>23.55242788148556</v>
+        <v>93.42099988148557</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2341029938325654</v>
+        <v>0.2280421913835447</v>
       </c>
       <c r="T87">
-        <v>3.668661736272446</v>
+        <v>3.552239517277729</v>
       </c>
       <c r="U87">
-        <v>0.1695366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V87">
-        <v>0.2196355605552315</v>
+        <v>0.25</v>
       </c>
       <c r="W87">
-        <v>0.132300346827221</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y87">
-        <v>0.8785422422209259</v>
+        <v>1.552536294511827</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8464,13 +8464,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.148808110044648</v>
+        <v>0.09554066445896926</v>
       </c>
       <c r="C88">
-        <v>-689.452445011038</v>
+        <v>-155.8166812904878</v>
       </c>
       <c r="D88">
-        <v>498.673554988962</v>
+        <v>1032.309318709512</v>
       </c>
       <c r="E88">
         <v>496.426</v>
@@ -8497,45 +8497,45 @@
         <v>188.525</v>
       </c>
       <c r="M88">
-        <v>217.1129992500744</v>
+        <v>122.8589256500744</v>
       </c>
       <c r="N88">
-        <v>-28.58799925007443</v>
+        <v>65.66607434992558</v>
       </c>
       <c r="O88">
-        <v>-7.146999812518608</v>
+        <v>16.4165185874814</v>
       </c>
       <c r="P88">
-        <v>-21.44099943755582</v>
+        <v>49.24955576244419</v>
       </c>
       <c r="Q88">
-        <v>21.6590005624442</v>
+        <v>92.34955576244421</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2475532076777486</v>
+        <v>0.2404396193688198</v>
       </c>
       <c r="T88">
-        <v>3.930709003149049</v>
+        <v>3.793888464031316</v>
       </c>
       <c r="U88">
-        <v>0.1695366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V88">
-        <v>0.2170816586883102</v>
+        <v>0.25</v>
       </c>
       <c r="W88">
-        <v>0.132733326709027</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y88">
-        <v>0.8683266347532407</v>
+        <v>1.534483546901224</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8546,13 +8546,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.1500454762112734</v>
+        <v>0.09571540708804133</v>
       </c>
       <c r="C89">
-        <v>-710.2625679078776</v>
+        <v>-174.3215643556646</v>
       </c>
       <c r="D89">
-        <v>492.7544320921222</v>
+        <v>1028.695435644335</v>
       </c>
       <c r="E89">
         <v>511.3169999999999</v>
@@ -8579,45 +8579,45 @@
         <v>188.525</v>
       </c>
       <c r="M89">
-        <v>219.6375690087962</v>
+        <v>124.2875178087962</v>
       </c>
       <c r="N89">
-        <v>-31.11256900879619</v>
+        <v>64.23748219120381</v>
       </c>
       <c r="O89">
-        <v>-7.778142252199046</v>
+        <v>16.05937054780095</v>
       </c>
       <c r="P89">
-        <v>-23.33442675659714</v>
+        <v>48.17811164340286</v>
       </c>
       <c r="Q89">
-        <v>19.76557324340288</v>
+        <v>91.27811164340288</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2630726851914216</v>
+        <v>0.2547443439672142</v>
       </c>
       <c r="T89">
-        <v>4.233071234160514</v>
+        <v>4.072714171823916</v>
       </c>
       <c r="U89">
-        <v>0.1695366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V89">
-        <v>0.2145864672091342</v>
+        <v>0.25</v>
       </c>
       <c r="W89">
-        <v>0.1331563530303317</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.8583458688365369</v>
+        <v>1.51684580498282</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8628,13 +8628,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.1512828423778987</v>
+        <v>0.1357728356645803</v>
       </c>
       <c r="C90">
-        <v>-730.9338222978865</v>
+        <v>-647.205175525044</v>
       </c>
       <c r="D90">
-        <v>486.9741777021134</v>
+        <v>570.7028244749559</v>
       </c>
       <c r="E90">
         <v>526.208</v>
@@ -8661,37 +8661,37 @@
         <v>188.525</v>
       </c>
       <c r="M90">
-        <v>222.162138767518</v>
+        <v>200.147284367518</v>
       </c>
       <c r="N90">
-        <v>-33.637138767518</v>
+        <v>-11.62228436751801</v>
       </c>
       <c r="O90">
-        <v>-8.409284691879499</v>
+        <v>-2.905571091879501</v>
       </c>
       <c r="P90">
-        <v>-25.2278540756385</v>
+        <v>-8.716713275638504</v>
       </c>
       <c r="Q90">
-        <v>17.87214592436153</v>
+        <v>34.38328672436152</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.2811787422907067</v>
+        <v>0.2751286863463867</v>
       </c>
       <c r="T90">
-        <v>4.585827170340557</v>
+        <v>4.470042946150506</v>
       </c>
       <c r="U90">
-        <v>0.1695366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V90">
-        <v>0.2121479846272122</v>
+        <v>0.2354828352977091</v>
       </c>
       <c r="W90">
-        <v>0.1335697651170612</v>
+        <v>0.1167697651170612</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.848591938508849</v>
+        <v>0.9419313411908365</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8710,13 +8710,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.1525202085445241</v>
+        <v>0.1368422018312056</v>
       </c>
       <c r="C91">
-        <v>-751.4710385087312</v>
+        <v>-668.7995535125684</v>
       </c>
       <c r="D91">
-        <v>481.3279614912688</v>
+        <v>563.9994464874316</v>
       </c>
       <c r="E91">
         <v>541.099</v>
@@ -8743,37 +8743,37 @@
         <v>188.525</v>
       </c>
       <c r="M91">
-        <v>224.6867085262398</v>
+        <v>202.4216853262398</v>
       </c>
       <c r="N91">
-        <v>-36.16170852623981</v>
+        <v>-13.8966853262398</v>
       </c>
       <c r="O91">
-        <v>-9.040427131559952</v>
+        <v>-3.474171331559951</v>
       </c>
       <c r="P91">
-        <v>-27.12128139467985</v>
+        <v>-10.42251399467985</v>
       </c>
       <c r="Q91">
-        <v>15.97871860532017</v>
+        <v>32.67748600532017</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.3025768097716801</v>
+        <v>0.2959767487415128</v>
       </c>
       <c r="T91">
-        <v>5.002720549462427</v>
+        <v>4.876410486709643</v>
       </c>
       <c r="U91">
-        <v>0.1695366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V91">
-        <v>0.2097642994066818</v>
+        <v>0.2328369607438023</v>
       </c>
       <c r="W91">
-        <v>0.1339738870445385</v>
+        <v>0.1171738870445385</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8390571976267269</v>
+        <v>0.9313478429752092</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8792,13 +8792,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.1537575747111494</v>
+        <v>0.137911567997831</v>
       </c>
       <c r="C92">
-        <v>-771.8788254150097</v>
+        <v>-690.2382862151895</v>
       </c>
       <c r="D92">
-        <v>475.8111745849904</v>
+        <v>557.4517137848105</v>
       </c>
       <c r="E92">
         <v>555.9900000000001</v>
@@ -8825,37 +8825,37 @@
         <v>188.525</v>
       </c>
       <c r="M92">
-        <v>227.2112782849616</v>
+        <v>204.6960862849616</v>
       </c>
       <c r="N92">
-        <v>-38.68627828496162</v>
+        <v>-16.1710862849616</v>
       </c>
       <c r="O92">
-        <v>-9.671569571240404</v>
+        <v>-4.042771571240401</v>
       </c>
       <c r="P92">
-        <v>-29.01470871372121</v>
+        <v>-12.1283147137212</v>
       </c>
       <c r="Q92">
-        <v>14.08529128627881</v>
+        <v>30.97168528627882</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.3282544907488482</v>
+        <v>0.3209944236156641</v>
       </c>
       <c r="T92">
-        <v>5.50299260440867</v>
+        <v>5.364051535380609</v>
       </c>
       <c r="U92">
-        <v>0.1695366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V92">
-        <v>0.2074335849688297</v>
+        <v>0.2302498834022045</v>
       </c>
       <c r="W92">
-        <v>0.1343690284847384</v>
+        <v>0.1175690284847384</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8297343398753189</v>
+        <v>0.9209995336088179</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8874,13 +8874,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.1549949408777747</v>
+        <v>0.1389809341644563</v>
       </c>
       <c r="C93">
-        <v>-792.1615829854701</v>
+        <v>-711.5267322978469</v>
       </c>
       <c r="D93">
-        <v>470.4194170145298</v>
+        <v>551.054267702153</v>
       </c>
       <c r="E93">
         <v>570.881</v>
@@ -8907,37 +8907,37 @@
         <v>188.525</v>
       </c>
       <c r="M93">
-        <v>229.7358480436834</v>
+        <v>206.9704872436834</v>
       </c>
       <c r="N93">
-        <v>-41.2108480436834</v>
+        <v>-18.44548724368337</v>
       </c>
       <c r="O93">
-        <v>-10.30271201092085</v>
+        <v>-4.611371810920843</v>
       </c>
       <c r="P93">
-        <v>-30.90813603276255</v>
+        <v>-13.83411543276253</v>
       </c>
       <c r="Q93">
-        <v>12.19186396723747</v>
+        <v>29.26588456723749</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.3596383230542758</v>
+        <v>0.3515715817951823</v>
       </c>
       <c r="T93">
-        <v>6.114436227120745</v>
+        <v>5.960057261534009</v>
       </c>
       <c r="U93">
-        <v>0.1695366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V93">
-        <v>0.2051540950241173</v>
+        <v>0.2277196649032792</v>
       </c>
       <c r="W93">
-        <v>0.1347554854976812</v>
+        <v>0.1179554854976812</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8206163800964692</v>
+        <v>0.9108786596131168</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8956,13 +8956,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.1562323070444001</v>
+        <v>0.1400503003310817</v>
       </c>
       <c r="C94">
-        <v>-812.3235139866977</v>
+        <v>-732.6700072273186</v>
       </c>
       <c r="D94">
-        <v>465.1484860133023</v>
+        <v>544.8019927726814</v>
       </c>
       <c r="E94">
         <v>585.772</v>
@@ -8989,37 +8989,37 @@
         <v>188.525</v>
       </c>
       <c r="M94">
-        <v>232.2604178024052</v>
+        <v>209.2448882024052</v>
       </c>
       <c r="N94">
-        <v>-43.73541780240521</v>
+        <v>-20.7198882024052</v>
       </c>
       <c r="O94">
-        <v>-10.9338544506013</v>
+        <v>-5.1799720506013</v>
       </c>
       <c r="P94">
-        <v>-32.80156335180391</v>
+        <v>-15.5399161518039</v>
       </c>
       <c r="Q94">
-        <v>10.29843664819612</v>
+        <v>27.56008384819612</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.3988681134360604</v>
+        <v>0.3897930295195802</v>
       </c>
       <c r="T94">
-        <v>6.87874075551084</v>
+        <v>6.705064419225764</v>
       </c>
       <c r="U94">
-        <v>0.1695366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V94">
-        <v>0.2029241592086378</v>
+        <v>0.2252444511543305</v>
       </c>
       <c r="W94">
-        <v>0.1351335412712123</v>
+        <v>0.1183335412712122</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8116966368345511</v>
+        <v>0.9009778046173219</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9038,13 +9038,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.1574696732110254</v>
+        <v>0.141119666497707</v>
       </c>
       <c r="C95">
-        <v>-832.3686349086977</v>
+        <v>-753.6729969140974</v>
       </c>
       <c r="D95">
-        <v>459.9943650913023</v>
+        <v>538.6900030859026</v>
       </c>
       <c r="E95">
         <v>600.6630000000001</v>
@@ -9071,37 +9071,37 @@
         <v>188.525</v>
       </c>
       <c r="M95">
-        <v>234.784987561127</v>
+        <v>211.519289161127</v>
       </c>
       <c r="N95">
-        <v>-46.25998756112702</v>
+        <v>-22.994289161127</v>
       </c>
       <c r="O95">
-        <v>-11.56499689028175</v>
+        <v>-5.74857229028175</v>
       </c>
       <c r="P95">
-        <v>-34.69499067084526</v>
+        <v>-17.24571687084525</v>
       </c>
       <c r="Q95">
-        <v>8.405009329154758</v>
+        <v>25.85428312915477</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.4493064153554976</v>
+        <v>0.4389348908795203</v>
       </c>
       <c r="T95">
-        <v>7.861418006298104</v>
+        <v>7.662930764829444</v>
       </c>
       <c r="U95">
-        <v>0.1695366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V95">
-        <v>0.2007421790020933</v>
+        <v>0.222822467808585</v>
       </c>
       <c r="W95">
-        <v>0.1355034668130544</v>
+        <v>0.1187034668130544</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8029687160083731</v>
+        <v>0.8912898712343399</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9120,13 +9120,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2093013648836878</v>
+        <v>0.1421890326643324</v>
       </c>
       <c r="C96">
-        <v>-993.0827974219615</v>
+        <v>-774.5403704461922</v>
       </c>
       <c r="D96">
-        <v>314.1712025780384</v>
+        <v>532.7136295538077</v>
       </c>
       <c r="E96">
         <v>615.554</v>
@@ -9153,45 +9153,45 @@
         <v>188.525</v>
       </c>
       <c r="M96">
-        <v>310.3767161198488</v>
+        <v>213.7936901198487</v>
       </c>
       <c r="N96">
-        <v>-121.8517161198488</v>
+        <v>-25.26869011984877</v>
       </c>
       <c r="O96">
-        <v>-30.4629290299622</v>
+        <v>-6.317172529962193</v>
       </c>
       <c r="P96">
-        <v>-91.38878708988659</v>
+        <v>-18.95151758988658</v>
       </c>
       <c r="Q96">
-        <v>-48.28878708988657</v>
+        <v>24.14848241011344</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.5419962430153648</v>
+        <v>0.5044573726927738</v>
       </c>
       <c r="T96">
-        <v>9.66727152543973</v>
+        <v>8.94008589230102</v>
       </c>
       <c r="U96">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V96">
-        <v>0.1518517580481158</v>
+        <v>0.2204520160233873</v>
       </c>
       <c r="W96">
-        <v>0.1880655215986872</v>
+        <v>0.1190655215986872</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y96">
-        <v>0.6074070321924632</v>
+        <v>0.8818080640935492</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9202,13 +9202,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2110607310503131</v>
+        <v>0.1432583988309577</v>
       </c>
       <c r="C97">
-        <v>-1011.318464850399</v>
+        <v>-795.2765919845958</v>
       </c>
       <c r="D97">
-        <v>310.8265351496005</v>
+        <v>526.8684080154042</v>
       </c>
       <c r="E97">
         <v>630.4450000000001</v>
@@ -9235,45 +9235,45 @@
         <v>188.525</v>
       </c>
       <c r="M97">
-        <v>313.6785960785705</v>
+        <v>216.0680910785705</v>
       </c>
       <c r="N97">
-        <v>-125.1535960785706</v>
+        <v>-27.54309107857057</v>
       </c>
       <c r="O97">
-        <v>-31.28839901964264</v>
+        <v>-6.885772769642642</v>
       </c>
       <c r="P97">
-        <v>-93.86519705892792</v>
+        <v>-20.65731830892793</v>
       </c>
       <c r="Q97">
-        <v>-50.7651970589279</v>
+        <v>22.4426816910721</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.6412354916184381</v>
+        <v>0.5961888472313288</v>
       </c>
       <c r="T97">
-        <v>11.60072583052768</v>
+        <v>10.72810307076123</v>
       </c>
       <c r="U97">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V97">
-        <v>0.1502533184897146</v>
+        <v>0.218131468486299</v>
       </c>
       <c r="W97">
-        <v>0.1884199541783066</v>
+        <v>0.1194199541783066</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y97">
-        <v>0.6010132739588583</v>
+        <v>0.872525873945196</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9284,13 +9284,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2128200972169385</v>
+        <v>0.144327764997583</v>
       </c>
       <c r="C98">
-        <v>-1029.483667768155</v>
+        <v>-815.8859318841075</v>
       </c>
       <c r="D98">
-        <v>307.5523322318444</v>
+        <v>521.1500681158923</v>
       </c>
       <c r="E98">
         <v>645.3359999999999</v>
@@ -9317,45 +9317,45 @@
         <v>188.525</v>
       </c>
       <c r="M98">
-        <v>316.9804760372923</v>
+        <v>218.3424920372923</v>
       </c>
       <c r="N98">
-        <v>-128.4554760372923</v>
+        <v>-29.81749203729234</v>
       </c>
       <c r="O98">
-        <v>-32.11386900932308</v>
+        <v>-7.454373009323085</v>
       </c>
       <c r="P98">
-        <v>-96.34160702796925</v>
+        <v>-22.36311902796925</v>
       </c>
       <c r="Q98">
-        <v>-53.24160702796922</v>
+        <v>20.73688097203077</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.7900943645230459</v>
+        <v>0.7337860590391593</v>
       </c>
       <c r="T98">
-        <v>14.50090728815957</v>
+        <v>13.4101288384515</v>
       </c>
       <c r="U98">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V98">
-        <v>0.1486881797554467</v>
+        <v>0.2158592656895668</v>
       </c>
       <c r="W98">
-        <v>0.1887670027458507</v>
+        <v>0.1197670027458506</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y98">
-        <v>0.5947527190217869</v>
+        <v>0.863437062758267</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9366,13 +9366,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2145794633835639</v>
+        <v>0.1453971311642084</v>
       </c>
       <c r="C99">
-        <v>-1047.580609752731</v>
+        <v>-836.3724770977425</v>
       </c>
       <c r="D99">
-        <v>304.3463902472693</v>
+        <v>515.5545229022574</v>
       </c>
       <c r="E99">
         <v>660.227</v>
@@ -9399,45 +9399,45 @@
         <v>188.525</v>
       </c>
       <c r="M99">
-        <v>320.2823559960141</v>
+        <v>220.6168929960141</v>
       </c>
       <c r="N99">
-        <v>-131.7573559960142</v>
+        <v>-32.09189299601417</v>
       </c>
       <c r="O99">
-        <v>-32.93933899900354</v>
+        <v>-8.022973249003542</v>
       </c>
       <c r="P99">
-        <v>-98.81801699701062</v>
+        <v>-24.06891974701063</v>
       </c>
       <c r="Q99">
-        <v>-55.71801699701059</v>
+        <v>19.0310802529894</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.038192486030728</v>
+        <v>0.9631147453855461</v>
       </c>
       <c r="T99">
-        <v>19.33454305087943</v>
+        <v>17.88017178460201</v>
       </c>
       <c r="U99">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V99">
-        <v>0.1471553119229163</v>
+        <v>0.2136339124350351</v>
       </c>
       <c r="W99">
-        <v>0.1891068956728268</v>
+        <v>0.1201068956728268</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y99">
-        <v>0.5886212476916654</v>
+        <v>0.8545356497401404</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9448,13 +9448,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2163388295501892</v>
+        <v>0.1464664973308337</v>
       </c>
       <c r="C100">
-        <v>-1065.611403448676</v>
+        <v>-856.7401409179853</v>
       </c>
       <c r="D100">
-        <v>301.206596551324</v>
+        <v>510.0778590820147</v>
       </c>
       <c r="E100">
         <v>675.1180000000001</v>
@@ -9481,45 +9481,45 @@
         <v>188.525</v>
       </c>
       <c r="M100">
-        <v>323.584235954736</v>
+        <v>222.8912939547359</v>
       </c>
       <c r="N100">
-        <v>-135.059235954736</v>
+        <v>-34.36629395473597</v>
       </c>
       <c r="O100">
-        <v>-33.764808988684</v>
+        <v>-8.591573488683991</v>
       </c>
       <c r="P100">
-        <v>-101.294426966052</v>
+        <v>-25.77472046605197</v>
       </c>
       <c r="Q100">
-        <v>-58.19442696605196</v>
+        <v>17.32527953394805</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.534388729046092</v>
+        <v>1.421772118078319</v>
       </c>
       <c r="T100">
-        <v>29.00181457631914</v>
+        <v>26.82025767690302</v>
       </c>
       <c r="U100">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V100">
-        <v>0.1456537271073764</v>
+        <v>0.2114539745530449</v>
       </c>
       <c r="W100">
-        <v>0.1894398520094565</v>
+        <v>0.1204398520094564</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y100">
-        <v>0.5826149084295055</v>
+        <v>0.8458158982121797</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9530,13 +9530,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2180981957168145</v>
+        <v>0.147535863497459</v>
       </c>
       <c r="C101">
-        <v>-1083.578075210252</v>
+        <v>-876.9926721036975</v>
       </c>
       <c r="D101">
-        <v>298.1309247897477</v>
+        <v>504.7163278963024</v>
       </c>
       <c r="E101">
         <v>690.0089999999999</v>
@@ -9563,45 +9563,45 @@
         <v>188.525</v>
       </c>
       <c r="M101">
-        <v>326.8861159134577</v>
+        <v>225.1656949134577</v>
       </c>
       <c r="N101">
-        <v>-138.3611159134578</v>
+        <v>-36.64069491345774</v>
       </c>
       <c r="O101">
-        <v>-34.59027897836444</v>
+        <v>-9.160173728364434</v>
       </c>
       <c r="P101">
-        <v>-103.7708369350933</v>
+        <v>-27.4805211850933</v>
       </c>
       <c r="Q101">
-        <v>-60.67083693509329</v>
+        <v>15.61947881490672</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.022977458092184</v>
+        <v>2.797744236156638</v>
       </c>
       <c r="T101">
-        <v>58.00362915263828</v>
+        <v>53.64051535380603</v>
       </c>
       <c r="U101">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V101">
-        <v>0.144182477338615</v>
+        <v>0.2093180758201859</v>
       </c>
       <c r="W101">
-        <v>0.1897660819554471</v>
+        <v>0.1207660819554471</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y101">
-        <v>0.57672990935446</v>
+        <v>0.8372723032807436</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/belgium/belgium_household_products.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_household_products.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08051279835877041</v>
+        <v>0.08038979098784249</v>
       </c>
       <c r="C2">
-        <v>1571.716711631768</v>
+        <v>1562.086066017674</v>
       </c>
       <c r="D2">
-        <v>1479.216711631768</v>
+        <v>1484.477066017674</v>
       </c>
       <c r="E2">
-        <v>-784.1999999999999</v>
+        <v>-769.309</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>14.891</v>
       </c>
       <c r="G2">
         <v>92.5</v>
@@ -1445,28 +1445,28 @@
         <v>188.525</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.8374194587217952</v>
       </c>
       <c r="N2">
-        <v>188.525</v>
+        <v>187.6875805412782</v>
       </c>
       <c r="O2">
-        <v>47.13124999999999</v>
+        <v>46.92189513531955</v>
       </c>
       <c r="P2">
-        <v>141.39375</v>
+        <v>140.7656854059586</v>
       </c>
       <c r="Q2">
-        <v>184.49375</v>
+        <v>183.8656854059587</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08051279835877041</v>
+        <v>0.08077577410391261</v>
       </c>
       <c r="T2">
-        <v>0.6766170509100436</v>
+        <v>0.6817429376593621</v>
       </c>
       <c r="U2">
         <v>0.0562366166625341</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>225.1261276968143</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08038979098784249</v>
+        <v>0.08026678361691457</v>
       </c>
       <c r="C3">
-        <v>1562.086066017674</v>
+        <v>1552.492967415239</v>
       </c>
       <c r="D3">
-        <v>1484.477066017674</v>
+        <v>1489.774967415239</v>
       </c>
       <c r="E3">
-        <v>-769.309</v>
+        <v>-754.4179999999999</v>
       </c>
       <c r="F3">
-        <v>14.891</v>
+        <v>29.782</v>
       </c>
       <c r="G3">
         <v>92.5</v>
@@ -1527,28 +1527,28 @@
         <v>188.525</v>
       </c>
       <c r="M3">
-        <v>0.8374194587217952</v>
+        <v>1.67483891744359</v>
       </c>
       <c r="N3">
-        <v>187.6875805412782</v>
+        <v>186.8501610825564</v>
       </c>
       <c r="O3">
-        <v>46.92189513531955</v>
+        <v>46.7125402706391</v>
       </c>
       <c r="P3">
-        <v>140.7656854059586</v>
+        <v>140.1376208119173</v>
       </c>
       <c r="Q3">
-        <v>183.8656854059587</v>
+        <v>183.2376208119173</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08077577410391261</v>
+        <v>0.08104411670099648</v>
       </c>
       <c r="T3">
-        <v>0.6817429376593621</v>
+        <v>0.6869734343423403</v>
       </c>
       <c r="U3">
         <v>0.0562366166625341</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>225.1261276968143</v>
+        <v>112.5630638484071</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08026678361691457</v>
+        <v>0.08014377624598665</v>
       </c>
       <c r="C4">
-        <v>1552.492967415239</v>
+        <v>1542.937819265177</v>
       </c>
       <c r="D4">
-        <v>1489.774967415239</v>
+        <v>1495.110819265177</v>
       </c>
       <c r="E4">
-        <v>-754.4179999999999</v>
+        <v>-739.5269999999999</v>
       </c>
       <c r="F4">
-        <v>29.782</v>
+        <v>44.67299999999999</v>
       </c>
       <c r="G4">
         <v>92.5</v>
@@ -1609,28 +1609,28 @@
         <v>188.525</v>
       </c>
       <c r="M4">
-        <v>1.67483891744359</v>
+        <v>2.512258376165386</v>
       </c>
       <c r="N4">
-        <v>186.8501610825564</v>
+        <v>186.0127416238346</v>
       </c>
       <c r="O4">
-        <v>46.7125402706391</v>
+        <v>46.50318540595865</v>
       </c>
       <c r="P4">
-        <v>140.1376208119173</v>
+        <v>139.5095562178759</v>
       </c>
       <c r="Q4">
-        <v>183.2376208119173</v>
+        <v>182.609556217876</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08104411670099648</v>
+        <v>0.08131799213513363</v>
       </c>
       <c r="T4">
-        <v>0.6869734343423403</v>
+        <v>0.6923117763177508</v>
       </c>
       <c r="U4">
         <v>0.0562366166625341</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>112.5630638484071</v>
+        <v>75.04204256560476</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08014377624598665</v>
+        <v>0.08002076887505874</v>
       </c>
       <c r="C5">
-        <v>1542.937819265177</v>
+        <v>1533.421030808907</v>
       </c>
       <c r="D5">
-        <v>1495.110819265177</v>
+        <v>1500.485030808907</v>
       </c>
       <c r="E5">
-        <v>-739.5269999999999</v>
+        <v>-724.636</v>
       </c>
       <c r="F5">
-        <v>44.67299999999999</v>
+        <v>59.564</v>
       </c>
       <c r="G5">
         <v>92.5</v>
@@ -1691,28 +1691,28 @@
         <v>188.525</v>
       </c>
       <c r="M5">
-        <v>2.512258376165386</v>
+        <v>3.349677834887181</v>
       </c>
       <c r="N5">
-        <v>186.0127416238346</v>
+        <v>185.1753221651128</v>
       </c>
       <c r="O5">
-        <v>46.50318540595865</v>
+        <v>46.2938305412782</v>
       </c>
       <c r="P5">
-        <v>139.5095562178759</v>
+        <v>138.8814916238346</v>
       </c>
       <c r="Q5">
-        <v>182.609556217876</v>
+        <v>181.9814916238346</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08131799213513363</v>
+        <v>0.08159757330748199</v>
       </c>
       <c r="T5">
-        <v>0.6923117763177508</v>
+        <v>0.6977613337509825</v>
       </c>
       <c r="U5">
         <v>0.0562366166625341</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>75.04204256560476</v>
+        <v>56.28153192420357</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08002076887505874</v>
+        <v>0.07989776150413082</v>
       </c>
       <c r="C6">
-        <v>1533.421030808907</v>
+        <v>1523.943017193194</v>
       </c>
       <c r="D6">
-        <v>1500.485030808907</v>
+        <v>1505.898017193194</v>
       </c>
       <c r="E6">
-        <v>-724.636</v>
+        <v>-709.7449999999999</v>
       </c>
       <c r="F6">
-        <v>59.564</v>
+        <v>74.455</v>
       </c>
       <c r="G6">
         <v>92.5</v>
@@ -1773,28 +1773,28 @@
         <v>188.525</v>
       </c>
       <c r="M6">
-        <v>3.349677834887181</v>
+        <v>4.187097293608977</v>
       </c>
       <c r="N6">
-        <v>185.1753221651128</v>
+        <v>184.337902706391</v>
       </c>
       <c r="O6">
-        <v>46.2938305412782</v>
+        <v>46.08447567659775</v>
       </c>
       <c r="P6">
-        <v>138.8814916238346</v>
+        <v>138.2534270297932</v>
       </c>
       <c r="Q6">
-        <v>181.9814916238346</v>
+        <v>181.3534270297933</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08159757330748199</v>
+        <v>0.08188304039924819</v>
       </c>
       <c r="T6">
-        <v>0.6977613337509825</v>
+        <v>0.7033256187091244</v>
       </c>
       <c r="U6">
         <v>0.0562366166625341</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>56.28153192420357</v>
+        <v>45.02522553936285</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07989776150413082</v>
+        <v>0.0797747541332029</v>
       </c>
       <c r="C7">
-        <v>1523.943017193194</v>
+        <v>1514.504199577038</v>
       </c>
       <c r="D7">
-        <v>1505.898017193194</v>
+        <v>1511.350199577038</v>
       </c>
       <c r="E7">
-        <v>-709.7449999999999</v>
+        <v>-694.8539999999999</v>
       </c>
       <c r="F7">
-        <v>74.455</v>
+        <v>89.346</v>
       </c>
       <c r="G7">
         <v>92.5</v>
@@ -1855,28 +1855,28 @@
         <v>188.525</v>
       </c>
       <c r="M7">
-        <v>4.187097293608977</v>
+        <v>5.024516752330772</v>
       </c>
       <c r="N7">
-        <v>184.337902706391</v>
+        <v>183.5004832476692</v>
       </c>
       <c r="O7">
-        <v>46.08447567659775</v>
+        <v>45.8751208119173</v>
       </c>
       <c r="P7">
-        <v>138.2534270297932</v>
+        <v>137.6253624357519</v>
       </c>
       <c r="Q7">
-        <v>181.3534270297933</v>
+        <v>180.7253624357519</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08188304039924819</v>
+        <v>0.08217458125892432</v>
       </c>
       <c r="T7">
-        <v>0.7033256187091244</v>
+        <v>0.7090082927089287</v>
       </c>
       <c r="U7">
         <v>0.0562366166625341</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>45.02522553936285</v>
+        <v>37.52102128280237</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.0797747541332029</v>
+        <v>0.07965174676227497</v>
       </c>
       <c r="C8">
-        <v>1514.504199577038</v>
+        <v>1505.10500524092</v>
       </c>
       <c r="D8">
-        <v>1511.350199577038</v>
+        <v>1516.84200524092</v>
       </c>
       <c r="E8">
-        <v>-694.8539999999999</v>
+        <v>-679.963</v>
       </c>
       <c r="F8">
-        <v>89.34599999999999</v>
+        <v>104.237</v>
       </c>
       <c r="G8">
         <v>92.5</v>
@@ -1937,28 +1937,28 @@
         <v>188.525</v>
       </c>
       <c r="M8">
-        <v>5.024516752330771</v>
+        <v>5.861936211052566</v>
       </c>
       <c r="N8">
-        <v>183.5004832476692</v>
+        <v>182.6630637889474</v>
       </c>
       <c r="O8">
-        <v>45.8751208119173</v>
+        <v>45.66576594723685</v>
       </c>
       <c r="P8">
-        <v>137.6253624357519</v>
+        <v>136.9972978417105</v>
       </c>
       <c r="Q8">
-        <v>180.7253624357519</v>
+        <v>180.0972978417106</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08217458125892432</v>
+        <v>0.08247239181450745</v>
       </c>
       <c r="T8">
-        <v>0.7090082927089287</v>
+        <v>0.7148131747517397</v>
       </c>
       <c r="U8">
         <v>0.0562366166625341</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>37.52102128280238</v>
+        <v>32.16087538525919</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07965174676227496</v>
+        <v>0.07952873939134704</v>
       </c>
       <c r="C9">
-        <v>1505.105005240921</v>
+        <v>1495.745867698419</v>
       </c>
       <c r="D9">
-        <v>1516.842005240921</v>
+        <v>1522.373867698419</v>
       </c>
       <c r="E9">
-        <v>-679.963</v>
+        <v>-665.0719999999999</v>
       </c>
       <c r="F9">
-        <v>104.237</v>
+        <v>119.128</v>
       </c>
       <c r="G9">
         <v>92.5</v>
@@ -2019,28 +2019,28 @@
         <v>188.525</v>
       </c>
       <c r="M9">
-        <v>5.861936211052567</v>
+        <v>6.699355669774362</v>
       </c>
       <c r="N9">
-        <v>182.6630637889474</v>
+        <v>181.8256443302256</v>
       </c>
       <c r="O9">
-        <v>45.66576594723685</v>
+        <v>45.45641108255641</v>
       </c>
       <c r="P9">
-        <v>136.9972978417105</v>
+        <v>136.3692332476692</v>
       </c>
       <c r="Q9">
-        <v>180.0972978417106</v>
+        <v>179.4692332476693</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08247239181450745</v>
+        <v>0.08277667651260326</v>
       </c>
       <c r="T9">
-        <v>0.7148131747517397</v>
+        <v>0.7207442498824378</v>
       </c>
       <c r="U9">
         <v>0.0562366166625341</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>32.16087538525917</v>
+        <v>28.14076596210179</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07952873939134704</v>
+        <v>0.07940573202041912</v>
       </c>
       <c r="C10">
-        <v>1495.745867698419</v>
+        <v>1486.427226810286</v>
       </c>
       <c r="D10">
-        <v>1522.373867698419</v>
+        <v>1527.946226810286</v>
       </c>
       <c r="E10">
-        <v>-665.0719999999999</v>
+        <v>-650.1809999999999</v>
       </c>
       <c r="F10">
-        <v>119.128</v>
+        <v>134.019</v>
       </c>
       <c r="G10">
         <v>92.5</v>
@@ -2101,28 +2101,28 @@
         <v>188.525</v>
       </c>
       <c r="M10">
-        <v>6.699355669774362</v>
+        <v>7.536775128496156</v>
       </c>
       <c r="N10">
-        <v>181.8256443302256</v>
+        <v>180.9882248715038</v>
       </c>
       <c r="O10">
-        <v>45.45641108255641</v>
+        <v>45.24705621787596</v>
       </c>
       <c r="P10">
-        <v>136.3692332476692</v>
+        <v>135.7411686536279</v>
       </c>
       <c r="Q10">
-        <v>179.4692332476693</v>
+        <v>178.8411686536279</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08277667651260326</v>
+        <v>0.08308764878648139</v>
       </c>
       <c r="T10">
-        <v>0.7207442498824378</v>
+        <v>0.7268056783127117</v>
       </c>
       <c r="U10">
         <v>0.0562366166625341</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>28.14076596210179</v>
+        <v>25.01401418853493</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07940573202041912</v>
+        <v>0.07928272464949121</v>
       </c>
       <c r="C11">
-        <v>1486.427226810286</v>
+        <v>1477.149528901041</v>
       </c>
       <c r="D11">
-        <v>1527.946226810286</v>
+        <v>1533.559528901041</v>
       </c>
       <c r="E11">
-        <v>-650.1809999999999</v>
+        <v>-635.29</v>
       </c>
       <c r="F11">
-        <v>134.019</v>
+        <v>148.91</v>
       </c>
       <c r="G11">
         <v>92.5</v>
@@ -2183,28 +2183,28 @@
         <v>188.525</v>
       </c>
       <c r="M11">
-        <v>7.536775128496156</v>
+        <v>8.374194587217952</v>
       </c>
       <c r="N11">
-        <v>180.9882248715038</v>
+        <v>180.150805412782</v>
       </c>
       <c r="O11">
-        <v>45.24705621787596</v>
+        <v>45.03770135319551</v>
       </c>
       <c r="P11">
-        <v>135.7411686536279</v>
+        <v>135.1131040595865</v>
       </c>
       <c r="Q11">
-        <v>178.8411686536279</v>
+        <v>178.2131040595866</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08308764878648139</v>
+        <v>0.08340553155533462</v>
       </c>
       <c r="T11">
-        <v>0.7268056783127117</v>
+        <v>0.7330018051525472</v>
       </c>
       <c r="U11">
         <v>0.0562366166625341</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>25.01401418853493</v>
+        <v>22.51261276968143</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07928272464949121</v>
+        <v>0.07915971727856329</v>
       </c>
       <c r="C12">
-        <v>1477.149528901041</v>
+        <v>1467.913226878137</v>
       </c>
       <c r="D12">
-        <v>1533.559528901041</v>
+        <v>1539.214226878137</v>
       </c>
       <c r="E12">
-        <v>-635.29</v>
+        <v>-620.3989999999999</v>
       </c>
       <c r="F12">
-        <v>148.91</v>
+        <v>163.801</v>
       </c>
       <c r="G12">
         <v>92.5</v>
@@ -2265,28 +2265,28 @@
         <v>188.525</v>
       </c>
       <c r="M12">
-        <v>8.374194587217954</v>
+        <v>9.211614045939747</v>
       </c>
       <c r="N12">
-        <v>180.150805412782</v>
+        <v>179.3133859540602</v>
       </c>
       <c r="O12">
-        <v>45.03770135319551</v>
+        <v>44.82834648851506</v>
       </c>
       <c r="P12">
-        <v>135.1131040595865</v>
+        <v>134.4850394655452</v>
       </c>
       <c r="Q12">
-        <v>178.2131040595866</v>
+        <v>177.5850394655452</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08340553155533462</v>
+        <v>0.08373055775719576</v>
       </c>
       <c r="T12">
-        <v>0.7330018051525472</v>
+        <v>0.7393371707977725</v>
       </c>
       <c r="U12">
         <v>0.0562366166625341</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>22.51261276968143</v>
+        <v>20.4660116088013</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07915971727856329</v>
+        <v>0.07903670990763538</v>
       </c>
       <c r="C13">
-        <v>1467.913226878137</v>
+        <v>1458.718780353775</v>
       </c>
       <c r="D13">
-        <v>1539.214226878137</v>
+        <v>1544.910780353775</v>
       </c>
       <c r="E13">
-        <v>-620.3989999999999</v>
+        <v>-605.5079999999999</v>
       </c>
       <c r="F13">
-        <v>163.801</v>
+        <v>178.692</v>
       </c>
       <c r="G13">
         <v>92.5</v>
@@ -2347,28 +2347,28 @@
         <v>188.525</v>
       </c>
       <c r="M13">
-        <v>9.211614045939747</v>
+        <v>10.04903350466154</v>
       </c>
       <c r="N13">
-        <v>179.3133859540602</v>
+        <v>178.4759664953384</v>
       </c>
       <c r="O13">
-        <v>44.82834648851506</v>
+        <v>44.61899162383461</v>
       </c>
       <c r="P13">
-        <v>134.4850394655452</v>
+        <v>133.8569748715038</v>
       </c>
       <c r="Q13">
-        <v>177.5850394655452</v>
+        <v>176.9569748715039</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08373055775719576</v>
+        <v>0.08406297091819012</v>
       </c>
       <c r="T13">
-        <v>0.7393371707977725</v>
+        <v>0.7458165220258436</v>
       </c>
       <c r="U13">
         <v>0.0562366166625341</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.4660116088013</v>
+        <v>18.76051064140119</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07903670990763538</v>
+        <v>0.07891370253670746</v>
       </c>
       <c r="C14">
-        <v>1458.718780353775</v>
+        <v>1449.566655769439</v>
       </c>
       <c r="D14">
-        <v>1544.910780353775</v>
+        <v>1550.649655769439</v>
       </c>
       <c r="E14">
-        <v>-605.5079999999999</v>
+        <v>-590.617</v>
       </c>
       <c r="F14">
-        <v>178.692</v>
+        <v>193.583</v>
       </c>
       <c r="G14">
         <v>92.5</v>
@@ -2429,28 +2429,28 @@
         <v>188.525</v>
       </c>
       <c r="M14">
-        <v>10.04903350466154</v>
+        <v>10.88645296338334</v>
       </c>
       <c r="N14">
-        <v>178.4759664953384</v>
+        <v>177.6385470366166</v>
       </c>
       <c r="O14">
-        <v>44.61899162383461</v>
+        <v>44.40963675915416</v>
       </c>
       <c r="P14">
-        <v>133.8569748715038</v>
+        <v>133.2289102774625</v>
       </c>
       <c r="Q14">
-        <v>176.9569748715039</v>
+        <v>176.3289102774625</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08406297091819012</v>
+        <v>0.08440302576104641</v>
       </c>
       <c r="T14">
-        <v>0.7458165220258436</v>
+        <v>0.7524448238568588</v>
       </c>
       <c r="U14">
         <v>0.0562366166625341</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.76051064140119</v>
+        <v>17.31739443821649</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07891370253670746</v>
+        <v>0.07879069516577954</v>
       </c>
       <c r="C15">
-        <v>1449.566655769439</v>
+        <v>1440.457326523207</v>
       </c>
       <c r="D15">
-        <v>1550.649655769439</v>
+        <v>1556.431326523207</v>
       </c>
       <c r="E15">
-        <v>-590.617</v>
+        <v>-575.7259999999999</v>
       </c>
       <c r="F15">
-        <v>193.583</v>
+        <v>208.474</v>
       </c>
       <c r="G15">
         <v>92.5</v>
@@ -2511,28 +2511,28 @@
         <v>188.525</v>
       </c>
       <c r="M15">
-        <v>10.88645296338334</v>
+        <v>11.72387242210513</v>
       </c>
       <c r="N15">
-        <v>177.6385470366166</v>
+        <v>176.8011275778948</v>
       </c>
       <c r="O15">
-        <v>44.40963675915416</v>
+        <v>44.20028189447371</v>
       </c>
       <c r="P15">
-        <v>133.2289102774625</v>
+        <v>132.6008456834211</v>
       </c>
       <c r="Q15">
-        <v>176.3289102774625</v>
+        <v>175.7008456834212</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08440302576104641</v>
+        <v>0.08475098885606215</v>
       </c>
       <c r="T15">
-        <v>0.7524448238568588</v>
+        <v>0.7592272722420839</v>
       </c>
       <c r="U15">
         <v>0.0562366166625341</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.31739443821649</v>
+        <v>16.08043769262959</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07879069516577954</v>
+        <v>0.07866768779485162</v>
       </c>
       <c r="C16">
-        <v>1440.457326523207</v>
+        <v>1431.391273099932</v>
       </c>
       <c r="D16">
-        <v>1556.431326523207</v>
+        <v>1562.256273099932</v>
       </c>
       <c r="E16">
-        <v>-575.7259999999999</v>
+        <v>-560.8349999999999</v>
       </c>
       <c r="F16">
-        <v>208.474</v>
+        <v>223.365</v>
       </c>
       <c r="G16">
         <v>92.5</v>
@@ -2593,28 +2593,28 @@
         <v>188.525</v>
       </c>
       <c r="M16">
-        <v>11.72387242210513</v>
+        <v>12.56129188082693</v>
       </c>
       <c r="N16">
-        <v>176.8011275778948</v>
+        <v>175.963708119173</v>
       </c>
       <c r="O16">
-        <v>44.20028189447371</v>
+        <v>43.99092702979326</v>
       </c>
       <c r="P16">
-        <v>132.6008456834211</v>
+        <v>131.9727810893798</v>
       </c>
       <c r="Q16">
-        <v>175.7008456834212</v>
+        <v>175.0727810893798</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08475098885606215</v>
+        <v>0.08510713931801944</v>
       </c>
       <c r="T16">
-        <v>0.7592272722420839</v>
+        <v>0.7661693076481376</v>
       </c>
       <c r="U16">
         <v>0.0562366166625341</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.08043769262959</v>
+        <v>15.00840851312095</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07866768779485162</v>
+        <v>0.07854468042392368</v>
       </c>
       <c r="C17">
-        <v>1431.391273099932</v>
+        <v>1422.368983204346</v>
       </c>
       <c r="D17">
-        <v>1562.256273099932</v>
+        <v>1568.124983204346</v>
       </c>
       <c r="E17">
-        <v>-560.8349999999999</v>
+        <v>-545.944</v>
       </c>
       <c r="F17">
-        <v>223.365</v>
+        <v>238.256</v>
       </c>
       <c r="G17">
         <v>92.5</v>
@@ -2675,28 +2675,28 @@
         <v>188.525</v>
       </c>
       <c r="M17">
-        <v>12.56129188082693</v>
+        <v>13.39871133954872</v>
       </c>
       <c r="N17">
-        <v>175.963708119173</v>
+        <v>175.1262886604513</v>
       </c>
       <c r="O17">
-        <v>43.99092702979326</v>
+        <v>43.78157216511281</v>
       </c>
       <c r="P17">
-        <v>131.9727810893798</v>
+        <v>131.3447164953384</v>
       </c>
       <c r="Q17">
-        <v>175.0727810893798</v>
+        <v>174.4447164953385</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08510713931801944</v>
+        <v>0.08547176955288047</v>
       </c>
       <c r="T17">
-        <v>0.7661693076481376</v>
+        <v>0.7732766296114784</v>
       </c>
       <c r="U17">
         <v>0.0562366166625341</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>15.00840851312095</v>
+        <v>14.07038298105089</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07854468042392368</v>
+        <v>0.07842167305299577</v>
       </c>
       <c r="C18">
-        <v>1422.368983204346</v>
+        <v>1413.390951897184</v>
       </c>
       <c r="D18">
-        <v>1568.124983204346</v>
+        <v>1574.037951897184</v>
       </c>
       <c r="E18">
-        <v>-545.944</v>
+        <v>-531.0529999999999</v>
       </c>
       <c r="F18">
-        <v>238.256</v>
+        <v>253.147</v>
       </c>
       <c r="G18">
         <v>92.5</v>
@@ -2757,28 +2757,28 @@
         <v>188.525</v>
       </c>
       <c r="M18">
-        <v>13.39871133954872</v>
+        <v>14.23613079827052</v>
       </c>
       <c r="N18">
-        <v>175.1262886604513</v>
+        <v>174.2888692017295</v>
       </c>
       <c r="O18">
-        <v>43.78157216511281</v>
+        <v>43.57221730043236</v>
       </c>
       <c r="P18">
-        <v>131.3447164953384</v>
+        <v>130.7166519012971</v>
       </c>
       <c r="Q18">
-        <v>174.4447164953385</v>
+        <v>173.8166519012971</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08547176955288047</v>
+        <v>0.08584518605846106</v>
       </c>
       <c r="T18">
-        <v>0.7732766296114784</v>
+        <v>0.7805552123450203</v>
       </c>
       <c r="U18">
         <v>0.0562366166625341</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.07038298105089</v>
+        <v>13.24271339393025</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07842167305299577</v>
+        <v>0.07850116568206784</v>
       </c>
       <c r="C19">
-        <v>1413.390951897184</v>
+        <v>1394.673653585006</v>
       </c>
       <c r="D19">
-        <v>1574.037951897184</v>
+        <v>1570.211653585006</v>
       </c>
       <c r="E19">
-        <v>-531.0529999999999</v>
+        <v>-516.1619999999999</v>
       </c>
       <c r="F19">
-        <v>253.147</v>
+        <v>268.038</v>
       </c>
       <c r="G19">
         <v>92.5</v>
@@ -2839,45 +2839,45 @@
         <v>188.525</v>
       </c>
       <c r="M19">
-        <v>14.23613079827052</v>
+        <v>15.47560725699231</v>
       </c>
       <c r="N19">
-        <v>174.2888692017295</v>
+        <v>173.0493927430077</v>
       </c>
       <c r="O19">
-        <v>43.57221730043236</v>
+        <v>43.26234818575192</v>
       </c>
       <c r="P19">
-        <v>130.7166519012971</v>
+        <v>129.7870445572557</v>
       </c>
       <c r="Q19">
-        <v>173.8166519012971</v>
+        <v>172.8870445572558</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08584518605846106</v>
+        <v>0.08622771028368993</v>
       </c>
       <c r="T19">
-        <v>0.7805552123450203</v>
+        <v>0.7880113214866972</v>
       </c>
       <c r="U19">
-        <v>0.0562366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.04217746249690058</v>
+        <v>0.04330246249690057</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>13.24271339393025</v>
+        <v>12.18207446527303</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07850116568206786</v>
+        <v>0.07838940831113994</v>
       </c>
       <c r="C20">
-        <v>1394.673653585006</v>
+        <v>1385.167308762837</v>
       </c>
       <c r="D20">
-        <v>1570.211653585006</v>
+        <v>1575.596308762837</v>
       </c>
       <c r="E20">
-        <v>-516.162</v>
+        <v>-501.271</v>
       </c>
       <c r="F20">
-        <v>268.038</v>
+        <v>282.929</v>
       </c>
       <c r="G20">
         <v>92.5</v>
@@ -2921,28 +2921,28 @@
         <v>188.525</v>
       </c>
       <c r="M20">
-        <v>15.47560725699231</v>
+        <v>16.33536321571411</v>
       </c>
       <c r="N20">
-        <v>173.0493927430077</v>
+        <v>172.1896367842859</v>
       </c>
       <c r="O20">
-        <v>43.26234818575192</v>
+        <v>43.04740919607147</v>
       </c>
       <c r="P20">
-        <v>129.7870445572557</v>
+        <v>129.1422275882144</v>
       </c>
       <c r="Q20">
-        <v>172.8870445572558</v>
+        <v>172.2422275882144</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08622771028368993</v>
+        <v>0.08661967955151706</v>
       </c>
       <c r="T20">
-        <v>0.7880113214866972</v>
+        <v>0.7956515320886626</v>
       </c>
       <c r="U20">
         <v>0.05773661666253409</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>12.18207446527303</v>
+        <v>11.54091265131129</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07838940831113994</v>
+        <v>0.07827765094021201</v>
       </c>
       <c r="C21">
-        <v>1385.167308762837</v>
+        <v>1375.69802172586</v>
       </c>
       <c r="D21">
-        <v>1575.596308762837</v>
+        <v>1581.01802172586</v>
       </c>
       <c r="E21">
-        <v>-501.271</v>
+        <v>-486.3799999999999</v>
       </c>
       <c r="F21">
-        <v>282.929</v>
+        <v>297.82</v>
       </c>
       <c r="G21">
         <v>92.5</v>
@@ -3003,28 +3003,28 @@
         <v>188.525</v>
       </c>
       <c r="M21">
-        <v>16.33536321571411</v>
+        <v>17.1951191744359</v>
       </c>
       <c r="N21">
-        <v>172.1896367842859</v>
+        <v>171.3298808255641</v>
       </c>
       <c r="O21">
-        <v>43.04740919607147</v>
+        <v>42.83247020639102</v>
       </c>
       <c r="P21">
-        <v>129.1422275882144</v>
+        <v>128.4974106191731</v>
       </c>
       <c r="Q21">
-        <v>172.2422275882144</v>
+        <v>171.5974106191731</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08661967955151706</v>
+        <v>0.08702144805103987</v>
       </c>
       <c r="T21">
-        <v>0.7956515320886626</v>
+        <v>0.8034827479556769</v>
       </c>
       <c r="U21">
         <v>0.05773661666253409</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.54091265131129</v>
+        <v>10.96386701874572</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07827765094021201</v>
+        <v>0.07816589356928409</v>
       </c>
       <c r="C22">
-        <v>1375.69802172586</v>
+        <v>1366.266176348596</v>
       </c>
       <c r="D22">
-        <v>1581.01802172586</v>
+        <v>1586.477176348596</v>
       </c>
       <c r="E22">
-        <v>-486.3799999999999</v>
+        <v>-471.4889999999999</v>
       </c>
       <c r="F22">
-        <v>297.82</v>
+        <v>312.711</v>
       </c>
       <c r="G22">
         <v>92.5</v>
@@ -3085,28 +3085,28 @@
         <v>188.525</v>
       </c>
       <c r="M22">
-        <v>17.1951191744359</v>
+        <v>18.0548751331577</v>
       </c>
       <c r="N22">
-        <v>171.3298808255641</v>
+        <v>170.4701248668423</v>
       </c>
       <c r="O22">
-        <v>42.83247020639102</v>
+        <v>42.61753121671057</v>
       </c>
       <c r="P22">
-        <v>128.4974106191731</v>
+        <v>127.8525936501317</v>
       </c>
       <c r="Q22">
-        <v>171.5974106191731</v>
+        <v>170.9525936501317</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08702144805103987</v>
+        <v>0.08743338790498097</v>
       </c>
       <c r="T22">
-        <v>0.8034827479556769</v>
+        <v>0.8115122224522359</v>
       </c>
       <c r="U22">
         <v>0.05773661666253409</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.96386701874572</v>
+        <v>10.44177811309116</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07816589356928409</v>
+        <v>0.07805413619835616</v>
       </c>
       <c r="C23">
-        <v>1366.266176348596</v>
+        <v>1356.872161825917</v>
       </c>
       <c r="D23">
-        <v>1586.477176348596</v>
+        <v>1591.974161825917</v>
       </c>
       <c r="E23">
-        <v>-471.489</v>
+        <v>-456.598</v>
       </c>
       <c r="F23">
-        <v>312.711</v>
+        <v>327.602</v>
       </c>
       <c r="G23">
         <v>92.5</v>
@@ -3167,28 +3167,28 @@
         <v>188.525</v>
       </c>
       <c r="M23">
-        <v>18.0548751331577</v>
+        <v>18.91463109187949</v>
       </c>
       <c r="N23">
-        <v>170.4701248668423</v>
+        <v>169.6103689081205</v>
       </c>
       <c r="O23">
-        <v>42.61753121671057</v>
+        <v>42.40259222703012</v>
       </c>
       <c r="P23">
-        <v>127.8525936501317</v>
+        <v>127.2077766810904</v>
       </c>
       <c r="Q23">
-        <v>170.9525936501317</v>
+        <v>170.3077766810904</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08743338790498097</v>
+        <v>0.08785589031927954</v>
       </c>
       <c r="T23">
-        <v>0.8115122224522359</v>
+        <v>0.8197475809102451</v>
       </c>
       <c r="U23">
         <v>0.05773661666253409</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.44177811309116</v>
+        <v>9.967151835223385</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07805413619835616</v>
+        <v>0.07823562882742824</v>
       </c>
       <c r="C24">
-        <v>1356.872161825917</v>
+        <v>1333.073316148503</v>
       </c>
       <c r="D24">
-        <v>1591.974161825917</v>
+        <v>1583.066316148503</v>
       </c>
       <c r="E24">
-        <v>-456.598</v>
+        <v>-441.7069999999999</v>
       </c>
       <c r="F24">
-        <v>327.602</v>
+        <v>342.493</v>
       </c>
       <c r="G24">
         <v>92.5</v>
@@ -3249,45 +3249,45 @@
         <v>188.525</v>
       </c>
       <c r="M24">
-        <v>18.91463109187949</v>
+        <v>20.35662515060129</v>
       </c>
       <c r="N24">
-        <v>169.6103689081205</v>
+        <v>168.1683748493987</v>
       </c>
       <c r="O24">
-        <v>42.40259222703012</v>
+        <v>42.04209371234967</v>
       </c>
       <c r="P24">
-        <v>127.2077766810904</v>
+        <v>126.126281137049</v>
       </c>
       <c r="Q24">
-        <v>170.3077766810904</v>
+        <v>169.226281137049</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08785589031927954</v>
+        <v>0.08828936682226118</v>
       </c>
       <c r="T24">
-        <v>0.8197475809102451</v>
+        <v>0.8281968447827482</v>
       </c>
       <c r="U24">
-        <v>0.05773661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V24">
         <v>0.25</v>
       </c>
       <c r="W24">
-        <v>0.04330246249690057</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>9.967151835223385</v>
+        <v>9.261112714178527</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07823562882742824</v>
+        <v>0.07813662145650033</v>
       </c>
       <c r="C25">
-        <v>1333.073316148503</v>
+        <v>1323.029304699154</v>
       </c>
       <c r="D25">
-        <v>1583.066316148503</v>
+        <v>1587.913304699154</v>
       </c>
       <c r="E25">
-        <v>-441.7069999999999</v>
+        <v>-426.8159999999999</v>
       </c>
       <c r="F25">
-        <v>342.493</v>
+        <v>357.384</v>
       </c>
       <c r="G25">
         <v>92.5</v>
@@ -3331,28 +3331,28 @@
         <v>188.525</v>
       </c>
       <c r="M25">
-        <v>20.35662515060129</v>
+        <v>21.24169580932309</v>
       </c>
       <c r="N25">
-        <v>168.1683748493987</v>
+        <v>167.2833041906769</v>
       </c>
       <c r="O25">
-        <v>42.04209371234967</v>
+        <v>41.82082604766922</v>
       </c>
       <c r="P25">
-        <v>126.126281137049</v>
+        <v>125.4624781430077</v>
       </c>
       <c r="Q25">
-        <v>169.226281137049</v>
+        <v>168.5624781430077</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08828936682226118</v>
+        <v>0.08873425060163709</v>
       </c>
       <c r="T25">
-        <v>0.8281968447827482</v>
+        <v>0.8368684577045277</v>
       </c>
       <c r="U25">
         <v>0.05943661666253409</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.261112714178527</v>
+        <v>8.875233017754422</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07813662145650033</v>
+        <v>0.0780376140855724</v>
       </c>
       <c r="C26">
-        <v>1323.029304699154</v>
+        <v>1313.015065154888</v>
       </c>
       <c r="D26">
-        <v>1587.913304699154</v>
+        <v>1592.790065154888</v>
       </c>
       <c r="E26">
-        <v>-426.816</v>
+        <v>-411.925</v>
       </c>
       <c r="F26">
-        <v>357.384</v>
+        <v>372.275</v>
       </c>
       <c r="G26">
         <v>92.5</v>
@@ -3413,28 +3413,28 @@
         <v>188.525</v>
       </c>
       <c r="M26">
-        <v>21.24169580932308</v>
+        <v>22.12676646804488</v>
       </c>
       <c r="N26">
-        <v>167.2833041906769</v>
+        <v>166.3982335319551</v>
       </c>
       <c r="O26">
-        <v>41.82082604766922</v>
+        <v>41.59955838298877</v>
       </c>
       <c r="P26">
-        <v>125.4624781430077</v>
+        <v>124.7986751489663</v>
       </c>
       <c r="Q26">
-        <v>168.5624781430077</v>
+        <v>167.8986751489663</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08873425060163709</v>
+        <v>0.08919099794846301</v>
       </c>
       <c r="T26">
-        <v>0.8368684577045277</v>
+        <v>0.8457713136375545</v>
       </c>
       <c r="U26">
         <v>0.05943661666253409</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.875233017754422</v>
+        <v>8.520223697044246</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0780376140855724</v>
+        <v>0.07793860671464449</v>
       </c>
       <c r="C27">
-        <v>1313.015065154888</v>
+        <v>1303.030872664973</v>
       </c>
       <c r="D27">
-        <v>1592.790065154888</v>
+        <v>1597.696872664973</v>
       </c>
       <c r="E27">
-        <v>-411.925</v>
+        <v>-397.0339999999999</v>
       </c>
       <c r="F27">
-        <v>372.275</v>
+        <v>387.166</v>
       </c>
       <c r="G27">
         <v>92.5</v>
@@ -3495,28 +3495,28 @@
         <v>188.525</v>
       </c>
       <c r="M27">
-        <v>22.12676646804488</v>
+        <v>23.01183712676668</v>
       </c>
       <c r="N27">
-        <v>166.3982335319551</v>
+        <v>165.5131628732333</v>
       </c>
       <c r="O27">
-        <v>41.59955838298877</v>
+        <v>41.37829071830833</v>
       </c>
       <c r="P27">
-        <v>124.7986751489663</v>
+        <v>124.134872154925</v>
       </c>
       <c r="Q27">
-        <v>167.8986751489663</v>
+        <v>167.234872154925</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08919099794846301</v>
+        <v>0.08966008981817614</v>
       </c>
       <c r="T27">
-        <v>0.8457713136375545</v>
+        <v>0.8549147872985011</v>
       </c>
       <c r="U27">
         <v>0.05943661666253409</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.520223697044246</v>
+        <v>8.192522785619467</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07793860671464449</v>
+        <v>0.07783959934371656</v>
       </c>
       <c r="C28">
-        <v>1303.030872664973</v>
+        <v>1293.077005779696</v>
       </c>
       <c r="D28">
-        <v>1597.696872664973</v>
+        <v>1602.634005779697</v>
       </c>
       <c r="E28">
-        <v>-397.0339999999999</v>
+        <v>-382.1429999999999</v>
       </c>
       <c r="F28">
-        <v>387.166</v>
+        <v>402.057</v>
       </c>
       <c r="G28">
         <v>92.5</v>
@@ -3577,28 +3577,28 @@
         <v>188.525</v>
       </c>
       <c r="M28">
-        <v>23.01183712676668</v>
+        <v>23.89690778548847</v>
       </c>
       <c r="N28">
-        <v>165.5131628732333</v>
+        <v>164.6280922145115</v>
       </c>
       <c r="O28">
-        <v>41.37829071830833</v>
+        <v>41.15702305362787</v>
       </c>
       <c r="P28">
-        <v>124.134872154925</v>
+        <v>123.4710691608836</v>
       </c>
       <c r="Q28">
-        <v>167.234872154925</v>
+        <v>166.5710691608836</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08966008981817614</v>
+        <v>0.09014203351993619</v>
       </c>
       <c r="T28">
-        <v>0.8549147872985011</v>
+        <v>0.8643087670871449</v>
       </c>
       <c r="U28">
         <v>0.05943661666253409</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.192522785619467</v>
+        <v>7.889096015781707</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07783959934371656</v>
+        <v>0.07774059197278864</v>
       </c>
       <c r="C29">
-        <v>1293.077005779696</v>
+        <v>1283.153746503072</v>
       </c>
       <c r="D29">
-        <v>1602.634005779697</v>
+        <v>1607.601746503072</v>
       </c>
       <c r="E29">
-        <v>-382.1429999999999</v>
+        <v>-367.2519999999999</v>
       </c>
       <c r="F29">
-        <v>402.057</v>
+        <v>416.948</v>
       </c>
       <c r="G29">
         <v>92.5</v>
@@ -3659,28 +3659,28 @@
         <v>188.525</v>
       </c>
       <c r="M29">
-        <v>23.89690778548847</v>
+        <v>24.78197844421027</v>
       </c>
       <c r="N29">
-        <v>164.6280922145115</v>
+        <v>163.7430215557897</v>
       </c>
       <c r="O29">
-        <v>41.15702305362787</v>
+        <v>40.93575538894743</v>
       </c>
       <c r="P29">
-        <v>123.4710691608836</v>
+        <v>122.8072661668423</v>
       </c>
       <c r="Q29">
-        <v>166.5710691608836</v>
+        <v>165.9072661668423</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09014203351993619</v>
+        <v>0.09063736454674512</v>
       </c>
       <c r="T29">
-        <v>0.8643087670871449</v>
+        <v>0.8739636907588064</v>
       </c>
       <c r="U29">
         <v>0.05943661666253409</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.889096015781707</v>
+        <v>7.607342586646647</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07774059197278864</v>
+        <v>0.07781558460186072</v>
       </c>
       <c r="C30">
-        <v>1283.153746503072</v>
+        <v>1264.497134131148</v>
       </c>
       <c r="D30">
-        <v>1607.601746503072</v>
+        <v>1603.836134131148</v>
       </c>
       <c r="E30">
-        <v>-367.2519999999999</v>
+        <v>-352.3609999999999</v>
       </c>
       <c r="F30">
-        <v>416.948</v>
+        <v>431.839</v>
       </c>
       <c r="G30">
         <v>92.5</v>
@@ -3741,45 +3741,45 @@
         <v>188.525</v>
       </c>
       <c r="M30">
-        <v>24.78197844421027</v>
+        <v>26.01252030293206</v>
       </c>
       <c r="N30">
-        <v>163.7430215557897</v>
+        <v>162.5124796970679</v>
       </c>
       <c r="O30">
-        <v>40.93575538894743</v>
+        <v>40.62811992426698</v>
       </c>
       <c r="P30">
-        <v>122.8072661668423</v>
+        <v>121.8843597728009</v>
       </c>
       <c r="Q30">
-        <v>165.9072661668423</v>
+        <v>164.984359772801</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09063736454674512</v>
+        <v>0.09114664856022472</v>
       </c>
       <c r="T30">
-        <v>0.8739636907588064</v>
+        <v>0.8838905841113598</v>
       </c>
       <c r="U30">
-        <v>0.05943661666253409</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.04457746249690057</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y30">
-        <v>7.607342586646647</v>
+        <v>7.247471517734865</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07781558460186072</v>
+        <v>0.0777225772309328</v>
       </c>
       <c r="C31">
-        <v>1264.497134131148</v>
+        <v>1254.278958043692</v>
       </c>
       <c r="D31">
-        <v>1603.836134131148</v>
+        <v>1608.508958043692</v>
       </c>
       <c r="E31">
-        <v>-352.361</v>
+        <v>-337.47</v>
       </c>
       <c r="F31">
-        <v>431.8389999999999</v>
+        <v>446.73</v>
       </c>
       <c r="G31">
         <v>92.5</v>
@@ -3823,28 +3823,28 @@
         <v>188.525</v>
       </c>
       <c r="M31">
-        <v>26.01252030293206</v>
+        <v>26.90950376165386</v>
       </c>
       <c r="N31">
-        <v>162.5124796970679</v>
+        <v>161.6154962383461</v>
       </c>
       <c r="O31">
-        <v>40.62811992426698</v>
+        <v>40.40387405958653</v>
       </c>
       <c r="P31">
-        <v>121.8843597728009</v>
+        <v>121.2116221787596</v>
       </c>
       <c r="Q31">
-        <v>164.984359772801</v>
+        <v>164.3116221787596</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09114664856022472</v>
+        <v>0.09167048354551804</v>
       </c>
       <c r="T31">
-        <v>0.8838905841113598</v>
+        <v>0.8941011029882719</v>
       </c>
       <c r="U31">
         <v>0.0602366166625341</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.247471517734865</v>
+        <v>7.005889133810368</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0777225772309328</v>
+        <v>0.07762956986000487</v>
       </c>
       <c r="C32">
-        <v>1254.278958043692</v>
+        <v>1244.088090340788</v>
       </c>
       <c r="D32">
-        <v>1608.508958043692</v>
+        <v>1613.209090340788</v>
       </c>
       <c r="E32">
-        <v>-337.47</v>
+        <v>-322.579</v>
       </c>
       <c r="F32">
-        <v>446.73</v>
+        <v>461.621</v>
       </c>
       <c r="G32">
         <v>92.5</v>
@@ -3905,28 +3905,28 @@
         <v>188.525</v>
       </c>
       <c r="M32">
-        <v>26.90950376165386</v>
+        <v>27.80648722037565</v>
       </c>
       <c r="N32">
-        <v>161.6154962383461</v>
+        <v>160.7185127796243</v>
       </c>
       <c r="O32">
-        <v>40.40387405958653</v>
+        <v>40.17962819490608</v>
       </c>
       <c r="P32">
-        <v>121.2116221787596</v>
+        <v>120.5388845847182</v>
       </c>
       <c r="Q32">
-        <v>164.3116221787596</v>
+        <v>163.6388845847183</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09167048354551804</v>
+        <v>0.09220950215357349</v>
       </c>
       <c r="T32">
-        <v>0.8941011029882719</v>
+        <v>0.9046075789340801</v>
       </c>
       <c r="U32">
         <v>0.0602366166625341</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.005889133810368</v>
+        <v>6.779892710139066</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07762956986000487</v>
+        <v>0.07753656248907695</v>
       </c>
       <c r="C33">
-        <v>1244.088090340788</v>
+        <v>1233.924771112808</v>
       </c>
       <c r="D33">
-        <v>1613.209090340788</v>
+        <v>1617.936771112808</v>
       </c>
       <c r="E33">
-        <v>-322.579</v>
+        <v>-307.6879999999999</v>
       </c>
       <c r="F33">
-        <v>461.621</v>
+        <v>476.512</v>
       </c>
       <c r="G33">
         <v>92.5</v>
@@ -3987,28 +3987,28 @@
         <v>188.525</v>
       </c>
       <c r="M33">
-        <v>27.80648722037565</v>
+        <v>28.70347067909745</v>
       </c>
       <c r="N33">
-        <v>160.7185127796243</v>
+        <v>159.8215293209025</v>
       </c>
       <c r="O33">
-        <v>40.17962819490608</v>
+        <v>39.95538233022563</v>
       </c>
       <c r="P33">
-        <v>120.5388845847182</v>
+        <v>119.8661469906769</v>
       </c>
       <c r="Q33">
-        <v>163.6388845847183</v>
+        <v>162.9661469906769</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09220950215357349</v>
+        <v>0.09276437425010114</v>
       </c>
       <c r="T33">
-        <v>0.9046075789340801</v>
+        <v>0.9154230688782944</v>
       </c>
       <c r="U33">
         <v>0.0602366166625341</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.779892710139066</v>
+        <v>6.56802106294722</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07753656248907695</v>
+        <v>0.07744355511814904</v>
       </c>
       <c r="C34">
-        <v>1233.924771112808</v>
+        <v>1223.789243272839</v>
       </c>
       <c r="D34">
-        <v>1617.936771112808</v>
+        <v>1622.69224327284</v>
       </c>
       <c r="E34">
-        <v>-307.6879999999999</v>
+        <v>-292.7969999999999</v>
       </c>
       <c r="F34">
-        <v>476.512</v>
+        <v>491.403</v>
       </c>
       <c r="G34">
         <v>92.5</v>
@@ -4069,28 +4069,28 @@
         <v>188.525</v>
       </c>
       <c r="M34">
-        <v>28.70347067909745</v>
+        <v>29.60045413781924</v>
       </c>
       <c r="N34">
-        <v>159.8215293209025</v>
+        <v>158.9245458621807</v>
       </c>
       <c r="O34">
-        <v>39.95538233022563</v>
+        <v>39.73113646554518</v>
       </c>
       <c r="P34">
-        <v>119.8661469906769</v>
+        <v>119.1934093966356</v>
       </c>
       <c r="Q34">
-        <v>162.9661469906769</v>
+        <v>162.2934093966356</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09276437425010114</v>
+        <v>0.09333580969279381</v>
       </c>
       <c r="T34">
-        <v>0.9154230688782944</v>
+        <v>0.9265614092686046</v>
       </c>
       <c r="U34">
         <v>0.0602366166625341</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.56802106294722</v>
+        <v>6.368990121645789</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07744355511814904</v>
+        <v>0.07735054774722111</v>
       </c>
       <c r="C35">
-        <v>1223.789243272839</v>
+        <v>1213.681752598291</v>
       </c>
       <c r="D35">
-        <v>1622.69224327284</v>
+        <v>1627.475752598292</v>
       </c>
       <c r="E35">
-        <v>-292.7969999999999</v>
+        <v>-277.9059999999999</v>
       </c>
       <c r="F35">
-        <v>491.403</v>
+        <v>506.294</v>
       </c>
       <c r="G35">
         <v>92.5</v>
@@ -4151,28 +4151,28 @@
         <v>188.525</v>
       </c>
       <c r="M35">
-        <v>29.60045413781924</v>
+        <v>30.49743759654104</v>
       </c>
       <c r="N35">
-        <v>158.9245458621807</v>
+        <v>158.0275624034589</v>
       </c>
       <c r="O35">
-        <v>39.73113646554518</v>
+        <v>39.50689060086474</v>
       </c>
       <c r="P35">
-        <v>119.1934093966356</v>
+        <v>118.5206718025942</v>
       </c>
       <c r="Q35">
-        <v>162.2934093966356</v>
+        <v>161.6206718025942</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09333580969279381</v>
+        <v>0.09392456136102262</v>
       </c>
       <c r="T35">
-        <v>0.9265614092686046</v>
+        <v>0.9380372751252879</v>
       </c>
       <c r="U35">
         <v>0.0602366166625341</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.368990121645789</v>
+        <v>6.181666882773855</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07735054774722111</v>
+        <v>0.0775200403762932</v>
       </c>
       <c r="C36">
-        <v>1213.681752598291</v>
+        <v>1190.094510702423</v>
       </c>
       <c r="D36">
-        <v>1627.475752598292</v>
+        <v>1618.779510702423</v>
       </c>
       <c r="E36">
-        <v>-277.9059999999999</v>
+        <v>-263.0149999999999</v>
       </c>
       <c r="F36">
-        <v>506.294</v>
+        <v>521.1850000000001</v>
       </c>
       <c r="G36">
         <v>92.5</v>
@@ -4233,45 +4233,45 @@
         <v>188.525</v>
       </c>
       <c r="M36">
-        <v>30.49743759654104</v>
+        <v>31.91560605526284</v>
       </c>
       <c r="N36">
-        <v>158.0275624034589</v>
+        <v>156.6093939447371</v>
       </c>
       <c r="O36">
-        <v>39.50689060086474</v>
+        <v>39.15234848618429</v>
       </c>
       <c r="P36">
-        <v>118.5206718025942</v>
+        <v>117.4570454585529</v>
       </c>
       <c r="Q36">
-        <v>161.6206718025942</v>
+        <v>160.5570454585529</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09392456136102262</v>
+        <v>0.09453142846519694</v>
       </c>
       <c r="T36">
-        <v>0.9380372751252879</v>
+        <v>0.9498662445467921</v>
       </c>
       <c r="U36">
-        <v>0.0602366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V36">
         <v>0.25</v>
       </c>
       <c r="W36">
-        <v>0.04517746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>6.181666882773855</v>
+        <v>5.906984804661495</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.0775200403762932</v>
+        <v>0.07743453300536528</v>
       </c>
       <c r="C37">
-        <v>1190.094510702423</v>
+        <v>1179.579032226597</v>
       </c>
       <c r="D37">
-        <v>1618.779510702423</v>
+        <v>1623.155032226597</v>
       </c>
       <c r="E37">
-        <v>-263.0149999999999</v>
+        <v>-248.1239999999999</v>
       </c>
       <c r="F37">
-        <v>521.1850000000001</v>
+        <v>536.076</v>
       </c>
       <c r="G37">
         <v>92.5</v>
@@ -4315,28 +4315,28 @@
         <v>188.525</v>
       </c>
       <c r="M37">
-        <v>31.91560605526284</v>
+        <v>32.82748051398463</v>
       </c>
       <c r="N37">
-        <v>156.6093939447371</v>
+        <v>155.6975194860154</v>
       </c>
       <c r="O37">
-        <v>39.15234848618429</v>
+        <v>38.92437987150384</v>
       </c>
       <c r="P37">
-        <v>117.4570454585529</v>
+        <v>116.7731396145115</v>
       </c>
       <c r="Q37">
-        <v>160.5570454585529</v>
+        <v>159.8731396145115</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09453142846519694</v>
+        <v>0.09515726016637668</v>
       </c>
       <c r="T37">
-        <v>0.9498662445467921</v>
+        <v>0.9620648692627183</v>
       </c>
       <c r="U37">
         <v>0.0612366166625341</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.906984804661495</v>
+        <v>5.742901893420898</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07743453300536529</v>
+        <v>0.07734902563443735</v>
       </c>
       <c r="C38">
-        <v>1179.579032226596</v>
+        <v>1169.087271715712</v>
       </c>
       <c r="D38">
-        <v>1623.155032226596</v>
+        <v>1627.554271715712</v>
       </c>
       <c r="E38">
-        <v>-248.124</v>
+        <v>-233.2329999999999</v>
       </c>
       <c r="F38">
-        <v>536.0759999999999</v>
+        <v>550.967</v>
       </c>
       <c r="G38">
         <v>92.5</v>
@@ -4397,28 +4397,28 @@
         <v>188.525</v>
       </c>
       <c r="M38">
-        <v>32.82748051398463</v>
+        <v>33.73935497270642</v>
       </c>
       <c r="N38">
-        <v>155.6975194860154</v>
+        <v>154.7856450272936</v>
       </c>
       <c r="O38">
-        <v>38.92437987150384</v>
+        <v>38.69641125682339</v>
       </c>
       <c r="P38">
-        <v>116.7731396145115</v>
+        <v>116.0892337704702</v>
       </c>
       <c r="Q38">
-        <v>159.8731396145115</v>
+        <v>159.1892337704702</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09515726016637668</v>
+        <v>0.09580295954060976</v>
       </c>
       <c r="T38">
-        <v>0.9620648692627183</v>
+        <v>0.9746507519061343</v>
       </c>
       <c r="U38">
         <v>0.0612366166625341</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.742901893420899</v>
+        <v>5.587688328733847</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07734902563443735</v>
+        <v>0.07726351826350944</v>
       </c>
       <c r="C39">
-        <v>1169.087271715712</v>
+        <v>1158.619422542373</v>
       </c>
       <c r="D39">
-        <v>1627.554271715712</v>
+        <v>1631.977422542373</v>
       </c>
       <c r="E39">
-        <v>-233.2329999999999</v>
+        <v>-218.342</v>
       </c>
       <c r="F39">
-        <v>550.967</v>
+        <v>565.8579999999999</v>
       </c>
       <c r="G39">
         <v>92.5</v>
@@ -4479,28 +4479,28 @@
         <v>188.525</v>
       </c>
       <c r="M39">
-        <v>33.73935497270642</v>
+        <v>34.65122943142821</v>
       </c>
       <c r="N39">
-        <v>154.7856450272936</v>
+        <v>153.8737705685718</v>
       </c>
       <c r="O39">
-        <v>38.69641125682339</v>
+        <v>38.46844264214294</v>
       </c>
       <c r="P39">
-        <v>116.0892337704702</v>
+        <v>115.4053279264288</v>
       </c>
       <c r="Q39">
-        <v>159.1892337704702</v>
+        <v>158.5053279264288</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09580295954060976</v>
+        <v>0.09646948792691487</v>
       </c>
       <c r="T39">
-        <v>0.9746507519061343</v>
+        <v>0.9876426307638541</v>
       </c>
       <c r="U39">
         <v>0.0612366166625341</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.587688328733847</v>
+        <v>5.440643899030325</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07726351826350944</v>
+        <v>0.07717801089258153</v>
       </c>
       <c r="C40">
-        <v>1158.619422542373</v>
+        <v>1148.175680187003</v>
       </c>
       <c r="D40">
-        <v>1631.977422542373</v>
+        <v>1636.424680187003</v>
       </c>
       <c r="E40">
-        <v>-218.342</v>
+        <v>-203.4509999999999</v>
       </c>
       <c r="F40">
-        <v>565.8579999999999</v>
+        <v>580.749</v>
       </c>
       <c r="G40">
         <v>92.5</v>
@@ -4561,28 +4561,28 @@
         <v>188.525</v>
       </c>
       <c r="M40">
-        <v>34.65122943142821</v>
+        <v>35.56310389015002</v>
       </c>
       <c r="N40">
-        <v>153.8737705685718</v>
+        <v>152.96189610985</v>
       </c>
       <c r="O40">
-        <v>38.46844264214294</v>
+        <v>38.24047402746249</v>
       </c>
       <c r="P40">
-        <v>115.4053279264288</v>
+        <v>114.7214220823875</v>
       </c>
       <c r="Q40">
-        <v>158.5053279264288</v>
+        <v>157.8214220823875</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09646948792691487</v>
+        <v>0.09715786970293491</v>
       </c>
       <c r="T40">
-        <v>0.9876426307638541</v>
+        <v>1.001060472862811</v>
       </c>
       <c r="U40">
         <v>0.0612366166625341</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.440643899030325</v>
+        <v>5.301140209311598</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07717801089258153</v>
+        <v>0.0770925035216536</v>
       </c>
       <c r="C41">
-        <v>1148.175680187003</v>
+        <v>1137.756242266641</v>
       </c>
       <c r="D41">
-        <v>1636.424680187003</v>
+        <v>1640.896242266641</v>
       </c>
       <c r="E41">
-        <v>-203.4509999999999</v>
+        <v>-188.5599999999999</v>
       </c>
       <c r="F41">
-        <v>580.749</v>
+        <v>595.64</v>
       </c>
       <c r="G41">
         <v>92.5</v>
@@ -4643,28 +4643,28 @@
         <v>188.525</v>
       </c>
       <c r="M41">
-        <v>35.56310389015002</v>
+        <v>36.47497834887181</v>
       </c>
       <c r="N41">
-        <v>152.96189610985</v>
+        <v>152.0500216511282</v>
       </c>
       <c r="O41">
-        <v>38.24047402746249</v>
+        <v>38.01250541278204</v>
       </c>
       <c r="P41">
-        <v>114.7214220823875</v>
+        <v>114.0375162383461</v>
       </c>
       <c r="Q41">
-        <v>157.8214220823875</v>
+        <v>157.1375162383461</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09715786970293491</v>
+        <v>0.09786919753815562</v>
       </c>
       <c r="T41">
-        <v>1.001060472862811</v>
+        <v>1.014925576365066</v>
       </c>
       <c r="U41">
         <v>0.0612366166625341</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.301140209311598</v>
+        <v>5.168611704078809</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.0770925035216536</v>
+        <v>0.07700699615072568</v>
       </c>
       <c r="C42">
-        <v>1137.756242266641</v>
+        <v>1127.361308564212</v>
       </c>
       <c r="D42">
-        <v>1640.896242266641</v>
+        <v>1645.392308564212</v>
       </c>
       <c r="E42">
-        <v>-188.5599999999999</v>
+        <v>-173.6689999999999</v>
       </c>
       <c r="F42">
-        <v>595.64</v>
+        <v>610.5310000000001</v>
       </c>
       <c r="G42">
         <v>92.5</v>
@@ -4725,28 +4725,28 @@
         <v>188.525</v>
       </c>
       <c r="M42">
-        <v>36.47497834887181</v>
+        <v>37.38685280759361</v>
       </c>
       <c r="N42">
-        <v>152.0500216511282</v>
+        <v>151.1381471924064</v>
       </c>
       <c r="O42">
-        <v>38.01250541278204</v>
+        <v>37.78453679810159</v>
       </c>
       <c r="P42">
-        <v>114.0375162383461</v>
+        <v>113.3536103943048</v>
       </c>
       <c r="Q42">
-        <v>157.1375162383461</v>
+        <v>156.4536103943048</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09786919753815562</v>
+        <v>0.0986046381813499</v>
       </c>
       <c r="T42">
-        <v>1.014925576365066</v>
+        <v>1.029260683375872</v>
       </c>
       <c r="U42">
         <v>0.0612366166625341</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.168611704078809</v>
+        <v>5.042548003979325</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07700699615072568</v>
+        <v>0.07692148877979775</v>
       </c>
       <c r="C43">
-        <v>1127.361308564212</v>
+        <v>1116.991081058287</v>
       </c>
       <c r="D43">
-        <v>1645.392308564212</v>
+        <v>1649.913081058287</v>
       </c>
       <c r="E43">
-        <v>-173.6689999999999</v>
+        <v>-158.7779999999999</v>
       </c>
       <c r="F43">
-        <v>610.5310000000001</v>
+        <v>625.422</v>
       </c>
       <c r="G43">
         <v>92.5</v>
@@ -4807,28 +4807,28 @@
         <v>188.525</v>
       </c>
       <c r="M43">
-        <v>37.38685280759361</v>
+        <v>38.2987272663154</v>
       </c>
       <c r="N43">
-        <v>151.1381471924064</v>
+        <v>150.2262727336846</v>
       </c>
       <c r="O43">
-        <v>37.78453679810159</v>
+        <v>37.55656818342114</v>
       </c>
       <c r="P43">
-        <v>113.3536103943048</v>
+        <v>112.6697045502634</v>
       </c>
       <c r="Q43">
-        <v>156.4536103943048</v>
+        <v>155.7697045502634</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.0986046381813499</v>
+        <v>0.0993654388467233</v>
       </c>
       <c r="T43">
-        <v>1.029260683375872</v>
+        <v>1.044090104421533</v>
       </c>
       <c r="U43">
         <v>0.0612366166625341</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.042548003979325</v>
+        <v>4.922487337217913</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07692148877979776</v>
+        <v>0.07683598140886984</v>
       </c>
       <c r="C44">
-        <v>1116.991081058286</v>
+        <v>1106.64576395332</v>
       </c>
       <c r="D44">
-        <v>1649.913081058286</v>
+        <v>1654.45876395332</v>
       </c>
       <c r="E44">
-        <v>-158.778</v>
+        <v>-143.8869999999999</v>
       </c>
       <c r="F44">
-        <v>625.4219999999999</v>
+        <v>640.313</v>
       </c>
       <c r="G44">
         <v>92.5</v>
@@ -4889,28 +4889,28 @@
         <v>188.525</v>
       </c>
       <c r="M44">
-        <v>38.2987272663154</v>
+        <v>39.21060172503719</v>
       </c>
       <c r="N44">
-        <v>150.2262727336846</v>
+        <v>149.3143982749628</v>
       </c>
       <c r="O44">
-        <v>37.55656818342115</v>
+        <v>37.3285995687407</v>
       </c>
       <c r="P44">
-        <v>112.6697045502634</v>
+        <v>111.9857987062221</v>
       </c>
       <c r="Q44">
-        <v>155.7697045502635</v>
+        <v>155.0857987062221</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.0993654388467233</v>
+        <v>0.1001529342722852</v>
       </c>
       <c r="T44">
-        <v>1.044090104421533</v>
+        <v>1.0594398560302</v>
       </c>
       <c r="U44">
         <v>0.0612366166625341</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.922487337217914</v>
+        <v>4.808010887515172</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07683598140886984</v>
+        <v>0.07675047403794193</v>
       </c>
       <c r="C45">
-        <v>1106.64576395332</v>
+        <v>1096.325563710405</v>
       </c>
       <c r="D45">
-        <v>1654.45876395332</v>
+        <v>1659.029563710405</v>
       </c>
       <c r="E45">
-        <v>-143.8869999999999</v>
+        <v>-128.996</v>
       </c>
       <c r="F45">
-        <v>640.313</v>
+        <v>655.204</v>
       </c>
       <c r="G45">
         <v>92.5</v>
@@ -4971,28 +4971,28 @@
         <v>188.525</v>
       </c>
       <c r="M45">
-        <v>39.21060172503719</v>
+        <v>40.12247618375899</v>
       </c>
       <c r="N45">
-        <v>149.3143982749628</v>
+        <v>148.402523816241</v>
       </c>
       <c r="O45">
-        <v>37.3285995687407</v>
+        <v>37.10063095406025</v>
       </c>
       <c r="P45">
-        <v>111.9857987062221</v>
+        <v>111.3018928621808</v>
       </c>
       <c r="Q45">
-        <v>155.0857987062221</v>
+        <v>154.4018928621808</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1001529342722852</v>
+        <v>0.1009685545344744</v>
       </c>
       <c r="T45">
-        <v>1.0594398560302</v>
+        <v>1.075337813053462</v>
       </c>
       <c r="U45">
         <v>0.0612366166625341</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.808010887515172</v>
+        <v>4.698737912798917</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07675047403794193</v>
+        <v>0.076664966667014</v>
       </c>
       <c r="C46">
-        <v>1096.325563710405</v>
+        <v>1086.03068907853</v>
       </c>
       <c r="D46">
-        <v>1659.029563710405</v>
+        <v>1663.62568907853</v>
       </c>
       <c r="E46">
-        <v>-128.996</v>
+        <v>-114.1049999999999</v>
       </c>
       <c r="F46">
-        <v>655.204</v>
+        <v>670.095</v>
       </c>
       <c r="G46">
         <v>92.5</v>
@@ -5053,28 +5053,28 @@
         <v>188.525</v>
       </c>
       <c r="M46">
-        <v>40.12247618375899</v>
+        <v>41.03435064248079</v>
       </c>
       <c r="N46">
-        <v>148.402523816241</v>
+        <v>147.4906493575192</v>
       </c>
       <c r="O46">
-        <v>37.10063095406025</v>
+        <v>36.8726623393798</v>
       </c>
       <c r="P46">
-        <v>111.3018928621808</v>
+        <v>110.6179870181394</v>
       </c>
       <c r="Q46">
-        <v>154.4018928621808</v>
+        <v>153.7179870181394</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1009685545344744</v>
+        <v>0.1018138337152886</v>
       </c>
       <c r="T46">
-        <v>1.075337813053462</v>
+        <v>1.091813877604843</v>
       </c>
       <c r="U46">
         <v>0.0612366166625341</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.698737912798917</v>
+        <v>4.594321514736719</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.076664966667014</v>
+        <v>0.07744195929608608</v>
       </c>
       <c r="C47">
-        <v>1086.03068907853</v>
+        <v>1030.288081696908</v>
       </c>
       <c r="D47">
-        <v>1663.62568907853</v>
+        <v>1622.774081696908</v>
       </c>
       <c r="E47">
-        <v>-114.1049999999999</v>
+        <v>-99.21399999999994</v>
       </c>
       <c r="F47">
-        <v>670.095</v>
+        <v>684.986</v>
       </c>
       <c r="G47">
         <v>92.5</v>
@@ -5135,45 +5135,45 @@
         <v>188.525</v>
       </c>
       <c r="M47">
-        <v>41.03435064248079</v>
+        <v>43.65869010120258</v>
       </c>
       <c r="N47">
-        <v>147.4906493575192</v>
+        <v>144.8663098987974</v>
       </c>
       <c r="O47">
-        <v>36.8726623393798</v>
+        <v>36.21657747469935</v>
       </c>
       <c r="P47">
-        <v>110.6179870181394</v>
+        <v>108.649732424098</v>
       </c>
       <c r="Q47">
-        <v>153.7179870181394</v>
+        <v>151.7497324240981</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1018138337152886</v>
+        <v>0.1026904195324293</v>
       </c>
       <c r="T47">
-        <v>1.091813877604843</v>
+        <v>1.108900166769238</v>
       </c>
       <c r="U47">
-        <v>0.0612366166625341</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V47">
         <v>0.25</v>
       </c>
       <c r="W47">
-        <v>0.04592746249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y47">
-        <v>4.594321514736719</v>
+        <v>4.318155207199106</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07744195929608608</v>
+        <v>0.07737520192515816</v>
       </c>
       <c r="C48">
-        <v>1030.288081696908</v>
+        <v>1018.828006115406</v>
       </c>
       <c r="D48">
-        <v>1622.774081696908</v>
+        <v>1626.205006115406</v>
       </c>
       <c r="E48">
-        <v>-99.21399999999994</v>
+        <v>-84.32299999999998</v>
       </c>
       <c r="F48">
-        <v>684.986</v>
+        <v>699.877</v>
       </c>
       <c r="G48">
         <v>92.5</v>
@@ -5217,28 +5217,28 @@
         <v>188.525</v>
       </c>
       <c r="M48">
-        <v>43.65869010120258</v>
+        <v>44.60779205992437</v>
       </c>
       <c r="N48">
-        <v>144.8663098987974</v>
+        <v>143.9172079400756</v>
       </c>
       <c r="O48">
-        <v>36.21657747469935</v>
+        <v>35.9793019850189</v>
       </c>
       <c r="P48">
-        <v>108.649732424098</v>
+        <v>107.9379059550567</v>
       </c>
       <c r="Q48">
-        <v>151.7497324240981</v>
+        <v>151.0379059550567</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1026904195324293</v>
+        <v>0.1036000840596507</v>
       </c>
       <c r="T48">
-        <v>1.108900166769238</v>
+        <v>1.126631221562478</v>
       </c>
       <c r="U48">
         <v>0.06373661666253409</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.318155207199106</v>
+        <v>4.226279564492742</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07737520192515816</v>
+        <v>0.07730844455423025</v>
       </c>
       <c r="C49">
-        <v>1018.828006115406</v>
+        <v>1007.38246882656</v>
       </c>
       <c r="D49">
-        <v>1626.205006115406</v>
+        <v>1629.65046882656</v>
       </c>
       <c r="E49">
-        <v>-84.32299999999998</v>
+        <v>-69.4319999999999</v>
       </c>
       <c r="F49">
-        <v>699.877</v>
+        <v>714.768</v>
       </c>
       <c r="G49">
         <v>92.5</v>
@@ -5299,28 +5299,28 @@
         <v>188.525</v>
       </c>
       <c r="M49">
-        <v>44.60779205992437</v>
+        <v>45.55689401864617</v>
       </c>
       <c r="N49">
-        <v>143.9172079400756</v>
+        <v>142.9681059813538</v>
       </c>
       <c r="O49">
-        <v>35.9793019850189</v>
+        <v>35.74202649533845</v>
       </c>
       <c r="P49">
-        <v>107.9379059550567</v>
+        <v>107.2260794860154</v>
       </c>
       <c r="Q49">
-        <v>151.0379059550567</v>
+        <v>150.3260794860154</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1036000840596507</v>
+        <v>0.104544735684073</v>
       </c>
       <c r="T49">
-        <v>1.126631221562478</v>
+        <v>1.145044240001612</v>
       </c>
       <c r="U49">
         <v>0.06373661666253409</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.226279564492742</v>
+        <v>4.13823207356581</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07730844455423024</v>
+        <v>0.07724168718330232</v>
       </c>
       <c r="C50">
-        <v>1007.382468826561</v>
+        <v>995.9515624340085</v>
       </c>
       <c r="D50">
-        <v>1629.650468826561</v>
+        <v>1633.110562434008</v>
       </c>
       <c r="E50">
-        <v>-69.43200000000002</v>
+        <v>-54.54099999999994</v>
       </c>
       <c r="F50">
-        <v>714.7679999999999</v>
+        <v>729.659</v>
       </c>
       <c r="G50">
         <v>92.5</v>
@@ -5381,28 +5381,28 @@
         <v>188.525</v>
       </c>
       <c r="M50">
-        <v>45.55689401864616</v>
+        <v>46.50599597736797</v>
       </c>
       <c r="N50">
-        <v>142.9681059813538</v>
+        <v>142.019004022632</v>
       </c>
       <c r="O50">
-        <v>35.74202649533845</v>
+        <v>35.504751005658</v>
       </c>
       <c r="P50">
-        <v>107.2260794860154</v>
+        <v>106.514253016974</v>
       </c>
       <c r="Q50">
-        <v>150.3260794860154</v>
+        <v>149.614253016974</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.104544735684073</v>
+        <v>0.1055264324702373</v>
       </c>
       <c r="T50">
-        <v>1.145044240001612</v>
+        <v>1.164179337595222</v>
       </c>
       <c r="U50">
         <v>0.06373661666253409</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.13823207356581</v>
+        <v>4.053778357778752</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07724168718330232</v>
+        <v>0.07848742981237439</v>
       </c>
       <c r="C51">
-        <v>995.9515624340085</v>
+        <v>918.8214859055222</v>
       </c>
       <c r="D51">
-        <v>1633.110562434008</v>
+        <v>1570.871485905522</v>
       </c>
       <c r="E51">
-        <v>-54.54099999999994</v>
+        <v>-39.64999999999998</v>
       </c>
       <c r="F51">
-        <v>729.659</v>
+        <v>744.55</v>
       </c>
       <c r="G51">
         <v>92.5</v>
@@ -5463,45 +5463,45 @@
         <v>188.525</v>
       </c>
       <c r="M51">
-        <v>46.50599597736797</v>
+        <v>50.06102293608976</v>
       </c>
       <c r="N51">
-        <v>142.019004022632</v>
+        <v>138.4639770639102</v>
       </c>
       <c r="O51">
-        <v>35.504751005658</v>
+        <v>34.61599426597756</v>
       </c>
       <c r="P51">
-        <v>106.514253016974</v>
+        <v>103.8479827979327</v>
       </c>
       <c r="Q51">
-        <v>149.614253016974</v>
+        <v>146.9479827979327</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1055264324702373</v>
+        <v>0.1065473971278482</v>
       </c>
       <c r="T51">
-        <v>1.164179337595222</v>
+        <v>1.184079839092576</v>
       </c>
       <c r="U51">
-        <v>0.06373661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V51">
         <v>0.25</v>
       </c>
       <c r="W51">
-        <v>0.04780246249690057</v>
+        <v>0.05042746249690057</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>4.053778357778752</v>
+        <v>3.765903869776689</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07848742981237439</v>
+        <v>0.07844692244144648</v>
       </c>
       <c r="C52">
-        <v>918.8214859055222</v>
+        <v>905.8795784753889</v>
       </c>
       <c r="D52">
-        <v>1570.871485905522</v>
+        <v>1572.820578475389</v>
       </c>
       <c r="E52">
-        <v>-39.64999999999998</v>
+        <v>-24.75900000000001</v>
       </c>
       <c r="F52">
-        <v>744.55</v>
+        <v>759.4409999999999</v>
       </c>
       <c r="G52">
         <v>92.5</v>
@@ -5545,28 +5545,28 @@
         <v>188.525</v>
       </c>
       <c r="M52">
-        <v>50.06102293608976</v>
+        <v>51.06224339481155</v>
       </c>
       <c r="N52">
-        <v>138.4639770639102</v>
+        <v>137.4627566051884</v>
       </c>
       <c r="O52">
-        <v>34.61599426597756</v>
+        <v>34.3656891512971</v>
       </c>
       <c r="P52">
-        <v>103.8479827979327</v>
+        <v>103.0970674538913</v>
       </c>
       <c r="Q52">
-        <v>146.9479827979327</v>
+        <v>146.1970674538913</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1065473971278482</v>
+        <v>0.1076100338123004</v>
       </c>
       <c r="T52">
-        <v>1.184079839092576</v>
+        <v>1.20479260595717</v>
       </c>
       <c r="U52">
         <v>0.0672366166625341</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.765903869776689</v>
+        <v>3.692062617428126</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07844692244144648</v>
+        <v>0.07840641507051856</v>
       </c>
       <c r="C53">
-        <v>905.8795784753889</v>
+        <v>892.9425138110454</v>
       </c>
       <c r="D53">
-        <v>1572.820578475389</v>
+        <v>1574.774513811045</v>
       </c>
       <c r="E53">
-        <v>-24.75900000000001</v>
+        <v>-9.867999999999938</v>
       </c>
       <c r="F53">
-        <v>759.4409999999999</v>
+        <v>774.332</v>
       </c>
       <c r="G53">
         <v>92.5</v>
@@ -5627,28 +5627,28 @@
         <v>188.525</v>
       </c>
       <c r="M53">
-        <v>51.06224339481155</v>
+        <v>52.06346385353335</v>
       </c>
       <c r="N53">
-        <v>137.4627566051884</v>
+        <v>136.4615361464666</v>
       </c>
       <c r="O53">
-        <v>34.3656891512971</v>
+        <v>34.11538403661666</v>
       </c>
       <c r="P53">
-        <v>103.0970674538913</v>
+        <v>102.34615210985</v>
       </c>
       <c r="Q53">
-        <v>146.1970674538913</v>
+        <v>145.44615210985</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1076100338123004</v>
+        <v>0.1087169470252714</v>
       </c>
       <c r="T53">
-        <v>1.20479260595717</v>
+        <v>1.226368404774454</v>
       </c>
       <c r="U53">
         <v>0.0672366166625341</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.692062617428126</v>
+        <v>3.621061413246816</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07840641507051856</v>
+        <v>0.07836590769959065</v>
       </c>
       <c r="C54">
-        <v>892.9425138110454</v>
+        <v>880.0103099836322</v>
       </c>
       <c r="D54">
-        <v>1574.774513811045</v>
+        <v>1576.733309983632</v>
       </c>
       <c r="E54">
-        <v>-9.867999999999938</v>
+        <v>5.023000000000025</v>
       </c>
       <c r="F54">
-        <v>774.332</v>
+        <v>789.223</v>
       </c>
       <c r="G54">
         <v>92.5</v>
@@ -5709,28 +5709,28 @@
         <v>188.525</v>
       </c>
       <c r="M54">
-        <v>52.06346385353335</v>
+        <v>53.06468431225515</v>
       </c>
       <c r="N54">
-        <v>136.4615361464666</v>
+        <v>135.4603156877448</v>
       </c>
       <c r="O54">
-        <v>34.11538403661666</v>
+        <v>33.86507892193621</v>
       </c>
       <c r="P54">
-        <v>102.34615210985</v>
+        <v>101.5952367658086</v>
       </c>
       <c r="Q54">
-        <v>145.44615210985</v>
+        <v>144.6952367658087</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1087169470252714</v>
+        <v>0.109870962928156</v>
       </c>
       <c r="T54">
-        <v>1.226368404774454</v>
+        <v>1.248862322690347</v>
       </c>
       <c r="U54">
         <v>0.0672366166625341</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.621061413246816</v>
+        <v>3.552739499789329</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07836590769959065</v>
+        <v>0.07945940032866272</v>
       </c>
       <c r="C55">
-        <v>880.0103099836322</v>
+        <v>813.8959894359004</v>
       </c>
       <c r="D55">
-        <v>1576.733309983632</v>
+        <v>1525.5099894359</v>
       </c>
       <c r="E55">
-        <v>5.023000000000025</v>
+        <v>19.9140000000001</v>
       </c>
       <c r="F55">
-        <v>789.223</v>
+        <v>804.114</v>
       </c>
       <c r="G55">
         <v>92.5</v>
@@ -5791,45 +5791,45 @@
         <v>188.525</v>
       </c>
       <c r="M55">
-        <v>53.06468431225515</v>
+        <v>56.31742397097694</v>
       </c>
       <c r="N55">
-        <v>135.4603156877448</v>
+        <v>132.207576029023</v>
       </c>
       <c r="O55">
-        <v>33.86507892193621</v>
+        <v>33.05189400725576</v>
       </c>
       <c r="P55">
-        <v>101.5952367658086</v>
+        <v>99.15568202176729</v>
       </c>
       <c r="Q55">
-        <v>144.6952367658087</v>
+        <v>142.2556820217673</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.109870962928156</v>
+        <v>0.1110751534355139</v>
       </c>
       <c r="T55">
-        <v>1.248862322690347</v>
+        <v>1.272334237037365</v>
       </c>
       <c r="U55">
-        <v>0.0672366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V55">
         <v>0.25</v>
       </c>
       <c r="W55">
-        <v>0.05042746249690057</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y55">
-        <v>3.552739499789329</v>
+        <v>3.347543028551092</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07945940032866272</v>
+        <v>0.07943989295773479</v>
       </c>
       <c r="C56">
-        <v>813.8959894359004</v>
+        <v>799.8896144035117</v>
       </c>
       <c r="D56">
-        <v>1525.5099894359</v>
+        <v>1526.394614403512</v>
       </c>
       <c r="E56">
-        <v>19.9140000000001</v>
+        <v>34.80500000000006</v>
       </c>
       <c r="F56">
-        <v>804.114</v>
+        <v>819.005</v>
       </c>
       <c r="G56">
         <v>92.5</v>
@@ -5873,28 +5873,28 @@
         <v>188.525</v>
       </c>
       <c r="M56">
-        <v>56.31742397097694</v>
+        <v>57.36033922969874</v>
       </c>
       <c r="N56">
-        <v>132.207576029023</v>
+        <v>131.1646607703012</v>
       </c>
       <c r="O56">
-        <v>33.05189400725576</v>
+        <v>32.79116519257531</v>
       </c>
       <c r="P56">
-        <v>99.15568202176729</v>
+        <v>98.37349557772592</v>
       </c>
       <c r="Q56">
-        <v>142.2556820217673</v>
+        <v>141.4734955777259</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1110751534355139</v>
+        <v>0.1123328635209766</v>
       </c>
       <c r="T56">
-        <v>1.272334237037365</v>
+        <v>1.296849347577584</v>
       </c>
       <c r="U56">
         <v>0.07003661666253409</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.347543028551092</v>
+        <v>3.286678609850162</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07943989295773479</v>
+        <v>0.07942038558680688</v>
       </c>
       <c r="C57">
-        <v>799.8896144035117</v>
+        <v>785.884265933256</v>
       </c>
       <c r="D57">
-        <v>1526.394614403512</v>
+        <v>1527.280265933256</v>
       </c>
       <c r="E57">
-        <v>34.80500000000006</v>
+        <v>49.69600000000014</v>
       </c>
       <c r="F57">
-        <v>819.005</v>
+        <v>833.8960000000001</v>
       </c>
       <c r="G57">
         <v>92.5</v>
@@ -5955,28 +5955,28 @@
         <v>188.525</v>
       </c>
       <c r="M57">
-        <v>57.36033922969874</v>
+        <v>58.40325448842054</v>
       </c>
       <c r="N57">
-        <v>131.1646607703012</v>
+        <v>130.1217455115794</v>
       </c>
       <c r="O57">
-        <v>32.79116519257531</v>
+        <v>32.53043637789486</v>
       </c>
       <c r="P57">
-        <v>98.37349557772592</v>
+        <v>97.59130913368458</v>
       </c>
       <c r="Q57">
-        <v>141.4734955777259</v>
+        <v>140.6913091336846</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1123328635209766</v>
+        <v>0.1136477422466876</v>
       </c>
       <c r="T57">
-        <v>1.296849347577584</v>
+        <v>1.322478781324176</v>
       </c>
       <c r="U57">
         <v>0.07003661666253409</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.286678609850162</v>
+        <v>3.227987920388552</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07942038558680688</v>
+        <v>0.07940087821587896</v>
       </c>
       <c r="C58">
-        <v>785.884265933256</v>
+        <v>771.87994581308</v>
       </c>
       <c r="D58">
-        <v>1527.280265933256</v>
+        <v>1528.16694581308</v>
       </c>
       <c r="E58">
-        <v>49.69600000000014</v>
+        <v>64.5870000000001</v>
       </c>
       <c r="F58">
-        <v>833.8960000000001</v>
+        <v>848.787</v>
       </c>
       <c r="G58">
         <v>92.5</v>
@@ -6037,28 +6037,28 @@
         <v>188.525</v>
       </c>
       <c r="M58">
-        <v>58.40325448842054</v>
+        <v>59.44616974714233</v>
       </c>
       <c r="N58">
-        <v>130.1217455115794</v>
+        <v>129.0788302528576</v>
       </c>
       <c r="O58">
-        <v>32.53043637789486</v>
+        <v>32.26970756321441</v>
       </c>
       <c r="P58">
-        <v>97.59130913368458</v>
+        <v>96.80912268964323</v>
       </c>
       <c r="Q58">
-        <v>140.6913091336846</v>
+        <v>139.9091226896433</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1136477422466876</v>
+        <v>0.1150237781224317</v>
       </c>
       <c r="T58">
-        <v>1.322478781324176</v>
+        <v>1.349300281756657</v>
       </c>
       <c r="U58">
         <v>0.07003661666253409</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.227987920388552</v>
+        <v>3.171356553364192</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07940087821587896</v>
+        <v>0.07938137084495103</v>
       </c>
       <c r="C59">
-        <v>771.87994581308</v>
+        <v>757.8766558350866</v>
       </c>
       <c r="D59">
-        <v>1528.16694581308</v>
+        <v>1529.054655835087</v>
       </c>
       <c r="E59">
-        <v>64.5870000000001</v>
+        <v>79.47800000000007</v>
       </c>
       <c r="F59">
-        <v>848.787</v>
+        <v>863.678</v>
       </c>
       <c r="G59">
         <v>92.5</v>
@@ -6119,28 +6119,28 @@
         <v>188.525</v>
       </c>
       <c r="M59">
-        <v>59.44616974714233</v>
+        <v>60.48908500586412</v>
       </c>
       <c r="N59">
-        <v>129.0788302528576</v>
+        <v>128.0359149941359</v>
       </c>
       <c r="O59">
-        <v>32.26970756321441</v>
+        <v>32.00897874853396</v>
       </c>
       <c r="P59">
-        <v>96.80912268964323</v>
+        <v>96.02693624560189</v>
       </c>
       <c r="Q59">
-        <v>139.9091226896433</v>
+        <v>139.1269362456019</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1150237781224317</v>
+        <v>0.1164653395160684</v>
       </c>
       <c r="T59">
-        <v>1.349300281756657</v>
+        <v>1.377398996495446</v>
       </c>
       <c r="U59">
         <v>0.07003661666253409</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.171356553364192</v>
+        <v>3.116677992099292</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07938137084495103</v>
+        <v>0.07936186347402312</v>
       </c>
       <c r="C60">
-        <v>757.8766558350867</v>
+        <v>743.8743977955418</v>
       </c>
       <c r="D60">
-        <v>1529.054655835087</v>
+        <v>1529.943397795542</v>
       </c>
       <c r="E60">
-        <v>79.47799999999995</v>
+        <v>94.36899999999991</v>
       </c>
       <c r="F60">
-        <v>863.6779999999999</v>
+        <v>878.5689999999998</v>
       </c>
       <c r="G60">
         <v>92.5</v>
@@ -6201,28 +6201,28 @@
         <v>188.525</v>
       </c>
       <c r="M60">
-        <v>60.48908500586411</v>
+        <v>61.5320002645859</v>
       </c>
       <c r="N60">
-        <v>128.0359149941359</v>
+        <v>126.9929997354141</v>
       </c>
       <c r="O60">
-        <v>32.00897874853396</v>
+        <v>31.74824993385352</v>
       </c>
       <c r="P60">
-        <v>96.02693624560189</v>
+        <v>95.24474980156056</v>
       </c>
       <c r="Q60">
-        <v>139.1269362456019</v>
+        <v>138.3447498015606</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1164653395160683</v>
+        <v>0.1179772209776873</v>
       </c>
       <c r="T60">
-        <v>1.377398996495446</v>
+        <v>1.406868380245883</v>
       </c>
       <c r="U60">
         <v>0.07003661666253409</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.116677992099292</v>
+        <v>3.063852941385745</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07936186347402312</v>
+        <v>0.0793423561030952</v>
       </c>
       <c r="C61">
-        <v>743.8743977955418</v>
+        <v>729.8731734948927</v>
       </c>
       <c r="D61">
-        <v>1529.943397795542</v>
+        <v>1530.833173494893</v>
       </c>
       <c r="E61">
-        <v>94.36899999999991</v>
+        <v>109.26</v>
       </c>
       <c r="F61">
-        <v>878.5689999999998</v>
+        <v>893.4599999999999</v>
       </c>
       <c r="G61">
         <v>92.5</v>
@@ -6283,28 +6283,28 @@
         <v>188.525</v>
       </c>
       <c r="M61">
-        <v>61.5320002645859</v>
+        <v>62.5749155233077</v>
       </c>
       <c r="N61">
-        <v>126.9929997354141</v>
+        <v>125.9500844766923</v>
       </c>
       <c r="O61">
-        <v>31.74824993385352</v>
+        <v>31.48752111917307</v>
       </c>
       <c r="P61">
-        <v>95.24474980156056</v>
+        <v>94.4625633575192</v>
       </c>
       <c r="Q61">
-        <v>138.3447498015606</v>
+        <v>137.5625633575192</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1179772209776873</v>
+        <v>0.1195646965123871</v>
       </c>
       <c r="T61">
-        <v>1.406868380245883</v>
+        <v>1.437811233183843</v>
       </c>
       <c r="U61">
         <v>0.07003661666253409</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.063852941385745</v>
+        <v>3.012788725695982</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.0793423561030952</v>
+        <v>0.08289134873216727</v>
       </c>
       <c r="C62">
-        <v>729.8731734948927</v>
+        <v>568.5082426518034</v>
       </c>
       <c r="D62">
-        <v>1530.833173494893</v>
+        <v>1384.359242651803</v>
       </c>
       <c r="E62">
-        <v>109.26</v>
+        <v>124.151</v>
       </c>
       <c r="F62">
-        <v>893.4599999999999</v>
+        <v>908.3509999999999</v>
       </c>
       <c r="G62">
         <v>92.5</v>
@@ -6365,45 +6365,45 @@
         <v>188.525</v>
       </c>
       <c r="M62">
-        <v>62.5749155233077</v>
+        <v>70.70296858202951</v>
       </c>
       <c r="N62">
-        <v>125.9500844766923</v>
+        <v>117.8220314179705</v>
       </c>
       <c r="O62">
-        <v>31.48752111917307</v>
+        <v>29.45550785449262</v>
       </c>
       <c r="P62">
-        <v>94.4625633575192</v>
+        <v>88.36652356347784</v>
       </c>
       <c r="Q62">
-        <v>137.5625633575192</v>
+        <v>131.4665235634779</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1195646965123871</v>
+        <v>0.1212335810488665</v>
       </c>
       <c r="T62">
-        <v>1.437811233183843</v>
+        <v>1.47034089909298</v>
       </c>
       <c r="U62">
-        <v>0.07003661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V62">
         <v>0.25</v>
       </c>
       <c r="W62">
-        <v>0.05252746249690057</v>
+        <v>0.05837746249690058</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y62">
-        <v>3.012788725695982</v>
+        <v>2.666436838239309</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08289134873216727</v>
+        <v>0.08293034136123936</v>
       </c>
       <c r="C63">
-        <v>568.5082426518034</v>
+        <v>552.1634502956795</v>
       </c>
       <c r="D63">
-        <v>1384.359242651803</v>
+        <v>1382.905450295679</v>
       </c>
       <c r="E63">
-        <v>124.151</v>
+        <v>139.042</v>
       </c>
       <c r="F63">
-        <v>908.3509999999999</v>
+        <v>923.242</v>
       </c>
       <c r="G63">
         <v>92.5</v>
@@ -6447,28 +6447,28 @@
         <v>188.525</v>
       </c>
       <c r="M63">
-        <v>70.70296858202951</v>
+        <v>71.86203364075131</v>
       </c>
       <c r="N63">
-        <v>117.8220314179705</v>
+        <v>116.6629663592487</v>
       </c>
       <c r="O63">
-        <v>29.45550785449262</v>
+        <v>29.16574158981217</v>
       </c>
       <c r="P63">
-        <v>88.36652356347784</v>
+        <v>87.4972247694365</v>
       </c>
       <c r="Q63">
-        <v>131.4665235634779</v>
+        <v>130.5972247694365</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1212335810488665</v>
+        <v>0.1229903016135816</v>
       </c>
       <c r="T63">
-        <v>1.47034089909298</v>
+        <v>1.504582652681544</v>
       </c>
       <c r="U63">
         <v>0.07783661666253411</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.666436838239309</v>
+        <v>2.623429792461256</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08293034136123936</v>
+        <v>0.08296933399031145</v>
       </c>
       <c r="C64">
-        <v>552.1634502956795</v>
+        <v>535.821708152191</v>
       </c>
       <c r="D64">
-        <v>1382.905450295679</v>
+        <v>1381.454708152191</v>
       </c>
       <c r="E64">
-        <v>139.042</v>
+        <v>153.933</v>
       </c>
       <c r="F64">
-        <v>923.242</v>
+        <v>938.1329999999999</v>
       </c>
       <c r="G64">
         <v>92.5</v>
@@ -6529,28 +6529,28 @@
         <v>188.525</v>
       </c>
       <c r="M64">
-        <v>71.86203364075131</v>
+        <v>73.0210986994731</v>
       </c>
       <c r="N64">
-        <v>116.6629663592487</v>
+        <v>115.5039013005269</v>
       </c>
       <c r="O64">
-        <v>29.16574158981217</v>
+        <v>28.87597532513172</v>
       </c>
       <c r="P64">
-        <v>87.4972247694365</v>
+        <v>86.62792597539516</v>
       </c>
       <c r="Q64">
-        <v>130.5972247694365</v>
+        <v>129.7279259753952</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1229903016135816</v>
+        <v>0.1248419800466597</v>
       </c>
       <c r="T64">
-        <v>1.504582652681544</v>
+        <v>1.540675311869491</v>
       </c>
       <c r="U64">
         <v>0.07783661666253411</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.623429792461256</v>
+        <v>2.581788049723776</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08296933399031145</v>
+        <v>0.08300832661938351</v>
       </c>
       <c r="C65">
-        <v>535.821708152191</v>
+        <v>519.4830066318874</v>
       </c>
       <c r="D65">
-        <v>1381.454708152191</v>
+        <v>1380.007006631887</v>
       </c>
       <c r="E65">
-        <v>153.933</v>
+        <v>168.8240000000001</v>
       </c>
       <c r="F65">
-        <v>938.1329999999999</v>
+        <v>953.024</v>
       </c>
       <c r="G65">
         <v>92.5</v>
@@ -6611,28 +6611,28 @@
         <v>188.525</v>
       </c>
       <c r="M65">
-        <v>73.0210986994731</v>
+        <v>74.18016375819491</v>
       </c>
       <c r="N65">
-        <v>115.5039013005269</v>
+        <v>114.3448362418051</v>
       </c>
       <c r="O65">
-        <v>28.87597532513172</v>
+        <v>28.58620906045127</v>
       </c>
       <c r="P65">
-        <v>86.62792597539516</v>
+        <v>85.7586271813538</v>
       </c>
       <c r="Q65">
-        <v>129.7279259753952</v>
+        <v>128.8586271813538</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1248419800466597</v>
+        <v>0.1267965295037976</v>
       </c>
       <c r="T65">
-        <v>1.540675311869491</v>
+        <v>1.578773118790102</v>
       </c>
       <c r="U65">
         <v>0.07783661666253411</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.581788049723776</v>
+        <v>2.541447611446841</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08300832661938351</v>
+        <v>0.0830473192484556</v>
       </c>
       <c r="C66">
-        <v>519.4830066318874</v>
+        <v>503.147336185471</v>
       </c>
       <c r="D66">
-        <v>1380.007006631887</v>
+        <v>1378.562336185471</v>
       </c>
       <c r="E66">
-        <v>168.8240000000001</v>
+        <v>183.715</v>
       </c>
       <c r="F66">
-        <v>953.024</v>
+        <v>967.915</v>
       </c>
       <c r="G66">
         <v>92.5</v>
@@ -6693,28 +6693,28 @@
         <v>188.525</v>
       </c>
       <c r="M66">
-        <v>74.18016375819491</v>
+        <v>75.3392288169167</v>
       </c>
       <c r="N66">
-        <v>114.3448362418051</v>
+        <v>113.1857711830833</v>
       </c>
       <c r="O66">
-        <v>28.58620906045127</v>
+        <v>28.29644279577082</v>
       </c>
       <c r="P66">
-        <v>85.7586271813538</v>
+        <v>84.88932838731246</v>
       </c>
       <c r="Q66">
-        <v>128.8586271813538</v>
+        <v>127.9893283873125</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1267965295037976</v>
+        <v>0.1288627675013435</v>
       </c>
       <c r="T66">
-        <v>1.578773118790102</v>
+        <v>1.619047943249033</v>
       </c>
       <c r="U66">
         <v>0.07783661666253411</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.541447611446841</v>
+        <v>2.502348417424582</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.0830473192484556</v>
+        <v>0.08501681187752766</v>
       </c>
       <c r="C67">
-        <v>503.147336185471</v>
+        <v>419.0240801746386</v>
       </c>
       <c r="D67">
-        <v>1378.562336185471</v>
+        <v>1309.330080174639</v>
       </c>
       <c r="E67">
-        <v>183.715</v>
+        <v>198.6060000000001</v>
       </c>
       <c r="F67">
-        <v>967.915</v>
+        <v>982.806</v>
       </c>
       <c r="G67">
         <v>92.5</v>
@@ -6775,45 +6775,45 @@
         <v>188.525</v>
       </c>
       <c r="M67">
-        <v>75.3392288169167</v>
+        <v>80.33123727563849</v>
       </c>
       <c r="N67">
-        <v>113.1857711830833</v>
+        <v>108.1937627243615</v>
       </c>
       <c r="O67">
-        <v>28.29644279577082</v>
+        <v>27.04844068109037</v>
       </c>
       <c r="P67">
-        <v>84.88932838731246</v>
+        <v>81.14532204327112</v>
       </c>
       <c r="Q67">
-        <v>127.9893283873125</v>
+        <v>124.2453220432711</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1288627675013435</v>
+        <v>0.1310505489105097</v>
       </c>
       <c r="T67">
-        <v>1.619047943249033</v>
+        <v>1.661691875029078</v>
       </c>
       <c r="U67">
-        <v>0.07783661666253411</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V67">
         <v>0.25</v>
       </c>
       <c r="W67">
-        <v>0.05837746249690058</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y67">
-        <v>2.502348417424582</v>
+        <v>2.346845466267612</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08501681187752766</v>
+        <v>0.08508505450659976</v>
       </c>
       <c r="C68">
-        <v>419.0240801746386</v>
+        <v>401.8586241985298</v>
       </c>
       <c r="D68">
-        <v>1309.330080174639</v>
+        <v>1307.05562419853</v>
       </c>
       <c r="E68">
-        <v>198.6060000000001</v>
+        <v>213.4970000000001</v>
       </c>
       <c r="F68">
-        <v>982.806</v>
+        <v>997.697</v>
       </c>
       <c r="G68">
         <v>92.5</v>
@@ -6857,28 +6857,28 @@
         <v>188.525</v>
       </c>
       <c r="M68">
-        <v>80.33123727563849</v>
+        <v>81.54837723436027</v>
       </c>
       <c r="N68">
-        <v>108.1937627243615</v>
+        <v>106.9766227656397</v>
       </c>
       <c r="O68">
-        <v>27.04844068109037</v>
+        <v>26.74415569140993</v>
       </c>
       <c r="P68">
-        <v>81.14532204327112</v>
+        <v>80.23246707422977</v>
       </c>
       <c r="Q68">
-        <v>124.2453220432711</v>
+        <v>123.3324670742298</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1310505489105097</v>
+        <v>0.1333709231323526</v>
       </c>
       <c r="T68">
-        <v>1.661691875029078</v>
+        <v>1.706920287523065</v>
       </c>
       <c r="U68">
         <v>0.0817366166625341</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.346845466267612</v>
+        <v>2.311817921994961</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08508505450659976</v>
+        <v>0.08515329713567184</v>
       </c>
       <c r="C69">
-        <v>401.8586241985298</v>
+        <v>384.7010564994816</v>
       </c>
       <c r="D69">
-        <v>1307.05562419853</v>
+        <v>1304.789056499482</v>
       </c>
       <c r="E69">
-        <v>213.4970000000001</v>
+        <v>228.388</v>
       </c>
       <c r="F69">
-        <v>997.697</v>
+        <v>1012.588</v>
       </c>
       <c r="G69">
         <v>92.5</v>
@@ -6939,28 +6939,28 @@
         <v>188.525</v>
       </c>
       <c r="M69">
-        <v>81.54837723436027</v>
+        <v>82.76551719308208</v>
       </c>
       <c r="N69">
-        <v>106.9766227656397</v>
+        <v>105.7594828069179</v>
       </c>
       <c r="O69">
-        <v>26.74415569140993</v>
+        <v>26.43987070172948</v>
       </c>
       <c r="P69">
-        <v>80.23246707422977</v>
+        <v>79.31961210518843</v>
       </c>
       <c r="Q69">
-        <v>123.3324670742298</v>
+        <v>122.4196121051884</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1333709231323526</v>
+        <v>0.1358363207430608</v>
       </c>
       <c r="T69">
-        <v>1.706920287523065</v>
+        <v>1.754975475797926</v>
       </c>
       <c r="U69">
         <v>0.0817366166625341</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.311817921994961</v>
+        <v>2.277820599612682</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08515329713567184</v>
+        <v>0.08522153976474392</v>
       </c>
       <c r="C70">
-        <v>384.7010564994816</v>
+        <v>367.5513361113033</v>
       </c>
       <c r="D70">
-        <v>1304.789056499482</v>
+        <v>1302.530336111303</v>
       </c>
       <c r="E70">
-        <v>228.388</v>
+        <v>243.2790000000001</v>
       </c>
       <c r="F70">
-        <v>1012.588</v>
+        <v>1027.479</v>
       </c>
       <c r="G70">
         <v>92.5</v>
@@ -7021,28 +7021,28 @@
         <v>188.525</v>
       </c>
       <c r="M70">
-        <v>82.76551719308208</v>
+        <v>83.98265715180388</v>
       </c>
       <c r="N70">
-        <v>105.7594828069179</v>
+        <v>104.5423428481961</v>
       </c>
       <c r="O70">
-        <v>26.43987070172948</v>
+        <v>26.13558571204902</v>
       </c>
       <c r="P70">
-        <v>79.31961210518843</v>
+        <v>78.40675713614708</v>
       </c>
       <c r="Q70">
-        <v>122.4196121051884</v>
+        <v>121.5067571361471</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1358363207430608</v>
+        <v>0.1384607762641372</v>
       </c>
       <c r="T70">
-        <v>1.754975475797926</v>
+        <v>1.806130998800197</v>
       </c>
       <c r="U70">
         <v>0.0817366166625341</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.277820599612682</v>
+        <v>2.244808706864672</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08522153976474392</v>
+        <v>0.08528978239381599</v>
       </c>
       <c r="C71">
-        <v>367.5513361113033</v>
+        <v>350.4094223509815</v>
       </c>
       <c r="D71">
-        <v>1302.530336111303</v>
+        <v>1300.279422350982</v>
       </c>
       <c r="E71">
-        <v>243.2790000000001</v>
+        <v>258.1700000000002</v>
       </c>
       <c r="F71">
-        <v>1027.479</v>
+        <v>1042.37</v>
       </c>
       <c r="G71">
         <v>92.5</v>
@@ -7103,28 +7103,28 @@
         <v>188.525</v>
       </c>
       <c r="M71">
-        <v>83.98265715180388</v>
+        <v>85.19979711052568</v>
       </c>
       <c r="N71">
-        <v>104.5423428481961</v>
+        <v>103.3252028894743</v>
       </c>
       <c r="O71">
-        <v>26.13558571204902</v>
+        <v>25.83130072236857</v>
       </c>
       <c r="P71">
-        <v>78.40675713614708</v>
+        <v>77.49390216710572</v>
       </c>
       <c r="Q71">
-        <v>121.5067571361471</v>
+        <v>120.5939021671057</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1384607762641372</v>
+        <v>0.1412601954866186</v>
       </c>
       <c r="T71">
-        <v>1.806130998800197</v>
+        <v>1.86069689000262</v>
       </c>
       <c r="U71">
         <v>0.0817366166625341</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.244808706864672</v>
+        <v>2.21274001105232</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08528978239381599</v>
+        <v>0.08535802502288808</v>
       </c>
       <c r="C72">
-        <v>350.4094223509815</v>
+        <v>333.2752748162338</v>
       </c>
       <c r="D72">
-        <v>1300.279422350982</v>
+        <v>1298.036274816234</v>
       </c>
       <c r="E72">
-        <v>258.1700000000002</v>
+        <v>273.061</v>
       </c>
       <c r="F72">
-        <v>1042.37</v>
+        <v>1057.261</v>
       </c>
       <c r="G72">
         <v>92.5</v>
@@ -7185,28 +7185,28 @@
         <v>188.525</v>
       </c>
       <c r="M72">
-        <v>85.19979711052568</v>
+        <v>86.41693706924745</v>
       </c>
       <c r="N72">
-        <v>103.3252028894743</v>
+        <v>102.1080629307525</v>
       </c>
       <c r="O72">
-        <v>25.83130072236857</v>
+        <v>25.52701573268813</v>
       </c>
       <c r="P72">
-        <v>77.49390216710572</v>
+        <v>76.5810471980644</v>
       </c>
       <c r="Q72">
-        <v>120.5939021671057</v>
+        <v>119.6810471980644</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1412601954866186</v>
+        <v>0.1442526781037541</v>
       </c>
       <c r="T72">
-        <v>1.86069689000262</v>
+        <v>1.919025946115555</v>
       </c>
       <c r="U72">
         <v>0.0817366166625341</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.21274001105232</v>
+        <v>2.181574658783977</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08535802502288807</v>
+        <v>0.08542626765196015</v>
       </c>
       <c r="C73">
-        <v>333.2752748162343</v>
+        <v>316.148853383098</v>
       </c>
       <c r="D73">
-        <v>1298.036274816234</v>
+        <v>1295.800853383098</v>
       </c>
       <c r="E73">
-        <v>273.061</v>
+        <v>287.9519999999999</v>
       </c>
       <c r="F73">
-        <v>1057.261</v>
+        <v>1072.152</v>
       </c>
       <c r="G73">
         <v>92.5</v>
@@ -7267,28 +7267,28 @@
         <v>188.525</v>
       </c>
       <c r="M73">
-        <v>86.41693706924745</v>
+        <v>87.63407702796924</v>
       </c>
       <c r="N73">
-        <v>102.1080629307525</v>
+        <v>100.8909229720307</v>
       </c>
       <c r="O73">
-        <v>25.52701573268813</v>
+        <v>25.22273074300768</v>
       </c>
       <c r="P73">
-        <v>76.5810471980644</v>
+        <v>75.66819222902305</v>
       </c>
       <c r="Q73">
-        <v>119.6810471980644</v>
+        <v>118.7681922290231</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.144252678103754</v>
+        <v>0.1474589094792562</v>
       </c>
       <c r="T73">
-        <v>1.919025946115555</v>
+        <v>1.981521363379413</v>
       </c>
       <c r="U73">
         <v>0.0817366166625341</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.181574658783977</v>
+        <v>2.151275010745311</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08542626765196015</v>
+        <v>0.08549451028103223</v>
       </c>
       <c r="C74">
-        <v>316.148853383098</v>
+        <v>299.0301182035316</v>
       </c>
       <c r="D74">
-        <v>1295.800853383098</v>
+        <v>1293.573118203532</v>
       </c>
       <c r="E74">
-        <v>287.9519999999999</v>
+        <v>302.843</v>
       </c>
       <c r="F74">
-        <v>1072.152</v>
+        <v>1087.043</v>
       </c>
       <c r="G74">
         <v>92.5</v>
@@ -7349,28 +7349,28 @@
         <v>188.525</v>
       </c>
       <c r="M74">
-        <v>87.63407702796924</v>
+        <v>88.85121698669104</v>
       </c>
       <c r="N74">
-        <v>100.8909229720307</v>
+        <v>99.67378301330893</v>
       </c>
       <c r="O74">
-        <v>25.22273074300768</v>
+        <v>24.91844575332723</v>
       </c>
       <c r="P74">
-        <v>75.66819222902305</v>
+        <v>74.7553372599817</v>
       </c>
       <c r="Q74">
-        <v>118.7681922290231</v>
+        <v>117.8553372599817</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1474589094792562</v>
+        <v>0.150902639475166</v>
       </c>
       <c r="T74">
-        <v>1.981521363379413</v>
+        <v>2.048646070810965</v>
       </c>
       <c r="U74">
         <v>0.0817366166625341</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.151275010745311</v>
+        <v>2.12180549005017</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08549451028103223</v>
+        <v>0.08556275291010432</v>
       </c>
       <c r="C75">
-        <v>299.0301182035316</v>
+        <v>281.9190297030507</v>
       </c>
       <c r="D75">
-        <v>1293.573118203532</v>
+        <v>1291.353029703051</v>
       </c>
       <c r="E75">
-        <v>302.843</v>
+        <v>317.734</v>
       </c>
       <c r="F75">
-        <v>1087.043</v>
+        <v>1101.934</v>
       </c>
       <c r="G75">
         <v>92.5</v>
@@ -7431,28 +7431,28 @@
         <v>188.525</v>
       </c>
       <c r="M75">
-        <v>88.85121698669104</v>
+        <v>90.06835694541284</v>
       </c>
       <c r="N75">
-        <v>99.67378301330893</v>
+        <v>98.45664305458713</v>
       </c>
       <c r="O75">
-        <v>24.91844575332723</v>
+        <v>24.61416076364678</v>
       </c>
       <c r="P75">
-        <v>74.7553372599817</v>
+        <v>73.84248229094035</v>
       </c>
       <c r="Q75">
-        <v>117.8553372599817</v>
+        <v>116.9424822909404</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.150902639475166</v>
+        <v>0.1546112717784534</v>
       </c>
       <c r="T75">
-        <v>2.048646070810965</v>
+        <v>2.120934217275714</v>
       </c>
       <c r="U75">
         <v>0.0817366166625341</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.12180549005017</v>
+        <v>2.09313244288733</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08556275291010432</v>
+        <v>0.08563099553917639</v>
       </c>
       <c r="C76">
-        <v>281.9190297030507</v>
+        <v>264.8155485783841</v>
       </c>
       <c r="D76">
-        <v>1291.353029703051</v>
+        <v>1289.140548578384</v>
       </c>
       <c r="E76">
-        <v>317.734</v>
+        <v>332.6249999999999</v>
       </c>
       <c r="F76">
-        <v>1101.934</v>
+        <v>1116.825</v>
       </c>
       <c r="G76">
         <v>92.5</v>
@@ -7513,28 +7513,28 @@
         <v>188.525</v>
       </c>
       <c r="M76">
-        <v>90.06835694541284</v>
+        <v>91.28549690413463</v>
       </c>
       <c r="N76">
-        <v>98.45664305458713</v>
+        <v>97.23950309586535</v>
       </c>
       <c r="O76">
-        <v>24.61416076364678</v>
+        <v>24.30987577396634</v>
       </c>
       <c r="P76">
-        <v>73.84248229094035</v>
+        <v>72.92962732189901</v>
       </c>
       <c r="Q76">
-        <v>116.9424822909404</v>
+        <v>116.029627321899</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1546112717784534</v>
+        <v>0.1586165946660038</v>
       </c>
       <c r="T76">
-        <v>2.120934217275714</v>
+        <v>2.199005415457642</v>
       </c>
       <c r="U76">
         <v>0.0817366166625341</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.09313244288733</v>
+        <v>2.065224010315499</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08563099553917639</v>
+        <v>0.08569923816824848</v>
       </c>
       <c r="C77">
-        <v>264.8155485783841</v>
+        <v>247.7196357951511</v>
       </c>
       <c r="D77">
-        <v>1289.140548578384</v>
+        <v>1286.935635795151</v>
       </c>
       <c r="E77">
-        <v>332.6249999999999</v>
+        <v>347.516</v>
       </c>
       <c r="F77">
-        <v>1116.825</v>
+        <v>1131.716</v>
       </c>
       <c r="G77">
         <v>92.5</v>
@@ -7595,28 +7595,28 @@
         <v>188.525</v>
       </c>
       <c r="M77">
-        <v>91.28549690413463</v>
+        <v>92.50263686285643</v>
       </c>
       <c r="N77">
-        <v>97.23950309586535</v>
+        <v>96.02236313714354</v>
       </c>
       <c r="O77">
-        <v>24.30987577396634</v>
+        <v>24.00559078428589</v>
       </c>
       <c r="P77">
-        <v>72.92962732189901</v>
+        <v>72.01677235285766</v>
       </c>
       <c r="Q77">
-        <v>116.029627321899</v>
+        <v>115.1167723528577</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1586165946660038</v>
+        <v>0.1629556944608501</v>
       </c>
       <c r="T77">
-        <v>2.199005415457642</v>
+        <v>2.283582546821397</v>
       </c>
       <c r="U77">
         <v>0.0817366166625341</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.065224010315499</v>
+        <v>2.038050010179768</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08569923816824848</v>
+        <v>0.08576748079732055</v>
       </c>
       <c r="C78">
-        <v>247.7196357951511</v>
+        <v>230.6312525855722</v>
       </c>
       <c r="D78">
-        <v>1286.935635795151</v>
+        <v>1284.738252585572</v>
       </c>
       <c r="E78">
-        <v>347.516</v>
+        <v>362.407</v>
       </c>
       <c r="F78">
-        <v>1131.716</v>
+        <v>1146.607</v>
       </c>
       <c r="G78">
         <v>92.5</v>
@@ -7677,28 +7677,28 @@
         <v>188.525</v>
       </c>
       <c r="M78">
-        <v>92.50263686285643</v>
+        <v>93.71977682157822</v>
       </c>
       <c r="N78">
-        <v>96.02236313714354</v>
+        <v>94.80522317842176</v>
       </c>
       <c r="O78">
-        <v>24.00559078428589</v>
+        <v>23.70130579460544</v>
       </c>
       <c r="P78">
-        <v>72.01677235285766</v>
+        <v>71.10391738381631</v>
       </c>
       <c r="Q78">
-        <v>115.1167723528577</v>
+        <v>114.2039173838163</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1629556944608501</v>
+        <v>0.1676721072813353</v>
       </c>
       <c r="T78">
-        <v>2.283582546821397</v>
+        <v>2.375514211347219</v>
       </c>
       <c r="U78">
         <v>0.0817366166625341</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.038050010179768</v>
+        <v>2.011581828229382</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08576748079732055</v>
+        <v>0.09414272342639263</v>
       </c>
       <c r="C79">
-        <v>230.6312525855722</v>
+        <v>-6.837083104618841</v>
       </c>
       <c r="D79">
-        <v>1284.738252585572</v>
+        <v>1062.160916895381</v>
       </c>
       <c r="E79">
-        <v>362.407</v>
+        <v>377.2980000000001</v>
       </c>
       <c r="F79">
-        <v>1146.607</v>
+        <v>1161.498</v>
       </c>
       <c r="G79">
         <v>92.5</v>
@@ -7759,45 +7759,45 @@
         <v>188.525</v>
       </c>
       <c r="M79">
-        <v>93.71977682157822</v>
+        <v>111.4301883803</v>
       </c>
       <c r="N79">
-        <v>94.80522317842176</v>
+        <v>77.09481161969994</v>
       </c>
       <c r="O79">
-        <v>23.70130579460544</v>
+        <v>19.27370290492498</v>
       </c>
       <c r="P79">
-        <v>71.10391738381631</v>
+        <v>57.82110871477495</v>
       </c>
       <c r="Q79">
-        <v>114.2039173838163</v>
+        <v>100.921108714775</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1676721072813353</v>
+        <v>0.1728172849036826</v>
       </c>
       <c r="T79">
-        <v>2.375514211347219</v>
+        <v>2.475803299920841</v>
       </c>
       <c r="U79">
-        <v>0.0817366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V79">
         <v>0.25</v>
       </c>
       <c r="W79">
-        <v>0.06130246249690057</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y79">
-        <v>2.011581828229382</v>
+        <v>1.691866474788529</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09414272342639263</v>
+        <v>0.0943174660554647</v>
       </c>
       <c r="C80">
-        <v>-6.837083104618841</v>
+        <v>-25.55360834750218</v>
       </c>
       <c r="D80">
-        <v>1062.160916895381</v>
+        <v>1058.335391652498</v>
       </c>
       <c r="E80">
-        <v>377.2980000000001</v>
+        <v>392.189</v>
       </c>
       <c r="F80">
-        <v>1161.498</v>
+        <v>1176.389</v>
       </c>
       <c r="G80">
         <v>92.5</v>
@@ -7841,28 +7841,28 @@
         <v>188.525</v>
       </c>
       <c r="M80">
-        <v>111.4301883803</v>
+        <v>112.8587805390218</v>
       </c>
       <c r="N80">
-        <v>77.09481161969994</v>
+        <v>75.66621946097816</v>
       </c>
       <c r="O80">
-        <v>19.27370290492498</v>
+        <v>18.91655486524454</v>
       </c>
       <c r="P80">
-        <v>57.82110871477495</v>
+        <v>56.74966459573362</v>
       </c>
       <c r="Q80">
-        <v>100.921108714775</v>
+        <v>99.84966459573364</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1728172849036826</v>
+        <v>0.1784524794424441</v>
       </c>
       <c r="T80">
-        <v>2.475803299920841</v>
+        <v>2.585643730263381</v>
       </c>
       <c r="U80">
         <v>0.0959366166625341</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.691866474788529</v>
+        <v>1.670450443462093</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.0943174660554647</v>
+        <v>0.09449220868453678</v>
       </c>
       <c r="C81">
-        <v>-25.55360834750218</v>
+        <v>-44.24267612412586</v>
       </c>
       <c r="D81">
-        <v>1058.335391652498</v>
+        <v>1054.537323875874</v>
       </c>
       <c r="E81">
-        <v>392.189</v>
+        <v>407.08</v>
       </c>
       <c r="F81">
-        <v>1176.389</v>
+        <v>1191.28</v>
       </c>
       <c r="G81">
         <v>92.5</v>
@@ -7923,28 +7923,28 @@
         <v>188.525</v>
       </c>
       <c r="M81">
-        <v>112.8587805390218</v>
+        <v>114.2873726977436</v>
       </c>
       <c r="N81">
-        <v>75.66621946097816</v>
+        <v>74.23762730225636</v>
       </c>
       <c r="O81">
-        <v>18.91655486524454</v>
+        <v>18.55940682556409</v>
       </c>
       <c r="P81">
-        <v>56.74966459573362</v>
+        <v>55.67822047669227</v>
       </c>
       <c r="Q81">
-        <v>99.84966459573364</v>
+        <v>98.7782204766923</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1784524794424441</v>
+        <v>0.1846511934350817</v>
       </c>
       <c r="T81">
-        <v>2.585643730263381</v>
+        <v>2.706468203640175</v>
       </c>
       <c r="U81">
         <v>0.0959366166625341</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.670450443462093</v>
+        <v>1.649569812918816</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09449220868453678</v>
+        <v>0.09466695131360886</v>
       </c>
       <c r="C82">
-        <v>-44.24267612412586</v>
+        <v>-62.90458098876798</v>
       </c>
       <c r="D82">
-        <v>1054.537323875874</v>
+        <v>1050.766419011232</v>
       </c>
       <c r="E82">
-        <v>407.08</v>
+        <v>421.9710000000001</v>
       </c>
       <c r="F82">
-        <v>1191.28</v>
+        <v>1206.171</v>
       </c>
       <c r="G82">
         <v>92.5</v>
@@ -8005,28 +8005,28 @@
         <v>188.525</v>
       </c>
       <c r="M82">
-        <v>114.2873726977436</v>
+        <v>115.7159648564654</v>
       </c>
       <c r="N82">
-        <v>74.23762730225636</v>
+        <v>72.80903514353456</v>
       </c>
       <c r="O82">
-        <v>18.55940682556409</v>
+        <v>18.20225878588364</v>
       </c>
       <c r="P82">
-        <v>55.67822047669227</v>
+        <v>54.60677635765092</v>
       </c>
       <c r="Q82">
-        <v>98.7782204766923</v>
+        <v>97.70677635765094</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1846511934350817</v>
+        <v>0.1915024036374706</v>
       </c>
       <c r="T82">
-        <v>2.706468203640175</v>
+        <v>2.840011042635579</v>
       </c>
       <c r="U82">
         <v>0.0959366166625341</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.649569812918816</v>
+        <v>1.629204753500066</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09466695131360886</v>
+        <v>0.09484169394268095</v>
       </c>
       <c r="C83">
-        <v>-62.90458098876798</v>
+        <v>-81.5396132975477</v>
       </c>
       <c r="D83">
-        <v>1050.766419011232</v>
+        <v>1047.022386702452</v>
       </c>
       <c r="E83">
-        <v>421.9710000000001</v>
+        <v>436.8620000000002</v>
       </c>
       <c r="F83">
-        <v>1206.171</v>
+        <v>1221.062</v>
       </c>
       <c r="G83">
         <v>92.5</v>
@@ -8087,28 +8087,28 @@
         <v>188.525</v>
       </c>
       <c r="M83">
-        <v>115.7159648564654</v>
+        <v>117.1445570151872</v>
       </c>
       <c r="N83">
-        <v>72.80903514353456</v>
+        <v>71.38044298481276</v>
       </c>
       <c r="O83">
-        <v>18.20225878588364</v>
+        <v>17.84511074620319</v>
       </c>
       <c r="P83">
-        <v>54.60677635765092</v>
+        <v>53.53533223860957</v>
       </c>
       <c r="Q83">
-        <v>97.70677635765094</v>
+        <v>96.63533223860959</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1915024036374706</v>
+        <v>0.1991148594179027</v>
       </c>
       <c r="T83">
-        <v>2.840011042635579</v>
+        <v>2.988391974852694</v>
       </c>
       <c r="U83">
         <v>0.0959366166625341</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.629204753500066</v>
+        <v>1.609336402847626</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09484169394268095</v>
+        <v>0.09501643657175303</v>
       </c>
       <c r="C84">
-        <v>-81.5396132975477</v>
+        <v>-100.1480592829548</v>
       </c>
       <c r="D84">
-        <v>1047.022386702452</v>
+        <v>1043.304940717045</v>
       </c>
       <c r="E84">
-        <v>436.8620000000002</v>
+        <v>451.753</v>
       </c>
       <c r="F84">
-        <v>1221.062</v>
+        <v>1235.953</v>
       </c>
       <c r="G84">
         <v>92.5</v>
@@ -8169,28 +8169,28 @@
         <v>188.525</v>
       </c>
       <c r="M84">
-        <v>117.1445570151872</v>
+        <v>118.573149173909</v>
       </c>
       <c r="N84">
-        <v>71.38044298481276</v>
+        <v>69.95185082609098</v>
       </c>
       <c r="O84">
-        <v>17.84511074620319</v>
+        <v>17.48796270652274</v>
       </c>
       <c r="P84">
-        <v>53.53533223860957</v>
+        <v>52.46388811956823</v>
       </c>
       <c r="Q84">
-        <v>96.63533223860959</v>
+        <v>95.56388811956825</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1991148594179027</v>
+        <v>0.2076228982313268</v>
       </c>
       <c r="T84">
-        <v>2.988391974852694</v>
+        <v>3.154229487330646</v>
       </c>
       <c r="U84">
         <v>0.0959366166625341</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.609336402847626</v>
+        <v>1.589946807632594</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09501643657175303</v>
+        <v>0.09519117920082511</v>
       </c>
       <c r="C85">
-        <v>-100.1480592829548</v>
+        <v>-118.7302011267952</v>
       </c>
       <c r="D85">
-        <v>1043.304940717045</v>
+        <v>1039.613798873205</v>
       </c>
       <c r="E85">
-        <v>451.753</v>
+        <v>466.6440000000001</v>
       </c>
       <c r="F85">
-        <v>1235.953</v>
+        <v>1250.844</v>
       </c>
       <c r="G85">
         <v>92.5</v>
@@ -8251,28 +8251,28 @@
         <v>188.525</v>
       </c>
       <c r="M85">
-        <v>118.573149173909</v>
+        <v>120.0017413326308</v>
       </c>
       <c r="N85">
-        <v>69.95185082609098</v>
+        <v>68.52325866736916</v>
       </c>
       <c r="O85">
-        <v>17.48796270652274</v>
+        <v>17.13081466684229</v>
       </c>
       <c r="P85">
-        <v>52.46388811956823</v>
+        <v>51.39244400052687</v>
       </c>
       <c r="Q85">
-        <v>95.56388811956825</v>
+        <v>94.49244400052689</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2076228982313268</v>
+        <v>0.217194441896429</v>
       </c>
       <c r="T85">
-        <v>3.154229487330646</v>
+        <v>3.340796688868342</v>
       </c>
       <c r="U85">
         <v>0.0959366166625341</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.589946807632594</v>
+        <v>1.571018869446491</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09519117920082511</v>
+        <v>0.0953659218298972</v>
       </c>
       <c r="C86">
-        <v>-118.730201126795</v>
+        <v>-137.2863170315932</v>
       </c>
       <c r="D86">
-        <v>1039.613798873205</v>
+        <v>1035.948682968407</v>
       </c>
       <c r="E86">
-        <v>466.6439999999999</v>
+        <v>481.535</v>
       </c>
       <c r="F86">
-        <v>1250.844</v>
+        <v>1265.735</v>
       </c>
       <c r="G86">
         <v>92.5</v>
@@ -8333,28 +8333,28 @@
         <v>188.525</v>
       </c>
       <c r="M86">
-        <v>120.0017413326308</v>
+        <v>121.4303334913526</v>
       </c>
       <c r="N86">
-        <v>68.52325866736919</v>
+        <v>67.09466650864739</v>
       </c>
       <c r="O86">
-        <v>17.1308146668423</v>
+        <v>16.77366662716185</v>
       </c>
       <c r="P86">
-        <v>51.39244400052689</v>
+        <v>50.32099988148555</v>
       </c>
       <c r="Q86">
-        <v>94.49244400052692</v>
+        <v>93.42099988148557</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2171944418964289</v>
+        <v>0.2280421913835447</v>
       </c>
       <c r="T86">
-        <v>3.34079668886834</v>
+        <v>3.552239517277729</v>
       </c>
       <c r="U86">
         <v>0.0959366166625341</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.571018869446492</v>
+        <v>1.552536294511827</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.0953659218298972</v>
+        <v>0.09554066445896926</v>
       </c>
       <c r="C87">
-        <v>-137.2863170315932</v>
+        <v>-155.8166812904878</v>
       </c>
       <c r="D87">
-        <v>1035.948682968407</v>
+        <v>1032.309318709512</v>
       </c>
       <c r="E87">
-        <v>481.535</v>
+        <v>496.426</v>
       </c>
       <c r="F87">
-        <v>1265.735</v>
+        <v>1280.626</v>
       </c>
       <c r="G87">
         <v>92.5</v>
@@ -8415,28 +8415,28 @@
         <v>188.525</v>
       </c>
       <c r="M87">
-        <v>121.4303334913526</v>
+        <v>122.8589256500744</v>
       </c>
       <c r="N87">
-        <v>67.09466650864739</v>
+        <v>65.66607434992558</v>
       </c>
       <c r="O87">
-        <v>16.77366662716185</v>
+        <v>16.4165185874814</v>
       </c>
       <c r="P87">
-        <v>50.32099988148555</v>
+        <v>49.24955576244419</v>
       </c>
       <c r="Q87">
-        <v>93.42099988148557</v>
+        <v>92.34955576244421</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2280421913835447</v>
+        <v>0.2404396193688198</v>
       </c>
       <c r="T87">
-        <v>3.552239517277729</v>
+        <v>3.793888464031316</v>
       </c>
       <c r="U87">
         <v>0.0959366166625341</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.552536294511827</v>
+        <v>1.534483546901224</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09554066445896926</v>
+        <v>0.09571540708804133</v>
       </c>
       <c r="C88">
-        <v>-155.8166812904878</v>
+        <v>-174.3215643556646</v>
       </c>
       <c r="D88">
-        <v>1032.309318709512</v>
+        <v>1028.695435644335</v>
       </c>
       <c r="E88">
-        <v>496.426</v>
+        <v>511.3169999999999</v>
       </c>
       <c r="F88">
-        <v>1280.626</v>
+        <v>1295.517</v>
       </c>
       <c r="G88">
         <v>92.5</v>
@@ -8497,28 +8497,28 @@
         <v>188.525</v>
       </c>
       <c r="M88">
-        <v>122.8589256500744</v>
+        <v>124.2875178087962</v>
       </c>
       <c r="N88">
-        <v>65.66607434992558</v>
+        <v>64.23748219120381</v>
       </c>
       <c r="O88">
-        <v>16.4165185874814</v>
+        <v>16.05937054780095</v>
       </c>
       <c r="P88">
-        <v>49.24955576244419</v>
+        <v>48.17811164340286</v>
       </c>
       <c r="Q88">
-        <v>92.34955576244421</v>
+        <v>91.27811164340288</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2404396193688198</v>
+        <v>0.2547443439672142</v>
       </c>
       <c r="T88">
-        <v>3.793888464031316</v>
+        <v>4.072714171823916</v>
       </c>
       <c r="U88">
         <v>0.0959366166625341</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.534483546901224</v>
+        <v>1.51684580498282</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09571540708804133</v>
+        <v>0.1357728356645803</v>
       </c>
       <c r="C89">
-        <v>-174.3215643556646</v>
+        <v>-647.205175525044</v>
       </c>
       <c r="D89">
-        <v>1028.695435644335</v>
+        <v>570.7028244749559</v>
       </c>
       <c r="E89">
-        <v>511.3169999999999</v>
+        <v>526.208</v>
       </c>
       <c r="F89">
-        <v>1295.517</v>
+        <v>1310.408</v>
       </c>
       <c r="G89">
         <v>92.5</v>
@@ -8579,45 +8579,45 @@
         <v>188.525</v>
       </c>
       <c r="M89">
-        <v>124.2875178087962</v>
+        <v>200.147284367518</v>
       </c>
       <c r="N89">
-        <v>64.23748219120381</v>
+        <v>-11.62228436751801</v>
       </c>
       <c r="O89">
-        <v>16.05937054780095</v>
+        <v>-2.905571091879501</v>
       </c>
       <c r="P89">
-        <v>48.17811164340286</v>
+        <v>-8.716713275638504</v>
       </c>
       <c r="Q89">
-        <v>91.27811164340288</v>
+        <v>34.38328672436152</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2547443439672142</v>
+        <v>0.2751286863463867</v>
       </c>
       <c r="T89">
-        <v>4.072714171823916</v>
+        <v>4.470042946150506</v>
       </c>
       <c r="U89">
-        <v>0.0959366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V89">
-        <v>0.25</v>
+        <v>0.2354828352977091</v>
       </c>
       <c r="W89">
-        <v>0.07195246249690057</v>
+        <v>0.1167697651170612</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y89">
-        <v>1.51684580498282</v>
+        <v>0.9419313411908365</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1357728356645803</v>
+        <v>0.1368422018312056</v>
       </c>
       <c r="C90">
-        <v>-647.205175525044</v>
+        <v>-668.7995535125684</v>
       </c>
       <c r="D90">
-        <v>570.7028244749559</v>
+        <v>563.9994464874316</v>
       </c>
       <c r="E90">
-        <v>526.208</v>
+        <v>541.099</v>
       </c>
       <c r="F90">
-        <v>1310.408</v>
+        <v>1325.299</v>
       </c>
       <c r="G90">
         <v>92.5</v>
@@ -8661,37 +8661,37 @@
         <v>188.525</v>
       </c>
       <c r="M90">
-        <v>200.147284367518</v>
+        <v>202.4216853262398</v>
       </c>
       <c r="N90">
-        <v>-11.62228436751801</v>
+        <v>-13.8966853262398</v>
       </c>
       <c r="O90">
-        <v>-2.905571091879501</v>
+        <v>-3.474171331559951</v>
       </c>
       <c r="P90">
-        <v>-8.716713275638504</v>
+        <v>-10.42251399467985</v>
       </c>
       <c r="Q90">
-        <v>34.38328672436152</v>
+        <v>32.67748600532017</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2751286863463867</v>
+        <v>0.2959767487415128</v>
       </c>
       <c r="T90">
-        <v>4.470042946150506</v>
+        <v>4.876410486709643</v>
       </c>
       <c r="U90">
         <v>0.1527366166625341</v>
       </c>
       <c r="V90">
-        <v>0.2354828352977091</v>
+        <v>0.2328369607438023</v>
       </c>
       <c r="W90">
-        <v>0.1167697651170612</v>
+        <v>0.1171738870445385</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.9419313411908365</v>
+        <v>0.9313478429752092</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1368422018312056</v>
+        <v>0.137911567997831</v>
       </c>
       <c r="C91">
-        <v>-668.7995535125684</v>
+        <v>-690.2382862151895</v>
       </c>
       <c r="D91">
-        <v>563.9994464874316</v>
+        <v>557.4517137848105</v>
       </c>
       <c r="E91">
-        <v>541.099</v>
+        <v>555.9900000000001</v>
       </c>
       <c r="F91">
-        <v>1325.299</v>
+        <v>1340.19</v>
       </c>
       <c r="G91">
         <v>92.5</v>
@@ -8743,37 +8743,37 @@
         <v>188.525</v>
       </c>
       <c r="M91">
-        <v>202.4216853262398</v>
+        <v>204.6960862849616</v>
       </c>
       <c r="N91">
-        <v>-13.8966853262398</v>
+        <v>-16.1710862849616</v>
       </c>
       <c r="O91">
-        <v>-3.474171331559951</v>
+        <v>-4.042771571240401</v>
       </c>
       <c r="P91">
-        <v>-10.42251399467985</v>
+        <v>-12.1283147137212</v>
       </c>
       <c r="Q91">
-        <v>32.67748600532017</v>
+        <v>30.97168528627882</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2959767487415128</v>
+        <v>0.3209944236156641</v>
       </c>
       <c r="T91">
-        <v>4.876410486709643</v>
+        <v>5.364051535380609</v>
       </c>
       <c r="U91">
         <v>0.1527366166625341</v>
       </c>
       <c r="V91">
-        <v>0.2328369607438023</v>
+        <v>0.2302498834022045</v>
       </c>
       <c r="W91">
-        <v>0.1171738870445385</v>
+        <v>0.1175690284847384</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.9313478429752092</v>
+        <v>0.9209995336088179</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.137911567997831</v>
+        <v>0.1389809341644563</v>
       </c>
       <c r="C92">
-        <v>-690.2382862151895</v>
+        <v>-711.5267322978469</v>
       </c>
       <c r="D92">
-        <v>557.4517137848105</v>
+        <v>551.054267702153</v>
       </c>
       <c r="E92">
-        <v>555.9900000000001</v>
+        <v>570.881</v>
       </c>
       <c r="F92">
-        <v>1340.19</v>
+        <v>1355.081</v>
       </c>
       <c r="G92">
         <v>92.5</v>
@@ -8825,37 +8825,37 @@
         <v>188.525</v>
       </c>
       <c r="M92">
-        <v>204.6960862849616</v>
+        <v>206.9704872436834</v>
       </c>
       <c r="N92">
-        <v>-16.1710862849616</v>
+        <v>-18.44548724368337</v>
       </c>
       <c r="O92">
-        <v>-4.042771571240401</v>
+        <v>-4.611371810920843</v>
       </c>
       <c r="P92">
-        <v>-12.1283147137212</v>
+        <v>-13.83411543276253</v>
       </c>
       <c r="Q92">
-        <v>30.97168528627882</v>
+        <v>29.26588456723749</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3209944236156641</v>
+        <v>0.3515715817951823</v>
       </c>
       <c r="T92">
-        <v>5.364051535380609</v>
+        <v>5.960057261534009</v>
       </c>
       <c r="U92">
         <v>0.1527366166625341</v>
       </c>
       <c r="V92">
-        <v>0.2302498834022045</v>
+        <v>0.2277196649032792</v>
       </c>
       <c r="W92">
-        <v>0.1175690284847384</v>
+        <v>0.1179554854976812</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.9209995336088179</v>
+        <v>0.9108786596131168</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1389809341644563</v>
+        <v>0.1400503003310817</v>
       </c>
       <c r="C93">
-        <v>-711.5267322978469</v>
+        <v>-732.6700072273186</v>
       </c>
       <c r="D93">
-        <v>551.054267702153</v>
+        <v>544.8019927726814</v>
       </c>
       <c r="E93">
-        <v>570.881</v>
+        <v>585.772</v>
       </c>
       <c r="F93">
-        <v>1355.081</v>
+        <v>1369.972</v>
       </c>
       <c r="G93">
         <v>92.5</v>
@@ -8907,37 +8907,37 @@
         <v>188.525</v>
       </c>
       <c r="M93">
-        <v>206.9704872436834</v>
+        <v>209.2448882024052</v>
       </c>
       <c r="N93">
-        <v>-18.44548724368337</v>
+        <v>-20.7198882024052</v>
       </c>
       <c r="O93">
-        <v>-4.611371810920843</v>
+        <v>-5.1799720506013</v>
       </c>
       <c r="P93">
-        <v>-13.83411543276253</v>
+        <v>-15.5399161518039</v>
       </c>
       <c r="Q93">
-        <v>29.26588456723749</v>
+        <v>27.56008384819612</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3515715817951823</v>
+        <v>0.3897930295195802</v>
       </c>
       <c r="T93">
-        <v>5.960057261534009</v>
+        <v>6.705064419225764</v>
       </c>
       <c r="U93">
         <v>0.1527366166625341</v>
       </c>
       <c r="V93">
-        <v>0.2277196649032792</v>
+        <v>0.2252444511543305</v>
       </c>
       <c r="W93">
-        <v>0.1179554854976812</v>
+        <v>0.1183335412712122</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.9108786596131168</v>
+        <v>0.9009778046173219</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1400503003310817</v>
+        <v>0.141119666497707</v>
       </c>
       <c r="C94">
-        <v>-732.6700072273186</v>
+        <v>-753.6729969140974</v>
       </c>
       <c r="D94">
-        <v>544.8019927726814</v>
+        <v>538.6900030859026</v>
       </c>
       <c r="E94">
-        <v>585.772</v>
+        <v>600.6630000000001</v>
       </c>
       <c r="F94">
-        <v>1369.972</v>
+        <v>1384.863</v>
       </c>
       <c r="G94">
         <v>92.5</v>
@@ -8989,37 +8989,37 @@
         <v>188.525</v>
       </c>
       <c r="M94">
-        <v>209.2448882024052</v>
+        <v>211.519289161127</v>
       </c>
       <c r="N94">
-        <v>-20.7198882024052</v>
+        <v>-22.994289161127</v>
       </c>
       <c r="O94">
-        <v>-5.1799720506013</v>
+        <v>-5.74857229028175</v>
       </c>
       <c r="P94">
-        <v>-15.5399161518039</v>
+        <v>-17.24571687084525</v>
       </c>
       <c r="Q94">
-        <v>27.56008384819612</v>
+        <v>25.85428312915477</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3897930295195802</v>
+        <v>0.4389348908795203</v>
       </c>
       <c r="T94">
-        <v>6.705064419225764</v>
+        <v>7.662930764829444</v>
       </c>
       <c r="U94">
         <v>0.1527366166625341</v>
       </c>
       <c r="V94">
-        <v>0.2252444511543305</v>
+        <v>0.222822467808585</v>
       </c>
       <c r="W94">
-        <v>0.1183335412712122</v>
+        <v>0.1187034668130544</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.9009778046173219</v>
+        <v>0.8912898712343399</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.141119666497707</v>
+        <v>0.1421890326643324</v>
       </c>
       <c r="C95">
-        <v>-753.6729969140974</v>
+        <v>-774.5403704461922</v>
       </c>
       <c r="D95">
-        <v>538.6900030859026</v>
+        <v>532.7136295538077</v>
       </c>
       <c r="E95">
-        <v>600.6630000000001</v>
+        <v>615.554</v>
       </c>
       <c r="F95">
-        <v>1384.863</v>
+        <v>1399.754</v>
       </c>
       <c r="G95">
         <v>92.5</v>
@@ -9071,37 +9071,37 @@
         <v>188.525</v>
       </c>
       <c r="M95">
-        <v>211.519289161127</v>
+        <v>213.7936901198487</v>
       </c>
       <c r="N95">
-        <v>-22.994289161127</v>
+        <v>-25.26869011984877</v>
       </c>
       <c r="O95">
-        <v>-5.74857229028175</v>
+        <v>-6.317172529962193</v>
       </c>
       <c r="P95">
-        <v>-17.24571687084525</v>
+        <v>-18.95151758988658</v>
       </c>
       <c r="Q95">
-        <v>25.85428312915477</v>
+        <v>24.14848241011344</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4389348908795203</v>
+        <v>0.5044573726927738</v>
       </c>
       <c r="T95">
-        <v>7.662930764829444</v>
+        <v>8.94008589230102</v>
       </c>
       <c r="U95">
         <v>0.1527366166625341</v>
       </c>
       <c r="V95">
-        <v>0.222822467808585</v>
+        <v>0.2204520160233873</v>
       </c>
       <c r="W95">
-        <v>0.1187034668130544</v>
+        <v>0.1190655215986872</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8912898712343399</v>
+        <v>0.8818080640935492</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1421890326643324</v>
+        <v>0.1432583988309577</v>
       </c>
       <c r="C96">
-        <v>-774.5403704461922</v>
+        <v>-795.2765919845958</v>
       </c>
       <c r="D96">
-        <v>532.7136295538077</v>
+        <v>526.8684080154042</v>
       </c>
       <c r="E96">
-        <v>615.554</v>
+        <v>630.4450000000001</v>
       </c>
       <c r="F96">
-        <v>1399.754</v>
+        <v>1414.645</v>
       </c>
       <c r="G96">
         <v>92.5</v>
@@ -9153,37 +9153,37 @@
         <v>188.525</v>
       </c>
       <c r="M96">
-        <v>213.7936901198487</v>
+        <v>216.0680910785705</v>
       </c>
       <c r="N96">
-        <v>-25.26869011984877</v>
+        <v>-27.54309107857057</v>
       </c>
       <c r="O96">
-        <v>-6.317172529962193</v>
+        <v>-6.885772769642642</v>
       </c>
       <c r="P96">
-        <v>-18.95151758988658</v>
+        <v>-20.65731830892793</v>
       </c>
       <c r="Q96">
-        <v>24.14848241011344</v>
+        <v>22.4426816910721</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5044573726927738</v>
+        <v>0.5961888472313288</v>
       </c>
       <c r="T96">
-        <v>8.94008589230102</v>
+        <v>10.72810307076123</v>
       </c>
       <c r="U96">
         <v>0.1527366166625341</v>
       </c>
       <c r="V96">
-        <v>0.2204520160233873</v>
+        <v>0.218131468486299</v>
       </c>
       <c r="W96">
-        <v>0.1190655215986872</v>
+        <v>0.1194199541783066</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8818080640935492</v>
+        <v>0.872525873945196</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1432583988309577</v>
+        <v>0.144327764997583</v>
       </c>
       <c r="C97">
-        <v>-795.2765919845958</v>
+        <v>-815.885931884108</v>
       </c>
       <c r="D97">
-        <v>526.8684080154042</v>
+        <v>521.1500681158921</v>
       </c>
       <c r="E97">
-        <v>630.4450000000001</v>
+        <v>645.3360000000001</v>
       </c>
       <c r="F97">
-        <v>1414.645</v>
+        <v>1429.536</v>
       </c>
       <c r="G97">
         <v>92.5</v>
@@ -9235,37 +9235,37 @@
         <v>188.525</v>
       </c>
       <c r="M97">
-        <v>216.0680910785705</v>
+        <v>218.3424920372924</v>
       </c>
       <c r="N97">
-        <v>-27.54309107857057</v>
+        <v>-29.8174920372924</v>
       </c>
       <c r="O97">
-        <v>-6.885772769642642</v>
+        <v>-7.454373009323099</v>
       </c>
       <c r="P97">
-        <v>-20.65731830892793</v>
+        <v>-22.3631190279693</v>
       </c>
       <c r="Q97">
-        <v>22.4426816910721</v>
+        <v>20.73688097203073</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5961888472313288</v>
+        <v>0.7337860590391613</v>
       </c>
       <c r="T97">
-        <v>10.72810307076123</v>
+        <v>13.41012883845154</v>
       </c>
       <c r="U97">
         <v>0.1527366166625341</v>
       </c>
       <c r="V97">
-        <v>0.218131468486299</v>
+        <v>0.2158592656895667</v>
       </c>
       <c r="W97">
-        <v>0.1194199541783066</v>
+        <v>0.1197670027458507</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.872525873945196</v>
+        <v>0.8634370627582668</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.144327764997583</v>
+        <v>0.1453971311642084</v>
       </c>
       <c r="C98">
-        <v>-815.8859318841075</v>
+        <v>-836.3724770977425</v>
       </c>
       <c r="D98">
-        <v>521.1500681158923</v>
+        <v>515.5545229022574</v>
       </c>
       <c r="E98">
-        <v>645.3359999999999</v>
+        <v>660.227</v>
       </c>
       <c r="F98">
-        <v>1429.536</v>
+        <v>1444.427</v>
       </c>
       <c r="G98">
         <v>92.5</v>
@@ -9317,37 +9317,37 @@
         <v>188.525</v>
       </c>
       <c r="M98">
-        <v>218.3424920372923</v>
+        <v>220.6168929960141</v>
       </c>
       <c r="N98">
-        <v>-29.81749203729234</v>
+        <v>-32.09189299601417</v>
       </c>
       <c r="O98">
-        <v>-7.454373009323085</v>
+        <v>-8.022973249003542</v>
       </c>
       <c r="P98">
-        <v>-22.36311902796925</v>
+        <v>-24.06891974701063</v>
       </c>
       <c r="Q98">
-        <v>20.73688097203077</v>
+        <v>19.0310802529894</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7337860590391593</v>
+        <v>0.9631147453855461</v>
       </c>
       <c r="T98">
-        <v>13.4101288384515</v>
+        <v>17.88017178460201</v>
       </c>
       <c r="U98">
         <v>0.1527366166625341</v>
       </c>
       <c r="V98">
-        <v>0.2158592656895668</v>
+        <v>0.2136339124350351</v>
       </c>
       <c r="W98">
-        <v>0.1197670027458506</v>
+        <v>0.1201068956728268</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.863437062758267</v>
+        <v>0.8545356497401404</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1453971311642084</v>
+        <v>0.1464664973308337</v>
       </c>
       <c r="C99">
-        <v>-836.3724770977425</v>
+        <v>-856.7401409179853</v>
       </c>
       <c r="D99">
-        <v>515.5545229022574</v>
+        <v>510.0778590820147</v>
       </c>
       <c r="E99">
-        <v>660.227</v>
+        <v>675.1180000000001</v>
       </c>
       <c r="F99">
-        <v>1444.427</v>
+        <v>1459.318</v>
       </c>
       <c r="G99">
         <v>92.5</v>
@@ -9399,37 +9399,37 @@
         <v>188.525</v>
       </c>
       <c r="M99">
-        <v>220.6168929960141</v>
+        <v>222.8912939547359</v>
       </c>
       <c r="N99">
-        <v>-32.09189299601417</v>
+        <v>-34.36629395473597</v>
       </c>
       <c r="O99">
-        <v>-8.022973249003542</v>
+        <v>-8.591573488683991</v>
       </c>
       <c r="P99">
-        <v>-24.06891974701063</v>
+        <v>-25.77472046605197</v>
       </c>
       <c r="Q99">
-        <v>19.0310802529894</v>
+        <v>17.32527953394805</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9631147453855461</v>
+        <v>1.421772118078319</v>
       </c>
       <c r="T99">
-        <v>17.88017178460201</v>
+        <v>26.82025767690302</v>
       </c>
       <c r="U99">
         <v>0.1527366166625341</v>
       </c>
       <c r="V99">
-        <v>0.2136339124350351</v>
+        <v>0.2114539745530449</v>
       </c>
       <c r="W99">
-        <v>0.1201068956728268</v>
+        <v>0.1204398520094564</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8545356497401404</v>
+        <v>0.8458158982121797</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1464664973308337</v>
+        <v>0.147535863497459</v>
       </c>
       <c r="C100">
-        <v>-856.7401409179853</v>
+        <v>-876.9926721036975</v>
       </c>
       <c r="D100">
-        <v>510.0778590820147</v>
+        <v>504.7163278963024</v>
       </c>
       <c r="E100">
-        <v>675.1180000000001</v>
+        <v>690.0089999999999</v>
       </c>
       <c r="F100">
-        <v>1459.318</v>
+        <v>1474.209</v>
       </c>
       <c r="G100">
         <v>92.5</v>
@@ -9481,37 +9481,37 @@
         <v>188.525</v>
       </c>
       <c r="M100">
-        <v>222.8912939547359</v>
+        <v>225.1656949134577</v>
       </c>
       <c r="N100">
-        <v>-34.36629395473597</v>
+        <v>-36.64069491345774</v>
       </c>
       <c r="O100">
-        <v>-8.591573488683991</v>
+        <v>-9.160173728364434</v>
       </c>
       <c r="P100">
-        <v>-25.77472046605197</v>
+        <v>-27.4805211850933</v>
       </c>
       <c r="Q100">
-        <v>17.32527953394805</v>
+        <v>15.61947881490672</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.421772118078319</v>
+        <v>2.797744236156638</v>
       </c>
       <c r="T100">
-        <v>26.82025767690302</v>
+        <v>53.64051535380603</v>
       </c>
       <c r="U100">
         <v>0.1527366166625341</v>
       </c>
       <c r="V100">
-        <v>0.2114539745530449</v>
+        <v>0.2093180758201859</v>
       </c>
       <c r="W100">
-        <v>0.1204398520094564</v>
+        <v>0.1207660819554471</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8458158982121797</v>
+        <v>0.8372723032807436</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.147535863497459</v>
-      </c>
-      <c r="C101">
-        <v>-876.9926721036975</v>
-      </c>
-      <c r="D101">
-        <v>504.7163278963024</v>
-      </c>
-      <c r="E101">
-        <v>690.0089999999999</v>
-      </c>
-      <c r="F101">
-        <v>1474.209</v>
-      </c>
-      <c r="G101">
-        <v>92.5</v>
-      </c>
-      <c r="H101">
-        <v>704.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>231.625</v>
-      </c>
-      <c r="K101">
-        <v>43.10000000000002</v>
-      </c>
-      <c r="L101">
-        <v>188.525</v>
-      </c>
-      <c r="M101">
-        <v>225.1656949134577</v>
-      </c>
-      <c r="N101">
-        <v>-36.64069491345774</v>
-      </c>
-      <c r="O101">
-        <v>-9.160173728364434</v>
-      </c>
-      <c r="P101">
-        <v>-27.4805211850933</v>
-      </c>
-      <c r="Q101">
-        <v>15.61947881490672</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.797744236156638</v>
-      </c>
-      <c r="T101">
-        <v>53.64051535380603</v>
-      </c>
-      <c r="U101">
-        <v>0.1527366166625341</v>
-      </c>
-      <c r="V101">
-        <v>0.2093180758201859</v>
-      </c>
-      <c r="W101">
-        <v>0.1207660819554471</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8372723032807436</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
